--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -52331,7 +52331,7 @@
         <v>6201</v>
       </c>
       <c r="D1854">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="1855" spans="1:4">
@@ -67437,7 +67437,7 @@
         <v>7234</v>
       </c>
       <c r="D2933">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2934" spans="1:4">
@@ -80961,7 +80961,7 @@
         <v>8157</v>
       </c>
       <c r="D3899">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="3900" spans="1:4">

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4544"/>
+  <dimension ref="A1:D4680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3.24</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="126">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="131">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FANT ZA PUNJENNU PAPRIKU</t>
+          <t>FANT ZA PUNJ. PAPRIKU I SARMU 60G</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="138">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="156">
@@ -4103,11 +4103,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>FANT ZA BOLONJEZE</t>
+          <t>FANT SPAGETE BOLONJEZE 58G</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="206">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>FANT ZA GULAS I PAPRIKAS</t>
+          <t>FANT ZA GULAS I PAPRIKAS 65G</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="252">
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="268">
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="283">
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="289">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="296">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>VANILIN SECER 5/1</t>
+          <t>DOLCELA VANILIN SECER 5/1</t>
         </is>
       </c>
       <c r="D311" t="n">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="392">
@@ -10209,7 +10209,7 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="545">
@@ -10659,7 +10659,7 @@
         </is>
       </c>
       <c r="D569" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="570">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>FINI COEUR DE PECHE 100 G</t>
+          <t>FINI BRESKVA SRCE 100G</t>
         </is>
       </c>
       <c r="D624" t="n">
@@ -14277,7 +14277,7 @@
         </is>
       </c>
       <c r="D770" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="771">
@@ -15321,7 +15321,7 @@
         </is>
       </c>
       <c r="D828" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="829">
@@ -16419,7 +16419,7 @@
         </is>
       </c>
       <c r="D889" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="890">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="D890" t="n">
-        <v>8.6</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="891">
@@ -17229,7 +17229,7 @@
         </is>
       </c>
       <c r="D934" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="935">
@@ -18291,7 +18291,7 @@
         </is>
       </c>
       <c r="D993" t="n">
-        <v>6.03</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="994">
@@ -18921,7 +18921,7 @@
         </is>
       </c>
       <c r="D1028" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1029">
@@ -18939,7 +18939,7 @@
         </is>
       </c>
       <c r="D1029" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1030">
@@ -20717,7 +20717,7 @@
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>FRESH OSVJEZIVAC SUMER FLOVERS</t>
+          <t>FRESH OSVJ. SUMMER FLOWERS 500ML</t>
         </is>
       </c>
       <c r="D1128" t="n">
@@ -20901,7 +20901,7 @@
         </is>
       </c>
       <c r="D1138" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="1139">
@@ -20919,7 +20919,7 @@
         </is>
       </c>
       <c r="D1139" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1140">
@@ -24213,7 +24213,7 @@
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="1323">
@@ -24231,7 +24231,7 @@
         </is>
       </c>
       <c r="D1323" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="1324">
@@ -24771,7 +24771,7 @@
         </is>
       </c>
       <c r="D1353" t="n">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="1354">
@@ -25527,7 +25527,7 @@
         </is>
       </c>
       <c r="D1395" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="1396">
@@ -25545,7 +25545,7 @@
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="1397">
@@ -25851,7 +25851,7 @@
         </is>
       </c>
       <c r="D1413" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="1414">
@@ -26931,7 +26931,7 @@
         </is>
       </c>
       <c r="D1473" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1474">
@@ -26985,7 +26985,7 @@
         </is>
       </c>
       <c r="D1476" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="1477">
@@ -27147,7 +27147,7 @@
         </is>
       </c>
       <c r="D1485" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1486">
@@ -27705,7 +27705,7 @@
         </is>
       </c>
       <c r="D1516" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="1517">
@@ -28695,7 +28695,7 @@
         </is>
       </c>
       <c r="D1571" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="1572">
@@ -29703,7 +29703,7 @@
         </is>
       </c>
       <c r="D1627" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1628">
@@ -32277,7 +32277,7 @@
         </is>
       </c>
       <c r="D1770" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="1771">
@@ -32385,7 +32385,7 @@
         </is>
       </c>
       <c r="D1776" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="1777">
@@ -32511,7 +32511,7 @@
         </is>
       </c>
       <c r="D1783" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1784">
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="D1787" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="1788">
@@ -33231,7 +33231,7 @@
         </is>
       </c>
       <c r="D1823" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="1824">
@@ -33285,7 +33285,7 @@
         </is>
       </c>
       <c r="D1826" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="1827">
@@ -33897,7 +33897,7 @@
         </is>
       </c>
       <c r="D1860" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1861">
@@ -34275,7 +34275,7 @@
         </is>
       </c>
       <c r="D1881" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1882">
@@ -36917,11 +36917,11 @@
       </c>
       <c r="C2028" t="inlineStr">
         <is>
-          <t>ŠLAG 5+ 0,5L</t>
+          <t>DOLCELA SLAG 5+ 0,5L</t>
         </is>
       </c>
       <c r="D2028" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="2029">
@@ -37551,7 +37551,7 @@
         </is>
       </c>
       <c r="D2063" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="2064">
@@ -38019,7 +38019,7 @@
         </is>
       </c>
       <c r="D2089" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="2090">
@@ -38051,7 +38051,7 @@
       </c>
       <c r="C2091" t="inlineStr">
         <is>
-          <t>DOMESTOS ZUTI</t>
+          <t>DOMESTOS CITRUS FRESH 750ML</t>
         </is>
       </c>
       <c r="D2091" t="n">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="D2103" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="2104">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="C2132" t="inlineStr">
         <is>
-          <t>7D MINI CROI. COCOA 60G</t>
+          <t>7D MINI CROISSANT COCOA 60G</t>
         </is>
       </c>
       <c r="D2132" t="n">
@@ -41021,11 +41021,11 @@
       </c>
       <c r="C2256" t="inlineStr">
         <is>
-          <t>SMAC MULTI DEGREASER</t>
+          <t>SMAC MULTI ODMASCIVAC 650ML</t>
         </is>
       </c>
       <c r="D2256" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="2257">
@@ -41759,11 +41759,11 @@
       </c>
       <c r="C2297" t="inlineStr">
         <is>
-          <t>TOFIX 300G</t>
+          <t>TOFFIX MIX 300G</t>
         </is>
       </c>
       <c r="D2297" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="2298">
@@ -41925,7 +41925,7 @@
         </is>
       </c>
       <c r="D2306" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2307">
@@ -42285,7 +42285,7 @@
         </is>
       </c>
       <c r="D2326" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="2327">
@@ -45431,7 +45431,7 @@
       </c>
       <c r="C2501" t="inlineStr">
         <is>
-          <t>XIXO RURRI FRUITY 250ML</t>
+          <t>XIXO TURRI FRUITY 250ML</t>
         </is>
       </c>
       <c r="D2501" t="n">
@@ -47879,11 +47879,11 @@
       </c>
       <c r="C2637" t="inlineStr">
         <is>
-          <t>GREKOPS KAJSIJA 150G</t>
+          <t>GREKOS KAJSIJA 150G</t>
         </is>
       </c>
       <c r="D2637" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="2638">
@@ -47901,7 +47901,7 @@
         </is>
       </c>
       <c r="D2638" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="2639">
@@ -49481,11 +49481,11 @@
       </c>
       <c r="C2726" t="inlineStr">
         <is>
-          <t>CELER KORIJEN BRIZ</t>
+          <t>BRIZ OSUSENI CELER KORIJEN 100G</t>
         </is>
       </c>
       <c r="D2726" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="2727">
@@ -52365,7 +52365,7 @@
         </is>
       </c>
       <c r="D2886" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="2887">
@@ -53805,7 +53805,7 @@
         </is>
       </c>
       <c r="D2966" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="2967">
@@ -55673,7 +55673,7 @@
       </c>
       <c r="C3070" t="inlineStr">
         <is>
-          <t>KORNET STRACCIATELLA-SUMSKO VOCE 73G</t>
+          <t>KORNET STRACC.&amp;SUMSKO VOCE 73G</t>
         </is>
       </c>
       <c r="D3070" t="n">
@@ -55767,7 +55767,7 @@
         </is>
       </c>
       <c r="D3075" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3076">
@@ -56217,7 +56217,7 @@
         </is>
       </c>
       <c r="D3100" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3101">
@@ -58161,7 +58161,7 @@
         </is>
       </c>
       <c r="D3208" t="n">
-        <v>21.2</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="3209">
@@ -58179,7 +58179,7 @@
         </is>
       </c>
       <c r="D3209" t="n">
-        <v>21.2</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="3210">
@@ -60033,7 +60033,7 @@
         </is>
       </c>
       <c r="D3312" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3313">
@@ -60069,7 +60069,7 @@
         </is>
       </c>
       <c r="D3314" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3315">
@@ -60699,7 +60699,7 @@
         </is>
       </c>
       <c r="D3349" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3350">
@@ -61311,7 +61311,7 @@
         </is>
       </c>
       <c r="D3383" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3384">
@@ -61329,7 +61329,7 @@
         </is>
       </c>
       <c r="D3384" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3385">
@@ -62841,7 +62841,7 @@
         </is>
       </c>
       <c r="D3468" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3469">
@@ -66297,7 +66297,7 @@
         </is>
       </c>
       <c r="D3660" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3661">
@@ -66549,7 +66549,7 @@
         </is>
       </c>
       <c r="D3674" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3675">
@@ -68871,7 +68871,7 @@
         </is>
       </c>
       <c r="D3803" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3804">
@@ -69263,7 +69263,7 @@
       </c>
       <c r="C3825" t="inlineStr">
         <is>
-          <t>COKOLADNO LIZALO 22G</t>
+          <t>COKOLADNO LIZALO SA KARAKT. 22G</t>
         </is>
       </c>
       <c r="D3825" t="n">
@@ -70433,11 +70433,11 @@
       </c>
       <c r="C3890" t="inlineStr">
         <is>
-          <t>SMAC UNIVERZAL 650ML</t>
+          <t>SMAC ODMASCIVAC UNIVERZAL 650ML</t>
         </is>
       </c>
       <c r="D3890" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3891">
@@ -70923,7 +70923,7 @@
         </is>
       </c>
       <c r="D3917" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3918">
@@ -71067,7 +71067,7 @@
         </is>
       </c>
       <c r="D3925" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3926">
@@ -71175,7 +71175,7 @@
         </is>
       </c>
       <c r="D3931" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3932">
@@ -71643,7 +71643,7 @@
         </is>
       </c>
       <c r="D3957" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="3958">
@@ -73389,7 +73389,7 @@
         </is>
       </c>
       <c r="D4054" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4055">
@@ -74631,7 +74631,7 @@
         </is>
       </c>
       <c r="D4123" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4124">
@@ -74987,11 +74987,11 @@
       </c>
       <c r="C4143" t="inlineStr">
         <is>
-          <t>SL MEDENJ. DARIA NAR. 150G</t>
+          <t>SL MEDENJ. DARIA NAR. 300G</t>
         </is>
       </c>
       <c r="D4143" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4144">
@@ -75045,7 +75045,7 @@
         </is>
       </c>
       <c r="D4146" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4147">
@@ -76197,7 +76197,7 @@
         </is>
       </c>
       <c r="D4210" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4211">
@@ -77277,7 +77277,7 @@
         </is>
       </c>
       <c r="D4270" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4271">
@@ -78285,7 +78285,7 @@
         </is>
       </c>
       <c r="D4326" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4327">
@@ -78681,7 +78681,7 @@
         </is>
       </c>
       <c r="D4348" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4349">
@@ -81021,7 +81021,7 @@
         </is>
       </c>
       <c r="D4478" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="4479">
@@ -82209,6 +82209,2454 @@
         </is>
       </c>
       <c r="D4544" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4545">
+      <c r="A4545" t="n">
+        <v>4544</v>
+      </c>
+      <c r="B4545" t="inlineStr">
+        <is>
+          <t>3871284000102</t>
+        </is>
+      </c>
+      <c r="C4545" t="inlineStr">
+        <is>
+          <t>TTO TERMO ROLNA 57/30M 10/1</t>
+        </is>
+      </c>
+      <c r="D4545" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4546">
+      <c r="A4546" t="n">
+        <v>4545</v>
+      </c>
+      <c r="B4546" t="inlineStr">
+        <is>
+          <t>8606103851628</t>
+        </is>
+      </c>
+      <c r="C4546" t="inlineStr">
+        <is>
+          <t>CRICKY SUNCOKRET 40G</t>
+        </is>
+      </c>
+      <c r="D4546" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4547">
+      <c r="A4547" t="n">
+        <v>4546</v>
+      </c>
+      <c r="B4547" t="inlineStr">
+        <is>
+          <t>8684097390934</t>
+        </is>
+      </c>
+      <c r="C4547" t="inlineStr">
+        <is>
+          <t>TWINS GUMMY BABY BOTTLE 80G</t>
+        </is>
+      </c>
+      <c r="D4547" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="4548">
+      <c r="A4548" t="n">
+        <v>4547</v>
+      </c>
+      <c r="B4548" t="inlineStr">
+        <is>
+          <t>8606033742539</t>
+        </is>
+      </c>
+      <c r="C4548" t="inlineStr">
+        <is>
+          <t>CHIPSY CLIPSY CRUNCHY SWE&amp;SPI 70G</t>
+        </is>
+      </c>
+      <c r="D4548" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4549">
+      <c r="A4549" t="n">
+        <v>4548</v>
+      </c>
+      <c r="B4549" t="inlineStr">
+        <is>
+          <t>5210045008953</t>
+        </is>
+      </c>
+      <c r="C4549" t="inlineStr">
+        <is>
+          <t>MASLINE CARPOS ZELENE B.KOS. 500G</t>
+        </is>
+      </c>
+      <c r="D4549" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4550">
+      <c r="A4550" t="n">
+        <v>4549</v>
+      </c>
+      <c r="B4550" t="inlineStr">
+        <is>
+          <t>3870379090486</t>
+        </is>
+      </c>
+      <c r="C4550" t="inlineStr">
+        <is>
+          <t>TOMICO SKUS. FILETI U MAS.U. 125G</t>
+        </is>
+      </c>
+      <c r="D4550" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4551">
+      <c r="A4551" t="n">
+        <v>4550</v>
+      </c>
+      <c r="B4551" t="inlineStr">
+        <is>
+          <t>3870379001932</t>
+        </is>
+      </c>
+      <c r="C4551" t="inlineStr">
+        <is>
+          <t>FRUKTAKO MULTI&amp;ANAN 1,5L</t>
+        </is>
+      </c>
+      <c r="D4551" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4552">
+      <c r="A4552" t="n">
+        <v>4551</v>
+      </c>
+      <c r="B4552" t="inlineStr">
+        <is>
+          <t>7622202319020</t>
+        </is>
+      </c>
+      <c r="C4552" t="inlineStr">
+        <is>
+          <t>7D CROISSANT ORO 70G</t>
+        </is>
+      </c>
+      <c r="D4552" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4553">
+      <c r="A4553" t="n">
+        <v>4552</v>
+      </c>
+      <c r="B4553" t="inlineStr">
+        <is>
+          <t>8683749137408</t>
+        </is>
+      </c>
+      <c r="C4553" t="inlineStr">
+        <is>
+          <t>RITO KAFA COKOL. PRALINE 170G</t>
+        </is>
+      </c>
+      <c r="D4553" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4554">
+      <c r="A4554" t="n">
+        <v>4553</v>
+      </c>
+      <c r="B4554" t="inlineStr">
+        <is>
+          <t>8683749137392</t>
+        </is>
+      </c>
+      <c r="C4554" t="inlineStr">
+        <is>
+          <t>RITO KARAM. COKO. PRALIN. 170G</t>
+        </is>
+      </c>
+      <c r="D4554" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4555">
+      <c r="A4555" t="n">
+        <v>4554</v>
+      </c>
+      <c r="B4555" t="inlineStr">
+        <is>
+          <t>8697439306111</t>
+        </is>
+      </c>
+      <c r="C4555" t="inlineStr">
+        <is>
+          <t>GROAN COKOL. BAR SA LJES. 32G</t>
+        </is>
+      </c>
+      <c r="D4555" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4556">
+      <c r="A4556" t="n">
+        <v>4555</v>
+      </c>
+      <c r="B4556" t="inlineStr">
+        <is>
+          <t>8697439306128</t>
+        </is>
+      </c>
+      <c r="C4556" t="inlineStr">
+        <is>
+          <t>GROAN COKOL. BAR SA LJES. 32G</t>
+        </is>
+      </c>
+      <c r="D4556" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4557">
+      <c r="A4557" t="n">
+        <v>4556</v>
+      </c>
+      <c r="B4557" t="inlineStr">
+        <is>
+          <t>9694707780377</t>
+        </is>
+      </c>
+      <c r="C4557" t="inlineStr">
+        <is>
+          <t>GROAN COKOL. BAR SA JAG. 32G</t>
+        </is>
+      </c>
+      <c r="D4557" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4558">
+      <c r="A4558" t="n">
+        <v>4557</v>
+      </c>
+      <c r="B4558" t="inlineStr">
+        <is>
+          <t>8684707780384</t>
+        </is>
+      </c>
+      <c r="C4558" t="inlineStr">
+        <is>
+          <t>GROAN COKOL. BAR SA JAG. 32G</t>
+        </is>
+      </c>
+      <c r="D4558" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4559">
+      <c r="A4559" t="n">
+        <v>4558</v>
+      </c>
+      <c r="B4559" t="inlineStr">
+        <is>
+          <t>8683749024111</t>
+        </is>
+      </c>
+      <c r="C4559" t="inlineStr">
+        <is>
+          <t>BONART GUMENE BOMB. MEDO 80G</t>
+        </is>
+      </c>
+      <c r="D4559" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4560">
+      <c r="A4560" t="n">
+        <v>4559</v>
+      </c>
+      <c r="B4560" t="inlineStr">
+        <is>
+          <t>8683749124118</t>
+        </is>
+      </c>
+      <c r="C4560" t="inlineStr">
+        <is>
+          <t>BONART GUMENE BOMB. MEDO 80G</t>
+        </is>
+      </c>
+      <c r="D4560" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4561">
+      <c r="A4561" t="n">
+        <v>4560</v>
+      </c>
+      <c r="B4561" t="inlineStr">
+        <is>
+          <t>8683749026603</t>
+        </is>
+      </c>
+      <c r="C4561" t="inlineStr">
+        <is>
+          <t>BONART GUMENE BOMB. MEDO 160G</t>
+        </is>
+      </c>
+      <c r="D4561" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="4562">
+      <c r="A4562" t="n">
+        <v>4561</v>
+      </c>
+      <c r="B4562" t="inlineStr">
+        <is>
+          <t>8683749026559</t>
+        </is>
+      </c>
+      <c r="C4562" t="inlineStr">
+        <is>
+          <t>BONART GUM.BOM. KIS.PRSTEN 160G</t>
+        </is>
+      </c>
+      <c r="D4562" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="4563">
+      <c r="A4563" t="n">
+        <v>4562</v>
+      </c>
+      <c r="B4563" t="inlineStr">
+        <is>
+          <t>8683749141078</t>
+        </is>
+      </c>
+      <c r="C4563" t="inlineStr">
+        <is>
+          <t>SQUISHY COKOLADNO JAJE 20G</t>
+        </is>
+      </c>
+      <c r="D4563" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4564">
+      <c r="A4564" t="n">
+        <v>4563</v>
+      </c>
+      <c r="B4564" t="inlineStr">
+        <is>
+          <t>0890997290342</t>
+        </is>
+      </c>
+      <c r="C4564" t="inlineStr">
+        <is>
+          <t>MAGICNI KARAMEL PRSTICI 7G</t>
+        </is>
+      </c>
+      <c r="D4564" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4565">
+      <c r="A4565" t="n">
+        <v>4564</v>
+      </c>
+      <c r="B4565" t="inlineStr">
+        <is>
+          <t>8690997190345</t>
+        </is>
+      </c>
+      <c r="C4565" t="inlineStr">
+        <is>
+          <t>MAGICNI KARAMEL PRSTICI 7G</t>
+        </is>
+      </c>
+      <c r="D4565" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4566">
+      <c r="A4566" t="n">
+        <v>4565</v>
+      </c>
+      <c r="B4566" t="inlineStr">
+        <is>
+          <t>8682134082569</t>
+        </is>
+      </c>
+      <c r="C4566" t="inlineStr">
+        <is>
+          <t>DIPPOBON 15G</t>
+        </is>
+      </c>
+      <c r="D4566" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4567">
+      <c r="A4567" t="n">
+        <v>4566</v>
+      </c>
+      <c r="B4567" t="inlineStr">
+        <is>
+          <t>8682134085256</t>
+        </is>
+      </c>
+      <c r="C4567" t="inlineStr">
+        <is>
+          <t>COKOLADNO LIZALO SA KARAKT. 22G</t>
+        </is>
+      </c>
+      <c r="D4567" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4568">
+      <c r="A4568" t="n">
+        <v>4567</v>
+      </c>
+      <c r="B4568" t="inlineStr">
+        <is>
+          <t>387019900121</t>
+        </is>
+      </c>
+      <c r="C4568" t="inlineStr">
+        <is>
+          <t>VITALIA VAJKREM 200G</t>
+        </is>
+      </c>
+      <c r="D4568" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="4569">
+      <c r="A4569" t="n">
+        <v>4568</v>
+      </c>
+      <c r="B4569" t="inlineStr">
+        <is>
+          <t>8606033742553</t>
+        </is>
+      </c>
+      <c r="C4569" t="inlineStr">
+        <is>
+          <t>CHIPSY REBRASTI GRIL ODREZAK 95GR</t>
+        </is>
+      </c>
+      <c r="D4569" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4570">
+      <c r="A4570" t="n">
+        <v>4569</v>
+      </c>
+      <c r="B4570" t="inlineStr">
+        <is>
+          <t>8606033742577</t>
+        </is>
+      </c>
+      <c r="C4570" t="inlineStr">
+        <is>
+          <t>CHIPSY RAVAN SIR 95GR</t>
+        </is>
+      </c>
+      <c r="D4570" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4571">
+      <c r="A4571" t="n">
+        <v>4570</v>
+      </c>
+      <c r="B4571" t="inlineStr">
+        <is>
+          <t>8606033742591</t>
+        </is>
+      </c>
+      <c r="C4571" t="inlineStr">
+        <is>
+          <t>CHIPSY RAVAN BBQ KOBASICA 95GR</t>
+        </is>
+      </c>
+      <c r="D4571" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4572">
+      <c r="A4572" t="n">
+        <v>4571</v>
+      </c>
+      <c r="B4572" t="inlineStr">
+        <is>
+          <t>8606033742621</t>
+        </is>
+      </c>
+      <c r="C4572" t="inlineStr">
+        <is>
+          <t>CLIPSY LOPTICA SIR SVJ. KUP 110GR</t>
+        </is>
+      </c>
+      <c r="D4572" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4573">
+      <c r="A4573" t="n">
+        <v>4572</v>
+      </c>
+      <c r="B4573" t="inlineStr">
+        <is>
+          <t>5941000034433</t>
+        </is>
+      </c>
+      <c r="C4573" t="inlineStr">
+        <is>
+          <t>DORITOS BEEF BURRITO SVJ. KUP 90G</t>
+        </is>
+      </c>
+      <c r="D4573" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4574">
+      <c r="A4574" t="n">
+        <v>4573</v>
+      </c>
+      <c r="B4574" t="inlineStr">
+        <is>
+          <t>5413548280189</t>
+        </is>
+      </c>
+      <c r="C4574" t="inlineStr">
+        <is>
+          <t>COKOLADA KINDER SCHOKO BONS 125G</t>
+        </is>
+      </c>
+      <c r="D4574" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="4575">
+      <c r="A4575" t="n">
+        <v>4574</v>
+      </c>
+      <c r="B4575" t="inlineStr">
+        <is>
+          <t>3838952030847</t>
+        </is>
+      </c>
+      <c r="C4575" t="inlineStr">
+        <is>
+          <t>PALOMA CLASSIC T.PAPIR 3SL. 24/1</t>
+        </is>
+      </c>
+      <c r="D4575" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="4576">
+      <c r="A4576" t="n">
+        <v>4575</v>
+      </c>
+      <c r="B4576" t="inlineStr">
+        <is>
+          <t>8600331000780</t>
+        </is>
+      </c>
+      <c r="C4576" t="inlineStr">
+        <is>
+          <t>PIVO TUBORG LIM. 0.5L</t>
+        </is>
+      </c>
+      <c r="D4576" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4577">
+      <c r="A4577" t="n">
+        <v>4576</v>
+      </c>
+      <c r="B4577" t="inlineStr">
+        <is>
+          <t>5900649000957</t>
+        </is>
+      </c>
+      <c r="C4577" t="inlineStr">
+        <is>
+          <t>MOKATE 3U1 576G 30/1</t>
+        </is>
+      </c>
+      <c r="D4577" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4578">
+      <c r="A4578" t="n">
+        <v>4577</v>
+      </c>
+      <c r="B4578" t="inlineStr">
+        <is>
+          <t>5202287008006</t>
+        </is>
+      </c>
+      <c r="C4578" t="inlineStr">
+        <is>
+          <t>LARI PVC TANJIRI 50/1 DUBOKI</t>
+        </is>
+      </c>
+      <c r="D4578" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4579">
+      <c r="A4579" t="n">
+        <v>4578</v>
+      </c>
+      <c r="B4579" t="inlineStr">
+        <is>
+          <t>3871862002771</t>
+        </is>
+      </c>
+      <c r="C4579" t="inlineStr">
+        <is>
+          <t>TREND KOMPOT OD BRESKVE 425ML</t>
+        </is>
+      </c>
+      <c r="D4579" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="4580">
+      <c r="A4580" t="n">
+        <v>4579</v>
+      </c>
+      <c r="B4580" t="inlineStr">
+        <is>
+          <t>3871862003693</t>
+        </is>
+      </c>
+      <c r="C4580" t="inlineStr">
+        <is>
+          <t>TREND SALATA S TUNOM MEXICANA 160G</t>
+        </is>
+      </c>
+      <c r="D4580" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4581">
+      <c r="A4581" t="n">
+        <v>4580</v>
+      </c>
+      <c r="B4581" t="inlineStr">
+        <is>
+          <t>3870102003653</t>
+        </is>
+      </c>
+      <c r="C4581" t="inlineStr">
+        <is>
+          <t>CELEX TP HARMONY PREMIUM 16/1 3SL.</t>
+        </is>
+      </c>
+      <c r="D4581" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="4582">
+      <c r="A4582" t="n">
+        <v>4581</v>
+      </c>
+      <c r="B4582" t="inlineStr">
+        <is>
+          <t>3871862002924</t>
+        </is>
+      </c>
+      <c r="C4582" t="inlineStr">
+        <is>
+          <t>TREND KOMAD. TUNE U BILJ. ULJU 80G</t>
+        </is>
+      </c>
+      <c r="D4582" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4583">
+      <c r="A4583" t="n">
+        <v>4582</v>
+      </c>
+      <c r="B4583" t="inlineStr">
+        <is>
+          <t>967858473</t>
+        </is>
+      </c>
+      <c r="C4583" t="inlineStr">
+        <is>
+          <t>CASE COFFEE TO GO 230ML 50/1</t>
+        </is>
+      </c>
+      <c r="D4583" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4584">
+      <c r="A4584" t="n">
+        <v>4583</v>
+      </c>
+      <c r="B4584" t="inlineStr">
+        <is>
+          <t>967858529</t>
+        </is>
+      </c>
+      <c r="C4584" t="inlineStr">
+        <is>
+          <t>PET POKL. ZA COFFE TO GO 100/1</t>
+        </is>
+      </c>
+      <c r="D4584" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="4585">
+      <c r="A4585" t="n">
+        <v>4584</v>
+      </c>
+      <c r="B4585" t="inlineStr">
+        <is>
+          <t>8681823380047</t>
+        </is>
+      </c>
+      <c r="C4585" t="inlineStr">
+        <is>
+          <t>CASE COFFEE TO GO 100ML 50/1</t>
+        </is>
+      </c>
+      <c r="D4585" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="4586">
+      <c r="A4586" t="n">
+        <v>4585</v>
+      </c>
+      <c r="B4586" t="inlineStr">
+        <is>
+          <t>967858475</t>
+        </is>
+      </c>
+      <c r="C4586" t="inlineStr">
+        <is>
+          <t>PET POKLOPCI ZA CASU 100/1</t>
+        </is>
+      </c>
+      <c r="D4586" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4587">
+      <c r="A4587" t="n">
+        <v>4586</v>
+      </c>
+      <c r="B4587" t="inlineStr">
+        <is>
+          <t>8697502227008</t>
+        </is>
+      </c>
+      <c r="C4587" t="inlineStr">
+        <is>
+          <t>CASE COFFEE TO GO 200ML 50/1</t>
+        </is>
+      </c>
+      <c r="D4587" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="4588">
+      <c r="A4588" t="n">
+        <v>4587</v>
+      </c>
+      <c r="B4588" t="inlineStr">
+        <is>
+          <t>07301795</t>
+        </is>
+      </c>
+      <c r="C4588" t="inlineStr">
+        <is>
+          <t>POK. ZACOFFEE TO GO 180ML 100/1</t>
+        </is>
+      </c>
+      <c r="D4588" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="4589">
+      <c r="A4589" t="n">
+        <v>4588</v>
+      </c>
+      <c r="B4589" t="inlineStr">
+        <is>
+          <t>7613107500019</t>
+        </is>
+      </c>
+      <c r="C4589" t="inlineStr">
+        <is>
+          <t>SOLEA KREMA ZA BRIJ. DAMARIS 60ML</t>
+        </is>
+      </c>
+      <c r="D4589" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="4590">
+      <c r="A4590" t="n">
+        <v>4589</v>
+      </c>
+      <c r="B4590" t="inlineStr">
+        <is>
+          <t>6920354835759</t>
+        </is>
+      </c>
+      <c r="C4590" t="inlineStr">
+        <is>
+          <t>COLGATE PASTA TRIPLE ACTION 100ML</t>
+        </is>
+      </c>
+      <c r="D4590" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4591">
+      <c r="A4591" t="n">
+        <v>4590</v>
+      </c>
+      <c r="B4591" t="inlineStr">
+        <is>
+          <t>7891024132074</t>
+        </is>
+      </c>
+      <c r="C4591" t="inlineStr">
+        <is>
+          <t>COLGATE PASTA TRIPLE ACTION 100ML</t>
+        </is>
+      </c>
+      <c r="D4591" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4592">
+      <c r="A4592" t="n">
+        <v>4591</v>
+      </c>
+      <c r="B4592" t="inlineStr">
+        <is>
+          <t>3872292005639</t>
+        </is>
+      </c>
+      <c r="C4592" t="inlineStr">
+        <is>
+          <t>ACETON ALOE VERA 100ML HELLENA</t>
+        </is>
+      </c>
+      <c r="D4592" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4593">
+      <c r="A4593" t="n">
+        <v>4592</v>
+      </c>
+      <c r="B4593" t="inlineStr">
+        <is>
+          <t>10034921</t>
+        </is>
+      </c>
+      <c r="C4593" t="inlineStr">
+        <is>
+          <t>LARI PVC CASE 80ML BIJELE 100/1</t>
+        </is>
+      </c>
+      <c r="D4593" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="4594">
+      <c r="A4594" t="n">
+        <v>4593</v>
+      </c>
+      <c r="B4594" t="inlineStr">
+        <is>
+          <t>5202287005029</t>
+        </is>
+      </c>
+      <c r="C4594" t="inlineStr">
+        <is>
+          <t>LARI PVC CASE 300ML 50/1</t>
+        </is>
+      </c>
+      <c r="D4594" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="4595">
+      <c r="A4595" t="n">
+        <v>4594</v>
+      </c>
+      <c r="B4595" t="inlineStr">
+        <is>
+          <t>5310133003454</t>
+        </is>
+      </c>
+      <c r="C4595" t="inlineStr">
+        <is>
+          <t>NUTRI PLUS SLANI STAP.SUS. 160G</t>
+        </is>
+      </c>
+      <c r="D4595" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4596">
+      <c r="A4596" t="n">
+        <v>4595</v>
+      </c>
+      <c r="B4596" t="inlineStr">
+        <is>
+          <t>3871862003709</t>
+        </is>
+      </c>
+      <c r="C4596" t="inlineStr">
+        <is>
+          <t>TREND SALATA S TUNOM MEDIT. 160G</t>
+        </is>
+      </c>
+      <c r="D4596" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4597">
+      <c r="A4597" t="n">
+        <v>4596</v>
+      </c>
+      <c r="B4597" t="inlineStr">
+        <is>
+          <t>3871284050725</t>
+        </is>
+      </c>
+      <c r="C4597" t="inlineStr">
+        <is>
+          <t>TTO ROLNA TERMO 57/17M</t>
+        </is>
+      </c>
+      <c r="D4597" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4598">
+      <c r="A4598" t="n">
+        <v>4597</v>
+      </c>
+      <c r="B4598" t="inlineStr">
+        <is>
+          <t>8007380002411</t>
+        </is>
+      </c>
+      <c r="C4598" t="inlineStr">
+        <is>
+          <t>G.RUALDE 5 KAKAO 225G</t>
+        </is>
+      </c>
+      <c r="D4598" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4599">
+      <c r="A4599" t="n">
+        <v>4598</v>
+      </c>
+      <c r="B4599" t="inlineStr">
+        <is>
+          <t>8600759500251</t>
+        </is>
+      </c>
+      <c r="C4599" t="inlineStr">
+        <is>
+          <t>BRASNO T-500 25/1 SENTA</t>
+        </is>
+      </c>
+      <c r="D4599" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="4600">
+      <c r="A4600" t="n">
+        <v>4599</v>
+      </c>
+      <c r="B4600" t="inlineStr">
+        <is>
+          <t>5202287020002</t>
+        </is>
+      </c>
+      <c r="C4600" t="inlineStr">
+        <is>
+          <t>LARI PVC CASE 180ML 100/1</t>
+        </is>
+      </c>
+      <c r="D4600" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="4601">
+      <c r="A4601" t="n">
+        <v>4600</v>
+      </c>
+      <c r="B4601" t="inlineStr">
+        <is>
+          <t>8697428239444</t>
+        </is>
+      </c>
+      <c r="C4601" t="inlineStr">
+        <is>
+          <t>MY LEYDI ULOSCI NORMA 24</t>
+        </is>
+      </c>
+      <c r="D4601" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4602">
+      <c r="A4602" t="n">
+        <v>4601</v>
+      </c>
+      <c r="B4602" t="inlineStr">
+        <is>
+          <t>8697428239437</t>
+        </is>
+      </c>
+      <c r="C4602" t="inlineStr">
+        <is>
+          <t>MY LEYDI ULOSCI LONG 24</t>
+        </is>
+      </c>
+      <c r="D4602" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4603">
+      <c r="A4603" t="n">
+        <v>4602</v>
+      </c>
+      <c r="B4603" t="inlineStr">
+        <is>
+          <t>8682392716145</t>
+        </is>
+      </c>
+      <c r="C4603" t="inlineStr">
+        <is>
+          <t>BOMBON KAIS PAW PATROL 80G</t>
+        </is>
+      </c>
+      <c r="D4603" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4604">
+      <c r="A4604" t="n">
+        <v>4603</v>
+      </c>
+      <c r="B4604" t="inlineStr">
+        <is>
+          <t>8682392716152</t>
+        </is>
+      </c>
+      <c r="C4604" t="inlineStr">
+        <is>
+          <t>BOMBON KAIS PAW PATROL 80G</t>
+        </is>
+      </c>
+      <c r="D4604" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4605">
+      <c r="A4605" t="n">
+        <v>4604</v>
+      </c>
+      <c r="B4605" t="inlineStr">
+        <is>
+          <t>8682392711140</t>
+        </is>
+      </c>
+      <c r="C4605" t="inlineStr">
+        <is>
+          <t>BOMBON PICAS MIRACULIS 80G</t>
+        </is>
+      </c>
+      <c r="D4605" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4606">
+      <c r="A4606" t="n">
+        <v>4605</v>
+      </c>
+      <c r="B4606" t="inlineStr">
+        <is>
+          <t>8682392711171</t>
+        </is>
+      </c>
+      <c r="C4606" t="inlineStr">
+        <is>
+          <t>BOMBON PICAS MIRACULIS 80G</t>
+        </is>
+      </c>
+      <c r="D4606" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4607">
+      <c r="A4607" t="n">
+        <v>4606</v>
+      </c>
+      <c r="B4607" t="inlineStr">
+        <is>
+          <t>8682392711157</t>
+        </is>
+      </c>
+      <c r="C4607" t="inlineStr">
+        <is>
+          <t>BOMBON PICAS MIRACULIS 80G</t>
+        </is>
+      </c>
+      <c r="D4607" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4608">
+      <c r="A4608" t="n">
+        <v>4607</v>
+      </c>
+      <c r="B4608" t="inlineStr">
+        <is>
+          <t>6927496900246</t>
+        </is>
+      </c>
+      <c r="C4608" t="inlineStr">
+        <is>
+          <t>BELUXE SIJALICA 150W</t>
+        </is>
+      </c>
+      <c r="D4608" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4609">
+      <c r="A4609" t="n">
+        <v>4608</v>
+      </c>
+      <c r="B4609" t="inlineStr">
+        <is>
+          <t>6927496900826</t>
+        </is>
+      </c>
+      <c r="C4609" t="inlineStr">
+        <is>
+          <t>BELUXE SIJALICA 200W</t>
+        </is>
+      </c>
+      <c r="D4609" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4610">
+      <c r="A4610" t="n">
+        <v>4609</v>
+      </c>
+      <c r="B4610" t="inlineStr">
+        <is>
+          <t>8605062104578</t>
+        </is>
+      </c>
+      <c r="C4610" t="inlineStr">
+        <is>
+          <t>GEOMETRIC EGGS 6/1</t>
+        </is>
+      </c>
+      <c r="D4610" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4611">
+      <c r="A4611" t="n">
+        <v>4610</v>
+      </c>
+      <c r="B4611" t="inlineStr">
+        <is>
+          <t>9002859126307</t>
+        </is>
+      </c>
+      <c r="C4611" t="inlineStr">
+        <is>
+          <t>EUR COKOLADA U MREZICI 85G</t>
+        </is>
+      </c>
+      <c r="D4611" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4612">
+      <c r="A4612" t="n">
+        <v>4611</v>
+      </c>
+      <c r="B4612" t="inlineStr">
+        <is>
+          <t>8691707162416</t>
+        </is>
+      </c>
+      <c r="C4612" t="inlineStr">
+        <is>
+          <t>PAPITA KOKOS 33G</t>
+        </is>
+      </c>
+      <c r="D4612" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4613">
+      <c r="A4613" t="n">
+        <v>4612</v>
+      </c>
+      <c r="B4613" t="inlineStr">
+        <is>
+          <t>8691707162409</t>
+        </is>
+      </c>
+      <c r="C4613" t="inlineStr">
+        <is>
+          <t>PAPITA MLIJEKO 33G</t>
+        </is>
+      </c>
+      <c r="D4613" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4614">
+      <c r="A4614" t="n">
+        <v>4613</v>
+      </c>
+      <c r="B4614" t="inlineStr">
+        <is>
+          <t>3870048000488</t>
+        </is>
+      </c>
+      <c r="C4614" t="inlineStr">
+        <is>
+          <t>HEDAL VR. ZA SM. 120L CRNA 70X110</t>
+        </is>
+      </c>
+      <c r="D4614" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="4615">
+      <c r="A4615" t="n">
+        <v>4614</v>
+      </c>
+      <c r="B4615" t="inlineStr">
+        <is>
+          <t>8601900002600</t>
+        </is>
+      </c>
+      <c r="C4615" t="inlineStr">
+        <is>
+          <t>TAKOVO SOK PARADAJZ 100% 1L</t>
+        </is>
+      </c>
+      <c r="D4615" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="4616">
+      <c r="A4616" t="n">
+        <v>4615</v>
+      </c>
+      <c r="B4616" t="inlineStr">
+        <is>
+          <t>3870048000754</t>
+        </is>
+      </c>
+      <c r="C4616" t="inlineStr">
+        <is>
+          <t>HEDAL VR. ZA SM. 150L 80X110 OJAC.</t>
+        </is>
+      </c>
+      <c r="D4616" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4617">
+      <c r="A4617" t="n">
+        <v>4616</v>
+      </c>
+      <c r="B4617" t="inlineStr">
+        <is>
+          <t>8681554633108</t>
+        </is>
+      </c>
+      <c r="C4617" t="inlineStr">
+        <is>
+          <t>FAIRY VL.MAR. ZA CIS. POWER 100/1</t>
+        </is>
+      </c>
+      <c r="D4617" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4618">
+      <c r="A4618" t="n">
+        <v>4617</v>
+      </c>
+      <c r="B4618" t="inlineStr">
+        <is>
+          <t>8699009465099</t>
+        </is>
+      </c>
+      <c r="C4618" t="inlineStr">
+        <is>
+          <t>LADYS SECRET SET MIDNIGHT BLOOM</t>
+        </is>
+      </c>
+      <c r="D4618" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="4619">
+      <c r="A4619" t="n">
+        <v>4618</v>
+      </c>
+      <c r="B4619" t="inlineStr">
+        <is>
+          <t>4005900009371</t>
+        </is>
+      </c>
+      <c r="C4619" t="inlineStr">
+        <is>
+          <t>NIVEA SOFT 300ML</t>
+        </is>
+      </c>
+      <c r="D4619" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="4620">
+      <c r="A4620" t="n">
+        <v>4619</v>
+      </c>
+      <c r="B4620" t="inlineStr">
+        <is>
+          <t>8008650290507</t>
+        </is>
+      </c>
+      <c r="C4620" t="inlineStr">
+        <is>
+          <t>DOPLA CASA BIJELA 200 ML 50/1</t>
+        </is>
+      </c>
+      <c r="D4620" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4621">
+      <c r="A4621" t="n">
+        <v>4620</v>
+      </c>
+      <c r="B4621" t="inlineStr">
+        <is>
+          <t>3890000285043</t>
+        </is>
+      </c>
+      <c r="C4621" t="inlineStr">
+        <is>
+          <t>WELLBOT PISTACI 80G</t>
+        </is>
+      </c>
+      <c r="D4621" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4622">
+      <c r="A4622" t="n">
+        <v>4621</v>
+      </c>
+      <c r="B4622" t="inlineStr">
+        <is>
+          <t>8413178402750</t>
+        </is>
+      </c>
+      <c r="C4622" t="inlineStr">
+        <is>
+          <t>VIDAL BOMBONA COLA 90G</t>
+        </is>
+      </c>
+      <c r="D4622" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4623">
+      <c r="A4623" t="n">
+        <v>4622</v>
+      </c>
+      <c r="B4623" t="inlineStr">
+        <is>
+          <t>8413178391481</t>
+        </is>
+      </c>
+      <c r="C4623" t="inlineStr">
+        <is>
+          <t>VUDAL BOMBONE JEDNOROG 90G</t>
+        </is>
+      </c>
+      <c r="D4623" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4624">
+      <c r="A4624" t="n">
+        <v>4623</v>
+      </c>
+      <c r="B4624" t="inlineStr">
+        <is>
+          <t>8003180031323</t>
+        </is>
+      </c>
+      <c r="C4624" t="inlineStr">
+        <is>
+          <t>ORASI BILJNI NAMAZ 25%MM POSNI</t>
+        </is>
+      </c>
+      <c r="D4624" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4625">
+      <c r="A4625" t="n">
+        <v>4624</v>
+      </c>
+      <c r="B4625" t="inlineStr">
+        <is>
+          <t>3850104051012</t>
+        </is>
+      </c>
+      <c r="C4625" t="inlineStr">
+        <is>
+          <t>PODRAVKA AJVAR BLAGI 690G</t>
+        </is>
+      </c>
+      <c r="D4625" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4626">
+      <c r="A4626" t="n">
+        <v>4625</v>
+      </c>
+      <c r="B4626" t="inlineStr">
+        <is>
+          <t>3850104023019</t>
+        </is>
+      </c>
+      <c r="C4626" t="inlineStr">
+        <is>
+          <t>PODRAVKA SENF ESTRAGON TUBA 100G</t>
+        </is>
+      </c>
+      <c r="D4626" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4627">
+      <c r="A4627" t="n">
+        <v>4626</v>
+      </c>
+      <c r="B4627" t="inlineStr">
+        <is>
+          <t>8456295463211</t>
+        </is>
+      </c>
+      <c r="C4627" t="inlineStr">
+        <is>
+          <t>LUBENICA SA ZVAKAMA 40G</t>
+        </is>
+      </c>
+      <c r="D4627" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4628">
+      <c r="A4628" t="n">
+        <v>4627</v>
+      </c>
+      <c r="B4628" t="inlineStr">
+        <is>
+          <t>8456295463228</t>
+        </is>
+      </c>
+      <c r="C4628" t="inlineStr">
+        <is>
+          <t>LUBENICA SA ZVAKAMA 40G</t>
+        </is>
+      </c>
+      <c r="D4628" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4629">
+      <c r="A4629" t="n">
+        <v>4628</v>
+      </c>
+      <c r="B4629" t="inlineStr">
+        <is>
+          <t>5010612808517</t>
+        </is>
+      </c>
+      <c r="C4629" t="inlineStr">
+        <is>
+          <t>BRUT DEO ORIGINAL 200ML</t>
+        </is>
+      </c>
+      <c r="D4629" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="4630">
+      <c r="A4630" t="n">
+        <v>4629</v>
+      </c>
+      <c r="B4630" t="inlineStr">
+        <is>
+          <t>6999985875830</t>
+        </is>
+      </c>
+      <c r="C4630" t="inlineStr">
+        <is>
+          <t>LIZALICA ANIMAL SORT 15G</t>
+        </is>
+      </c>
+      <c r="D4630" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4631">
+      <c r="A4631" t="n">
+        <v>4630</v>
+      </c>
+      <c r="B4631" t="inlineStr">
+        <is>
+          <t>3875000050679</t>
+        </is>
+      </c>
+      <c r="C4631" t="inlineStr">
+        <is>
+          <t>VESELA FARMA 140G</t>
+        </is>
+      </c>
+      <c r="D4631" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="4632">
+      <c r="A4632" t="n">
+        <v>4631</v>
+      </c>
+      <c r="B4632" t="inlineStr">
+        <is>
+          <t>7896321012838</t>
+        </is>
+      </c>
+      <c r="C4632" t="inlineStr">
+        <is>
+          <t>FLORESTAL LOVE POP 200G</t>
+        </is>
+      </c>
+      <c r="D4632" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4633">
+      <c r="A4633" t="n">
+        <v>4632</v>
+      </c>
+      <c r="B4633" t="inlineStr">
+        <is>
+          <t>8699009465082</t>
+        </is>
+      </c>
+      <c r="C4633" t="inlineStr">
+        <is>
+          <t>LADYS SECRET SET VANILLA</t>
+        </is>
+      </c>
+      <c r="D4633" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="4634">
+      <c r="A4634" t="n">
+        <v>4633</v>
+      </c>
+      <c r="B4634" t="inlineStr">
+        <is>
+          <t>3875000183056</t>
+        </is>
+      </c>
+      <c r="C4634" t="inlineStr">
+        <is>
+          <t>SARAJEVSKI KISELJAK 1.5L</t>
+        </is>
+      </c>
+      <c r="D4634" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="4635">
+      <c r="A4635" t="n">
+        <v>4634</v>
+      </c>
+      <c r="B4635" t="inlineStr">
+        <is>
+          <t>3838945501392</t>
+        </is>
+      </c>
+      <c r="C4635" t="inlineStr">
+        <is>
+          <t>FRUC LIMUNADA 0,5L</t>
+        </is>
+      </c>
+      <c r="D4635" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="4636">
+      <c r="A4636" t="n">
+        <v>4635</v>
+      </c>
+      <c r="B4636" t="inlineStr">
+        <is>
+          <t>8600939313329</t>
+        </is>
+      </c>
+      <c r="C4636" t="inlineStr">
+        <is>
+          <t>NAJLJEPSE ZELJE MLIJECNA 250G</t>
+        </is>
+      </c>
+      <c r="D4636" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="4637">
+      <c r="A4637" t="n">
+        <v>4636</v>
+      </c>
+      <c r="B4637" t="inlineStr">
+        <is>
+          <t>90087200136768</t>
+        </is>
+      </c>
+      <c r="C4637" t="inlineStr">
+        <is>
+          <t>BRAVO BRESKVA 0.5L</t>
+        </is>
+      </c>
+      <c r="D4637" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4638">
+      <c r="A4638" t="n">
+        <v>4637</v>
+      </c>
+      <c r="B4638" t="inlineStr">
+        <is>
+          <t>3871832009373</t>
+        </is>
+      </c>
+      <c r="C4638" t="inlineStr">
+        <is>
+          <t>JAMI JUFKA ZA BAKLAVU 450G</t>
+        </is>
+      </c>
+      <c r="D4638" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4639">
+      <c r="A4639" t="n">
+        <v>4638</v>
+      </c>
+      <c r="B4639" t="inlineStr">
+        <is>
+          <t>3877002209536</t>
+        </is>
+      </c>
+      <c r="C4639" t="inlineStr">
+        <is>
+          <t>CLASSY VRECE ZA ZAM. 3KG</t>
+        </is>
+      </c>
+      <c r="D4639" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4640">
+      <c r="A4640" t="n">
+        <v>4639</v>
+      </c>
+      <c r="B4640" t="inlineStr">
+        <is>
+          <t>3877002209543</t>
+        </is>
+      </c>
+      <c r="C4640" t="inlineStr">
+        <is>
+          <t>CLASSY VRECE ZA ZAM. 4KG</t>
+        </is>
+      </c>
+      <c r="D4640" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4641">
+      <c r="A4641" t="n">
+        <v>4640</v>
+      </c>
+      <c r="B4641" t="inlineStr">
+        <is>
+          <t>8004350003744</t>
+        </is>
+      </c>
+      <c r="C4641" t="inlineStr">
+        <is>
+          <t>COKO SMOKI 40G</t>
+        </is>
+      </c>
+      <c r="D4641" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4642">
+      <c r="A4642" t="n">
+        <v>4641</v>
+      </c>
+      <c r="B4642" t="inlineStr">
+        <is>
+          <t>3800205875109</t>
+        </is>
+      </c>
+      <c r="C4642" t="inlineStr">
+        <is>
+          <t>MARETTI PARADAJZ I MASLINE 70G</t>
+        </is>
+      </c>
+      <c r="D4642" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4643">
+      <c r="A4643" t="n">
+        <v>4642</v>
+      </c>
+      <c r="B4643" t="inlineStr">
+        <is>
+          <t>3872944000470</t>
+        </is>
+      </c>
+      <c r="C4643" t="inlineStr">
+        <is>
+          <t>DOMACE SOK 100% OD MRKVE 0,72L</t>
+        </is>
+      </c>
+      <c r="D4643" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4644">
+      <c r="A4644" t="n">
+        <v>4643</v>
+      </c>
+      <c r="B4644" t="inlineStr">
+        <is>
+          <t>3872944000487</t>
+        </is>
+      </c>
+      <c r="C4644" t="inlineStr">
+        <is>
+          <t>DOMACE SOK 100% OD CVEKLE 0,72L</t>
+        </is>
+      </c>
+      <c r="D4644" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4645">
+      <c r="A4645" t="n">
+        <v>4644</v>
+      </c>
+      <c r="B4645" t="inlineStr">
+        <is>
+          <t>3872944000494</t>
+        </is>
+      </c>
+      <c r="C4645" t="inlineStr">
+        <is>
+          <t>DOMACE SOK 100% VITAMIN MIX 0,72L</t>
+        </is>
+      </c>
+      <c r="D4645" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4646">
+      <c r="A4646" t="n">
+        <v>4645</v>
+      </c>
+      <c r="B4646" t="inlineStr">
+        <is>
+          <t>8004350005502</t>
+        </is>
+      </c>
+      <c r="C4646" t="inlineStr">
+        <is>
+          <t>PASTA ZARA FIDELINI TAGLIATI 400G</t>
+        </is>
+      </c>
+      <c r="D4646" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4647">
+      <c r="A4647" t="n">
+        <v>4646</v>
+      </c>
+      <c r="B4647" t="inlineStr">
+        <is>
+          <t>5310001208820</t>
+        </is>
+      </c>
+      <c r="C4647" t="inlineStr">
+        <is>
+          <t>BECUTAN KREMA VITAMINSKA 50ML</t>
+        </is>
+      </c>
+      <c r="D4647" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4648">
+      <c r="A4648" t="n">
+        <v>4647</v>
+      </c>
+      <c r="B4648" t="inlineStr">
+        <is>
+          <t>5310001139803</t>
+        </is>
+      </c>
+      <c r="C4648" t="inlineStr">
+        <is>
+          <t>BECUTAN DJECJI SAMPON 200ML</t>
+        </is>
+      </c>
+      <c r="D4648" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="4649">
+      <c r="A4649" t="n">
+        <v>4648</v>
+      </c>
+      <c r="B4649" t="inlineStr">
+        <is>
+          <t>5310001139780</t>
+        </is>
+      </c>
+      <c r="C4649" t="inlineStr">
+        <is>
+          <t>BECUTAN DJECIJA KUPKA 200ML</t>
+        </is>
+      </c>
+      <c r="D4649" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="4650">
+      <c r="A4650" t="n">
+        <v>4649</v>
+      </c>
+      <c r="B4650" t="inlineStr">
+        <is>
+          <t>5310001139735</t>
+        </is>
+      </c>
+      <c r="C4650" t="inlineStr">
+        <is>
+          <t>BECUTAN DJECIJE MLI. ZA TIJ. 200ML</t>
+        </is>
+      </c>
+      <c r="D4650" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="4651">
+      <c r="A4651" t="n">
+        <v>4650</v>
+      </c>
+      <c r="B4651" t="inlineStr">
+        <is>
+          <t>5310001247201</t>
+        </is>
+      </c>
+      <c r="C4651" t="inlineStr">
+        <is>
+          <t>BECUTAN PELENE 3 MIDI 4-9KG 56/1</t>
+        </is>
+      </c>
+      <c r="D4651" t="n">
+        <v>15.73</v>
+      </c>
+    </row>
+    <row r="4652">
+      <c r="A4652" t="n">
+        <v>4651</v>
+      </c>
+      <c r="B4652" t="inlineStr">
+        <is>
+          <t>5999109563279</t>
+        </is>
+      </c>
+      <c r="C4652" t="inlineStr">
+        <is>
+          <t>VANISH GEL PINK 500ML</t>
+        </is>
+      </c>
+      <c r="D4652" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="4653">
+      <c r="A4653" t="n">
+        <v>4652</v>
+      </c>
+      <c r="B4653" t="inlineStr">
+        <is>
+          <t>5999109563309</t>
+        </is>
+      </c>
+      <c r="C4653" t="inlineStr">
+        <is>
+          <t>VANISH EL WHITE 500ML</t>
+        </is>
+      </c>
+      <c r="D4653" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="4654">
+      <c r="A4654" t="n">
+        <v>4653</v>
+      </c>
+      <c r="B4654" t="inlineStr">
+        <is>
+          <t>7638900083590</t>
+        </is>
+      </c>
+      <c r="C4654" t="inlineStr">
+        <is>
+          <t>EVEREADY SUPER HEAVY DUTY AA 1KOM</t>
+        </is>
+      </c>
+      <c r="D4654" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4655">
+      <c r="A4655" t="n">
+        <v>4654</v>
+      </c>
+      <c r="B4655" t="inlineStr">
+        <is>
+          <t>5310079004447</t>
+        </is>
+      </c>
+      <c r="C4655" t="inlineStr">
+        <is>
+          <t>DOLCE VITA MALINA 65ML</t>
+        </is>
+      </c>
+      <c r="D4655" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4656">
+      <c r="A4656" t="n">
+        <v>4655</v>
+      </c>
+      <c r="B4656" t="inlineStr">
+        <is>
+          <t>5310079002559</t>
+        </is>
+      </c>
+      <c r="C4656" t="inlineStr">
+        <is>
+          <t>METROPOLI BERLIN 85ML</t>
+        </is>
+      </c>
+      <c r="D4656" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4657">
+      <c r="A4657" t="n">
+        <v>4656</v>
+      </c>
+      <c r="B4657" t="inlineStr">
+        <is>
+          <t>5310079002573</t>
+        </is>
+      </c>
+      <c r="C4657" t="inlineStr">
+        <is>
+          <t>METROPOLI LONDON 85ML</t>
+        </is>
+      </c>
+      <c r="D4657" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4658">
+      <c r="A4658" t="n">
+        <v>4657</v>
+      </c>
+      <c r="B4658" t="inlineStr">
+        <is>
+          <t>5310079002008</t>
+        </is>
+      </c>
+      <c r="C4658" t="inlineStr">
+        <is>
+          <t>GELATO VOCNI MIX VANILIJA 900ML</t>
+        </is>
+      </c>
+      <c r="D4658" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4659">
+      <c r="A4659" t="n">
+        <v>4658</v>
+      </c>
+      <c r="B4659" t="inlineStr">
+        <is>
+          <t>8711327590816</t>
+        </is>
+      </c>
+      <c r="C4659" t="inlineStr">
+        <is>
+          <t>BIG MILK TRIO POP 90ML</t>
+        </is>
+      </c>
+      <c r="D4659" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4660">
+      <c r="A4660" t="n">
+        <v>4659</v>
+      </c>
+      <c r="B4660" t="inlineStr">
+        <is>
+          <t>8711327671584</t>
+        </is>
+      </c>
+      <c r="C4660" t="inlineStr">
+        <is>
+          <t>SMILE EXOTIC MANGO 100ML</t>
+        </is>
+      </c>
+      <c r="D4660" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4661">
+      <c r="A4661" t="n">
+        <v>4660</v>
+      </c>
+      <c r="B4661" t="inlineStr">
+        <is>
+          <t>5000159460866</t>
+        </is>
+      </c>
+      <c r="C4661" t="inlineStr">
+        <is>
+          <t>MARS XTRA BAR 74ML</t>
+        </is>
+      </c>
+      <c r="D4661" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4662">
+      <c r="A4662" t="n">
+        <v>4661</v>
+      </c>
+      <c r="B4662" t="inlineStr">
+        <is>
+          <t>5000159460880</t>
+        </is>
+      </c>
+      <c r="C4662" t="inlineStr">
+        <is>
+          <t>SNICKERS XTRA BAR 73ML</t>
+        </is>
+      </c>
+      <c r="D4662" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4663">
+      <c r="A4663" t="n">
+        <v>4662</v>
+      </c>
+      <c r="B4663" t="inlineStr">
+        <is>
+          <t>5310079002306</t>
+        </is>
+      </c>
+      <c r="C4663" t="inlineStr">
+        <is>
+          <t>CERMAT SANDWICH 110ML</t>
+        </is>
+      </c>
+      <c r="D4663" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4664">
+      <c r="A4664" t="n">
+        <v>4663</v>
+      </c>
+      <c r="B4664" t="inlineStr">
+        <is>
+          <t>8606019841959</t>
+        </is>
+      </c>
+      <c r="C4664" t="inlineStr">
+        <is>
+          <t>CHIPS WAY CHIPS PAPRIKA 90G</t>
+        </is>
+      </c>
+      <c r="D4664" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4665">
+      <c r="A4665" t="n">
+        <v>4664</v>
+      </c>
+      <c r="B4665" t="inlineStr">
+        <is>
+          <t>8606019841577</t>
+        </is>
+      </c>
+      <c r="C4665" t="inlineStr">
+        <is>
+          <t>CHIPS WAY CHIPS PAPRIKA 150G</t>
+        </is>
+      </c>
+      <c r="D4665" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4666">
+      <c r="A4666" t="n">
+        <v>4665</v>
+      </c>
+      <c r="B4666" t="inlineStr">
+        <is>
+          <t>8600043041149</t>
+        </is>
+      </c>
+      <c r="C4666" t="inlineStr">
+        <is>
+          <t>ZLATNI PEK KAKAO KEKS 250G</t>
+        </is>
+      </c>
+      <c r="D4666" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4667">
+      <c r="A4667" t="n">
+        <v>4666</v>
+      </c>
+      <c r="B4667" t="inlineStr">
+        <is>
+          <t>7622201392192</t>
+        </is>
+      </c>
+      <c r="C4667" t="inlineStr">
+        <is>
+          <t>7D CROISSANT PEANUTS MAX 80G</t>
+        </is>
+      </c>
+      <c r="D4667" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4668">
+      <c r="A4668" t="n">
+        <v>4667</v>
+      </c>
+      <c r="B4668" t="inlineStr">
+        <is>
+          <t>8600037005492</t>
+        </is>
+      </c>
+      <c r="C4668" t="inlineStr">
+        <is>
+          <t>AQUA VIVA 1,5L</t>
+        </is>
+      </c>
+      <c r="D4668" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="4669">
+      <c r="A4669" t="n">
+        <v>4668</v>
+      </c>
+      <c r="B4669" t="inlineStr">
+        <is>
+          <t>8606106433708</t>
+        </is>
+      </c>
+      <c r="C4669" t="inlineStr">
+        <is>
+          <t>SLAVSKA KESA</t>
+        </is>
+      </c>
+      <c r="D4669" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4670">
+      <c r="A4670" t="n">
+        <v>4669</v>
+      </c>
+      <c r="B4670" t="inlineStr">
+        <is>
+          <t>8606012141957</t>
+        </is>
+      </c>
+      <c r="C4670" t="inlineStr">
+        <is>
+          <t>DEFT DETER. ZA SUDJE LIMUN 1L</t>
+        </is>
+      </c>
+      <c r="D4670" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4671">
+      <c r="A4671" t="n">
+        <v>4670</v>
+      </c>
+      <c r="B4671" t="inlineStr">
+        <is>
+          <t>3870343003733</t>
+        </is>
+      </c>
+      <c r="C4671" t="inlineStr">
+        <is>
+          <t>DEA VRECE ZA SMECE 70L</t>
+        </is>
+      </c>
+      <c r="D4671" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4672">
+      <c r="A4672" t="n">
+        <v>4671</v>
+      </c>
+      <c r="B4672" t="inlineStr">
+        <is>
+          <t>8606012142978</t>
+        </is>
+      </c>
+      <c r="C4672" t="inlineStr">
+        <is>
+          <t>DEFT DETER. ZA SUDJE JABUKA 500ML</t>
+        </is>
+      </c>
+      <c r="D4672" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4673">
+      <c r="A4673" t="n">
+        <v>4672</v>
+      </c>
+      <c r="B4673" t="inlineStr">
+        <is>
+          <t>8606012142558</t>
+        </is>
+      </c>
+      <c r="C4673" t="inlineStr">
+        <is>
+          <t>LMX SAPUN 75GR BLUE OCEAN</t>
+        </is>
+      </c>
+      <c r="D4673" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4674">
+      <c r="A4674" t="n">
+        <v>4673</v>
+      </c>
+      <c r="B4674" t="inlineStr">
+        <is>
+          <t>8606012142572</t>
+        </is>
+      </c>
+      <c r="C4674" t="inlineStr">
+        <is>
+          <t>LMX SAPUN 75GR HONEY&amp;MILK</t>
+        </is>
+      </c>
+      <c r="D4674" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4675">
+      <c r="A4675" t="n">
+        <v>4674</v>
+      </c>
+      <c r="B4675" t="inlineStr">
+        <is>
+          <t>3875000170742</t>
+        </is>
+      </c>
+      <c r="C4675" t="inlineStr">
+        <is>
+          <t>HAHNE ZOBENE PAHULJICE 450G</t>
+        </is>
+      </c>
+      <c r="D4675" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="4676">
+      <c r="A4676" t="n">
+        <v>4675</v>
+      </c>
+      <c r="B4676" t="inlineStr">
+        <is>
+          <t>3871862003389</t>
+        </is>
+      </c>
+      <c r="C4676" t="inlineStr">
+        <is>
+          <t>TREND TUNA U PARADAJZ SOSU 2X150G</t>
+        </is>
+      </c>
+      <c r="D4676" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4677">
+      <c r="A4677" t="n">
+        <v>4676</v>
+      </c>
+      <c r="B4677" t="inlineStr">
+        <is>
+          <t>3871862002184</t>
+        </is>
+      </c>
+      <c r="C4677" t="inlineStr">
+        <is>
+          <t>TREND KOMPOT OD BRESKVE 850ML</t>
+        </is>
+      </c>
+      <c r="D4677" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="4678">
+      <c r="A4678" t="n">
+        <v>4677</v>
+      </c>
+      <c r="B4678" t="inlineStr">
+        <is>
+          <t>3872252000049</t>
+        </is>
+      </c>
+      <c r="C4678" t="inlineStr">
+        <is>
+          <t>VODA LEDA 0.25L</t>
+        </is>
+      </c>
+      <c r="D4678" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4679">
+      <c r="A4679" t="n">
+        <v>4678</v>
+      </c>
+      <c r="B4679" t="inlineStr">
+        <is>
+          <t>8606106300109</t>
+        </is>
+      </c>
+      <c r="C4679" t="inlineStr">
+        <is>
+          <t>ZITO. STRUDLA SMOKVA 252G</t>
+        </is>
+      </c>
+      <c r="D4679" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4680">
+      <c r="A4680" t="n">
+        <v>4679</v>
+      </c>
+      <c r="B4680" t="inlineStr">
+        <is>
+          <t>9001378800941</t>
+        </is>
+      </c>
+      <c r="C4680" t="inlineStr">
+        <is>
+          <t>SPONTEX PLASTICNA MUHOLOVKA</t>
+        </is>
+      </c>
+      <c r="D4680" t="n">
         <v>1</v>
       </c>
     </row>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4680"/>
+  <dimension ref="A1:D4691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="103">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="156">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="157">
@@ -25941,7 +25941,7 @@
         </is>
       </c>
       <c r="D1418" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="1419">
@@ -31337,11 +31337,11 @@
       </c>
       <c r="C1718" t="inlineStr">
         <is>
-          <t>VOCNE KAPI JABUKA 2 L</t>
+          <t>VOCNE KAPI JABUKA 2L</t>
         </is>
       </c>
       <c r="D1718" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="1719">
@@ -32309,11 +32309,11 @@
       </c>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>BALANS JOGURT +0,9%MM 500 G</t>
+          <t>BALANS JOGURT +0,9%MM 500G</t>
         </is>
       </c>
       <c r="D1772" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="1773">
@@ -32403,7 +32403,7 @@
         </is>
       </c>
       <c r="D1777" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="1778">
@@ -32475,7 +32475,7 @@
         </is>
       </c>
       <c r="D1781" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="1782">
@@ -44283,7 +44283,7 @@
         </is>
       </c>
       <c r="D2437" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="2438">
@@ -44315,11 +44315,11 @@
       </c>
       <c r="C2439" t="inlineStr">
         <is>
-          <t>NEKTAR VOCNI MIX 1l</t>
+          <t>NEKTAR VOCNI MIX 1L</t>
         </is>
       </c>
       <c r="D2439" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="2440">
@@ -48675,7 +48675,7 @@
         </is>
       </c>
       <c r="D2681" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2682">
@@ -55551,7 +55551,7 @@
         </is>
       </c>
       <c r="D3063" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3064">
@@ -56865,7 +56865,7 @@
         </is>
       </c>
       <c r="D3136" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3137">
@@ -61019,11 +61019,11 @@
       </c>
       <c r="C3367" t="inlineStr">
         <is>
-          <t>JOGOOD VOC.JOG. SUMSKO VOCE 2.8%MM 330G</t>
+          <t>JOGOOD VOC.JOG. SUM.V. 2.8%MM 330G</t>
         </is>
       </c>
       <c r="D3367" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="3368">
@@ -84658,6 +84658,204 @@
       </c>
       <c r="D4680" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4681">
+      <c r="A4681" t="n">
+        <v>4680</v>
+      </c>
+      <c r="B4681" t="inlineStr">
+        <is>
+          <t>8606018726035</t>
+        </is>
+      </c>
+      <c r="C4681" t="inlineStr">
+        <is>
+          <t>NEKTAR MALINADA 1.5L</t>
+        </is>
+      </c>
+      <c r="D4681" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4682">
+      <c r="A4682" t="n">
+        <v>4681</v>
+      </c>
+      <c r="B4682" t="inlineStr">
+        <is>
+          <t>5310089006288</t>
+        </is>
+      </c>
+      <c r="C4682" t="inlineStr">
+        <is>
+          <t>CUNGA LUNGA MEGA JAGODA 15G</t>
+        </is>
+      </c>
+      <c r="D4682" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4683">
+      <c r="A4683" t="n">
+        <v>4682</v>
+      </c>
+      <c r="B4683" t="inlineStr">
+        <is>
+          <t>3877000105434</t>
+        </is>
+      </c>
+      <c r="C4683" t="inlineStr">
+        <is>
+          <t>BOJANIC DOMACI REZANI HLJEB 500G</t>
+        </is>
+      </c>
+      <c r="D4683" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4684">
+      <c r="A4684" t="n">
+        <v>4683</v>
+      </c>
+      <c r="B4684" t="inlineStr">
+        <is>
+          <t>3877000105144</t>
+        </is>
+      </c>
+      <c r="C4684" t="inlineStr">
+        <is>
+          <t>BOJANIC INTEGR. REZANI HLJEB 500G</t>
+        </is>
+      </c>
+      <c r="D4684" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4685">
+      <c r="A4685" t="n">
+        <v>4684</v>
+      </c>
+      <c r="B4685" t="inlineStr">
+        <is>
+          <t>3877000105533</t>
+        </is>
+      </c>
+      <c r="C4685" t="inlineStr">
+        <is>
+          <t>BOJANIC HLJEB INT. SA SJEM. 400G</t>
+        </is>
+      </c>
+      <c r="D4685" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4686">
+      <c r="A4686" t="n">
+        <v>4685</v>
+      </c>
+      <c r="B4686" t="inlineStr">
+        <is>
+          <t>3877000105335</t>
+        </is>
+      </c>
+      <c r="C4686" t="inlineStr">
+        <is>
+          <t>BOJANIC HLJEB KUKURUZNI 400G</t>
+        </is>
+      </c>
+      <c r="D4686" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4687">
+      <c r="A4687" t="n">
+        <v>4686</v>
+      </c>
+      <c r="B4687" t="inlineStr">
+        <is>
+          <t>8680836352133</t>
+        </is>
+      </c>
+      <c r="C4687" t="inlineStr">
+        <is>
+          <t>NOVA BOON BOMBONE</t>
+        </is>
+      </c>
+      <c r="D4687" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4688">
+      <c r="A4688" t="n">
+        <v>4687</v>
+      </c>
+      <c r="B4688" t="inlineStr">
+        <is>
+          <t>3877000105540</t>
+        </is>
+      </c>
+      <c r="C4688" t="inlineStr">
+        <is>
+          <t>BOJANIC STARA PEKA 600G</t>
+        </is>
+      </c>
+      <c r="D4688" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4689">
+      <c r="A4689" t="n">
+        <v>4688</v>
+      </c>
+      <c r="B4689" t="inlineStr">
+        <is>
+          <t>3877000105106</t>
+        </is>
+      </c>
+      <c r="C4689" t="inlineStr">
+        <is>
+          <t>BOJANIC KRSNI HLJEB 1200G</t>
+        </is>
+      </c>
+      <c r="D4689" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4690">
+      <c r="A4690" t="n">
+        <v>4689</v>
+      </c>
+      <c r="B4690" t="inlineStr">
+        <is>
+          <t>3877000105090</t>
+        </is>
+      </c>
+      <c r="C4690" t="inlineStr">
+        <is>
+          <t>BOJANIC BIJELO PECIVO 80G</t>
+        </is>
+      </c>
+      <c r="D4690" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4691">
+      <c r="A4691" t="n">
+        <v>4690</v>
+      </c>
+      <c r="B4691" t="inlineStr">
+        <is>
+          <t>3875000031487</t>
+        </is>
+      </c>
+      <c r="C4691" t="inlineStr">
+        <is>
+          <t>EXOTIC KRUSKA 0.33L</t>
+        </is>
+      </c>
+      <c r="D4691" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4691"/>
+  <dimension ref="A1:D4740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="143">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="296">
@@ -6119,11 +6119,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>NIVEA DEZODORANS</t>
+          <t>NIVEA DEZODORANS FRESH PURE 150ML</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="318">
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="461">
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="508">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="520">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="528">
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="D668" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="669">
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="D776" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="777">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="D883" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="884">
@@ -21869,11 +21869,11 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>HIGIJENSKE RUKAVICE</t>
+          <t>HIGIJENSKE RUKAVICE 100/1</t>
         </is>
       </c>
       <c r="D1192" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1193">
@@ -24213,7 +24213,7 @@
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="1323">
@@ -24231,7 +24231,7 @@
         </is>
       </c>
       <c r="D1323" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="1324">
@@ -25995,7 +25995,7 @@
         </is>
       </c>
       <c r="D1421" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="1422">
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="D1482" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1483">
@@ -28155,7 +28155,7 @@
         </is>
       </c>
       <c r="D1541" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="1542">
@@ -28875,7 +28875,7 @@
         </is>
       </c>
       <c r="D1581" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1582">
@@ -29109,7 +29109,7 @@
         </is>
       </c>
       <c r="D1594" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="1595">
@@ -32529,7 +32529,7 @@
         </is>
       </c>
       <c r="D1784" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1785">
@@ -35945,11 +35945,11 @@
       </c>
       <c r="C1974" t="inlineStr">
         <is>
-          <t>OVAL 15 L</t>
+          <t>OVAL 15L</t>
         </is>
       </c>
       <c r="D1974" t="n">
-        <v>10.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1975">
@@ -35963,11 +35963,11 @@
       </c>
       <c r="C1975" t="inlineStr">
         <is>
-          <t>OVAL 25 L</t>
+          <t>OVAL 25L</t>
         </is>
       </c>
       <c r="D1975" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="1976">
@@ -40611,7 +40611,7 @@
         </is>
       </c>
       <c r="D2233" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="2234">
@@ -41259,7 +41259,7 @@
         </is>
       </c>
       <c r="D2269" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="2270">
@@ -41763,7 +41763,7 @@
         </is>
       </c>
       <c r="D2297" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2298">
@@ -43113,7 +43113,7 @@
         </is>
       </c>
       <c r="D2372" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="2373">
@@ -43451,11 +43451,11 @@
       </c>
       <c r="C2391" t="inlineStr">
         <is>
-          <t>VINCINNI NAPOLITANKA 160GR</t>
+          <t>VINCINNI NAPOLITANKA KAKAO 160G</t>
         </is>
       </c>
       <c r="D2391" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="2392">
@@ -47145,7 +47145,7 @@
         </is>
       </c>
       <c r="D2596" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="2597">
@@ -47631,7 +47631,7 @@
         </is>
       </c>
       <c r="D2623" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="2624">
@@ -52077,7 +52077,7 @@
         </is>
       </c>
       <c r="D2870" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="2871">
@@ -55425,7 +55425,7 @@
         </is>
       </c>
       <c r="D3056" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3057">
@@ -57657,7 +57657,7 @@
         </is>
       </c>
       <c r="D3180" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3181">
@@ -58845,7 +58845,7 @@
         </is>
       </c>
       <c r="D3246" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3247">
@@ -65469,7 +65469,7 @@
         </is>
       </c>
       <c r="D3614" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3615">
@@ -67989,7 +67989,7 @@
         </is>
       </c>
       <c r="D3754" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="3755">
@@ -68439,7 +68439,7 @@
         </is>
       </c>
       <c r="D3779" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3780">
@@ -73983,7 +73983,7 @@
         </is>
       </c>
       <c r="D4087" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4088">
@@ -78609,7 +78609,7 @@
         </is>
       </c>
       <c r="D4344" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4345">
@@ -79563,7 +79563,7 @@
         </is>
       </c>
       <c r="D4397" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4398">
@@ -80571,7 +80571,7 @@
         </is>
       </c>
       <c r="D4453" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4454">
@@ -84779,7 +84779,7 @@
       </c>
       <c r="C4687" t="inlineStr">
         <is>
-          <t>NOVA BOON BOMBONE</t>
+          <t>NOVA BOON BOMBONE 18G</t>
         </is>
       </c>
       <c r="D4687" t="n">
@@ -84856,6 +84856,888 @@
       </c>
       <c r="D4691" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="4692">
+      <c r="A4692" t="n">
+        <v>4691</v>
+      </c>
+      <c r="B4692" t="inlineStr">
+        <is>
+          <t>5907180884893</t>
+        </is>
+      </c>
+      <c r="C4692" t="inlineStr">
+        <is>
+          <t>T&amp;T FILTER 200</t>
+        </is>
+      </c>
+      <c r="D4692" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4693">
+      <c r="A4693" t="n">
+        <v>4692</v>
+      </c>
+      <c r="B4693" t="inlineStr">
+        <is>
+          <t>3875000975897</t>
+        </is>
+      </c>
+      <c r="C4693" t="inlineStr">
+        <is>
+          <t>UBRUS LILY U500 3SLOJA</t>
+        </is>
+      </c>
+      <c r="D4693" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4694">
+      <c r="A4694" t="n">
+        <v>4693</v>
+      </c>
+      <c r="B4694" t="inlineStr">
+        <is>
+          <t>8610056008299</t>
+        </is>
+      </c>
+      <c r="C4694" t="inlineStr">
+        <is>
+          <t>VIOLLA STAPICI ZA USI 200/1</t>
+        </is>
+      </c>
+      <c r="D4694" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4695">
+      <c r="A4695" t="n">
+        <v>4694</v>
+      </c>
+      <c r="B4695" t="inlineStr">
+        <is>
+          <t>6903618900004</t>
+        </is>
+      </c>
+      <c r="C4695" t="inlineStr">
+        <is>
+          <t>STAKLENA VAZA 20CM</t>
+        </is>
+      </c>
+      <c r="D4695" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="4696">
+      <c r="A4696" t="n">
+        <v>4695</v>
+      </c>
+      <c r="B4696" t="inlineStr">
+        <is>
+          <t>6903031400006</t>
+        </is>
+      </c>
+      <c r="C4696" t="inlineStr">
+        <is>
+          <t>STAKLENA VAZA 20CM</t>
+        </is>
+      </c>
+      <c r="D4696" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="4697">
+      <c r="A4697" t="n">
+        <v>4696</v>
+      </c>
+      <c r="B4697" t="inlineStr">
+        <is>
+          <t>8681480314775</t>
+        </is>
+      </c>
+      <c r="C4697" t="inlineStr">
+        <is>
+          <t>FENOMEN LIZALO POLONYA</t>
+        </is>
+      </c>
+      <c r="D4697" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4698">
+      <c r="A4698" t="n">
+        <v>4697</v>
+      </c>
+      <c r="B4698" t="inlineStr">
+        <is>
+          <t>5999883273616</t>
+        </is>
+      </c>
+      <c r="C4698" t="inlineStr">
+        <is>
+          <t>FINESI SALAMA ZA PSE 800G GOVED.</t>
+        </is>
+      </c>
+      <c r="D4698" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4699">
+      <c r="A4699" t="n">
+        <v>4698</v>
+      </c>
+      <c r="B4699" t="inlineStr">
+        <is>
+          <t>3875000976399</t>
+        </is>
+      </c>
+      <c r="C4699" t="inlineStr">
+        <is>
+          <t>VL.MAR. BELLA HOME LAVANDER 100/1</t>
+        </is>
+      </c>
+      <c r="D4699" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="4700">
+      <c r="A4700" t="n">
+        <v>4699</v>
+      </c>
+      <c r="B4700" t="inlineStr">
+        <is>
+          <t>3875000976405</t>
+        </is>
+      </c>
+      <c r="C4700" t="inlineStr">
+        <is>
+          <t>VL.MAR. BELLA HOME LIMUN 100/1</t>
+        </is>
+      </c>
+      <c r="D4700" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4701">
+      <c r="A4701" t="n">
+        <v>4700</v>
+      </c>
+      <c r="B4701" t="inlineStr">
+        <is>
+          <t>3875000973855</t>
+        </is>
+      </c>
+      <c r="C4701" t="inlineStr">
+        <is>
+          <t>BELLA DESTILOVANA VODA 1.5L</t>
+        </is>
+      </c>
+      <c r="D4701" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="4702">
+      <c r="A4702" t="n">
+        <v>4701</v>
+      </c>
+      <c r="B4702" t="inlineStr">
+        <is>
+          <t>8610056000705</t>
+        </is>
+      </c>
+      <c r="C4702" t="inlineStr">
+        <is>
+          <t>PLASTICNE SLAMKE 50/1</t>
+        </is>
+      </c>
+      <c r="D4702" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4703">
+      <c r="A4703" t="n">
+        <v>4702</v>
+      </c>
+      <c r="B4703" t="inlineStr">
+        <is>
+          <t>8606003590535</t>
+        </is>
+      </c>
+      <c r="C4703" t="inlineStr">
+        <is>
+          <t>PECALJKA ZA MUHE DRINA 46CM</t>
+        </is>
+      </c>
+      <c r="D4703" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4704">
+      <c r="A4704" t="n">
+        <v>4703</v>
+      </c>
+      <c r="B4704" t="inlineStr">
+        <is>
+          <t>5948351010246</t>
+        </is>
+      </c>
+      <c r="C4704" t="inlineStr">
+        <is>
+          <t>POK.VREC. CRNO-CRVENA</t>
+        </is>
+      </c>
+      <c r="D4704" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4705">
+      <c r="A4705" t="n">
+        <v>4704</v>
+      </c>
+      <c r="B4705" t="inlineStr">
+        <is>
+          <t>5948351009400</t>
+        </is>
+      </c>
+      <c r="C4705" t="inlineStr">
+        <is>
+          <t>POK.VREC. PICE POSLOVNA</t>
+        </is>
+      </c>
+      <c r="D4705" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4706">
+      <c r="A4706" t="n">
+        <v>4705</v>
+      </c>
+      <c r="B4706" t="inlineStr">
+        <is>
+          <t>5948351010239</t>
+        </is>
+      </c>
+      <c r="C4706" t="inlineStr">
+        <is>
+          <t>POK.VREC. NARANDZASTA</t>
+        </is>
+      </c>
+      <c r="D4706" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4707">
+      <c r="A4707" t="n">
+        <v>4706</v>
+      </c>
+      <c r="B4707" t="inlineStr">
+        <is>
+          <t>5948351000216</t>
+        </is>
+      </c>
+      <c r="C4707" t="inlineStr">
+        <is>
+          <t>POK.VREC. MIX CVIJECE</t>
+        </is>
+      </c>
+      <c r="D4707" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4708">
+      <c r="A4708" t="n">
+        <v>4707</v>
+      </c>
+      <c r="B4708" t="inlineStr">
+        <is>
+          <t>5948351010215</t>
+        </is>
+      </c>
+      <c r="C4708" t="inlineStr">
+        <is>
+          <t>POK.VREC. LEPTIR</t>
+        </is>
+      </c>
+      <c r="D4708" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4709">
+      <c r="A4709" t="n">
+        <v>4708</v>
+      </c>
+      <c r="B4709" t="inlineStr">
+        <is>
+          <t>5948351009417</t>
+        </is>
+      </c>
+      <c r="C4709" t="inlineStr">
+        <is>
+          <t>POK.VREC. CRVENO SRCE</t>
+        </is>
+      </c>
+      <c r="D4709" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4710">
+      <c r="A4710" t="n">
+        <v>4709</v>
+      </c>
+      <c r="B4710" t="inlineStr">
+        <is>
+          <t>5948351013506</t>
+        </is>
+      </c>
+      <c r="C4710" t="inlineStr">
+        <is>
+          <t>POK.VREC. MASNA</t>
+        </is>
+      </c>
+      <c r="D4710" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4711">
+      <c r="A4711" t="n">
+        <v>4710</v>
+      </c>
+      <c r="B4711" t="inlineStr">
+        <is>
+          <t>5948351013094</t>
+        </is>
+      </c>
+      <c r="C4711" t="inlineStr">
+        <is>
+          <t>CESTITKA PRSTEN</t>
+        </is>
+      </c>
+      <c r="D4711" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4712">
+      <c r="A4712" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B4712" t="inlineStr">
+        <is>
+          <t>5948351013100</t>
+        </is>
+      </c>
+      <c r="C4712" t="inlineStr">
+        <is>
+          <t>CESTITKA SRCE</t>
+        </is>
+      </c>
+      <c r="D4712" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4713">
+      <c r="A4713" t="n">
+        <v>4712</v>
+      </c>
+      <c r="B4713" t="inlineStr">
+        <is>
+          <t>5310115009375</t>
+        </is>
+      </c>
+      <c r="C4713" t="inlineStr">
+        <is>
+          <t>VINCINNI NAPOLITANKA LJES. 160G</t>
+        </is>
+      </c>
+      <c r="D4713" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4714">
+      <c r="A4714" t="n">
+        <v>4713</v>
+      </c>
+      <c r="B4714" t="inlineStr">
+        <is>
+          <t>5310345012077</t>
+        </is>
+      </c>
+      <c r="C4714" t="inlineStr">
+        <is>
+          <t>VINCINNI NAPOLITANKA LJES. 300G</t>
+        </is>
+      </c>
+      <c r="D4714" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4715">
+      <c r="A4715" t="n">
+        <v>4714</v>
+      </c>
+      <c r="B4715" t="inlineStr">
+        <is>
+          <t>5310345012053</t>
+        </is>
+      </c>
+      <c r="C4715" t="inlineStr">
+        <is>
+          <t>VINCINNI NAPOLITANKA KAKAO 300G</t>
+        </is>
+      </c>
+      <c r="D4715" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4716">
+      <c r="A4716" t="n">
+        <v>4715</v>
+      </c>
+      <c r="B4716" t="inlineStr">
+        <is>
+          <t>8700216803670</t>
+        </is>
+      </c>
+      <c r="C4716" t="inlineStr">
+        <is>
+          <t>ARIEL COLOR CAPS 10/1</t>
+        </is>
+      </c>
+      <c r="D4716" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="4717">
+      <c r="A4717" t="n">
+        <v>4716</v>
+      </c>
+      <c r="B4717" t="inlineStr">
+        <is>
+          <t>8006530126588</t>
+        </is>
+      </c>
+      <c r="C4717" t="inlineStr">
+        <is>
+          <t>FAIRY TABLETE PLATINUM 15/1</t>
+        </is>
+      </c>
+      <c r="D4717" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="4718">
+      <c r="A4718" t="n">
+        <v>4717</v>
+      </c>
+      <c r="B4718" t="inlineStr">
+        <is>
+          <t>7702018622054</t>
+        </is>
+      </c>
+      <c r="C4718" t="inlineStr">
+        <is>
+          <t>GILLETTE 200ML SENSITIVE</t>
+        </is>
+      </c>
+      <c r="D4718" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="4719">
+      <c r="A4719" t="n">
+        <v>4718</v>
+      </c>
+      <c r="B4719" t="inlineStr">
+        <is>
+          <t>8006530159111</t>
+        </is>
+      </c>
+      <c r="C4719" t="inlineStr">
+        <is>
+          <t>GILLETTE 250ML LIMUN</t>
+        </is>
+      </c>
+      <c r="D4719" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="4720">
+      <c r="A4720" t="n">
+        <v>4719</v>
+      </c>
+      <c r="B4720" t="inlineStr">
+        <is>
+          <t>5310089000019</t>
+        </is>
+      </c>
+      <c r="C4720" t="inlineStr">
+        <is>
+          <t>CUNGA LUNGA</t>
+        </is>
+      </c>
+      <c r="D4720" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4721">
+      <c r="A4721" t="n">
+        <v>4720</v>
+      </c>
+      <c r="B4721" t="inlineStr">
+        <is>
+          <t>4026700370355</t>
+        </is>
+      </c>
+      <c r="C4721" t="inlineStr">
+        <is>
+          <t>UHU JUMBO SUPER LJEPILO 12X2</t>
+        </is>
+      </c>
+      <c r="D4721" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="4722">
+      <c r="A4722" t="n">
+        <v>4721</v>
+      </c>
+      <c r="B4722" t="inlineStr">
+        <is>
+          <t>8720181114441</t>
+        </is>
+      </c>
+      <c r="C4722" t="inlineStr">
+        <is>
+          <t>AXE DEO 150ML AFRICA</t>
+        </is>
+      </c>
+      <c r="D4722" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="4723">
+      <c r="A4723" t="n">
+        <v>4722</v>
+      </c>
+      <c r="B4723" t="inlineStr">
+        <is>
+          <t>8720181114472</t>
+        </is>
+      </c>
+      <c r="C4723" t="inlineStr">
+        <is>
+          <t>AXE DEO 150ML APOLLO</t>
+        </is>
+      </c>
+      <c r="D4723" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4724">
+      <c r="A4724" t="n">
+        <v>4723</v>
+      </c>
+      <c r="B4724" t="inlineStr">
+        <is>
+          <t>8720181295546</t>
+        </is>
+      </c>
+      <c r="C4724" t="inlineStr">
+        <is>
+          <t>DOVE DEO MEN 150ML CLASSIC</t>
+        </is>
+      </c>
+      <c r="D4724" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4725">
+      <c r="A4725" t="n">
+        <v>4724</v>
+      </c>
+      <c r="B4725" t="inlineStr">
+        <is>
+          <t>8720181340581</t>
+        </is>
+      </c>
+      <c r="C4725" t="inlineStr">
+        <is>
+          <t>DOVE DEO 150ML CLEAN COMFORT</t>
+        </is>
+      </c>
+      <c r="D4725" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4726">
+      <c r="A4726" t="n">
+        <v>4725</v>
+      </c>
+      <c r="B4726" t="inlineStr">
+        <is>
+          <t>8720181291715</t>
+        </is>
+      </c>
+      <c r="C4726" t="inlineStr">
+        <is>
+          <t>DOVE DEO 150ML ORIGINAL</t>
+        </is>
+      </c>
+      <c r="D4726" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4727">
+      <c r="A4727" t="n">
+        <v>4726</v>
+      </c>
+      <c r="B4727" t="inlineStr">
+        <is>
+          <t>5413149798864</t>
+        </is>
+      </c>
+      <c r="C4727" t="inlineStr">
+        <is>
+          <t>FAIRY LEMON 650ML</t>
+        </is>
+      </c>
+      <c r="D4727" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="4728">
+      <c r="A4728" t="n">
+        <v>4727</v>
+      </c>
+      <c r="B4728" t="inlineStr">
+        <is>
+          <t>4084500410534</t>
+        </is>
+      </c>
+      <c r="C4728" t="inlineStr">
+        <is>
+          <t>FAIRY TABLETE ORIGINAL 36/1</t>
+        </is>
+      </c>
+      <c r="D4728" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4729">
+      <c r="A4729" t="n">
+        <v>4728</v>
+      </c>
+      <c r="B4729" t="inlineStr">
+        <is>
+          <t>4005900486646</t>
+        </is>
+      </c>
+      <c r="C4729" t="inlineStr">
+        <is>
+          <t>NIVEA DEZODORANS DRY FRESH 150ML</t>
+        </is>
+      </c>
+      <c r="D4729" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="4730">
+      <c r="A4730" t="n">
+        <v>4729</v>
+      </c>
+      <c r="B4730" t="inlineStr">
+        <is>
+          <t>4005808801039</t>
+        </is>
+      </c>
+      <c r="C4730" t="inlineStr">
+        <is>
+          <t>NIVEA KREMA 75ML</t>
+        </is>
+      </c>
+      <c r="D4730" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="4731">
+      <c r="A4731" t="n">
+        <v>4730</v>
+      </c>
+      <c r="B4731" t="inlineStr">
+        <is>
+          <t>9005800356112</t>
+        </is>
+      </c>
+      <c r="C4731" t="inlineStr">
+        <is>
+          <t>NIVEA DEO PEA&amp;BEA BLACK 150ML</t>
+        </is>
+      </c>
+      <c r="D4731" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="4732">
+      <c r="A4732" t="n">
+        <v>4731</v>
+      </c>
+      <c r="B4732" t="inlineStr">
+        <is>
+          <t>6191370900060</t>
+        </is>
+      </c>
+      <c r="C4732" t="inlineStr">
+        <is>
+          <t>SOLIVERA EKS.DJEV. MASL. ULJE 0.5L</t>
+        </is>
+      </c>
+      <c r="D4732" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="4733">
+      <c r="A4733" t="n">
+        <v>4732</v>
+      </c>
+      <c r="B4733" t="inlineStr">
+        <is>
+          <t>6191370900046</t>
+        </is>
+      </c>
+      <c r="C4733" t="inlineStr">
+        <is>
+          <t>SOLIVERA EKS.DJEV. MASL. ULJE 1L</t>
+        </is>
+      </c>
+      <c r="D4733" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="4734">
+      <c r="A4734" t="n">
+        <v>4733</v>
+      </c>
+      <c r="B4734" t="inlineStr">
+        <is>
+          <t>8606107718637</t>
+        </is>
+      </c>
+      <c r="C4734" t="inlineStr">
+        <is>
+          <t>CHIPS CLASSIC 150G CHIPSY WAY</t>
+        </is>
+      </c>
+      <c r="D4734" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4735">
+      <c r="A4735" t="n">
+        <v>4734</v>
+      </c>
+      <c r="B4735" t="inlineStr">
+        <is>
+          <t>3850102111961</t>
+        </is>
+      </c>
+      <c r="C4735" t="inlineStr">
+        <is>
+          <t>DORINA MLIJECNA 80G</t>
+        </is>
+      </c>
+      <c r="D4735" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4736">
+      <c r="A4736" t="n">
+        <v>4735</v>
+      </c>
+      <c r="B4736" t="inlineStr">
+        <is>
+          <t>3850102117970</t>
+        </is>
+      </c>
+      <c r="C4736" t="inlineStr">
+        <is>
+          <t>DORINA KEKS 80G</t>
+        </is>
+      </c>
+      <c r="D4736" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4737">
+      <c r="A4737" t="n">
+        <v>4736</v>
+      </c>
+      <c r="B4737" t="inlineStr">
+        <is>
+          <t>8601500141389</t>
+        </is>
+      </c>
+      <c r="C4737" t="inlineStr">
+        <is>
+          <t>COK. ML. MK CHILL 1%MM CASA 230ML</t>
+        </is>
+      </c>
+      <c r="D4737" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="4738">
+      <c r="A4738" t="n">
+        <v>4737</v>
+      </c>
+      <c r="B4738" t="inlineStr">
+        <is>
+          <t>3850116108957</t>
+        </is>
+      </c>
+      <c r="C4738" t="inlineStr">
+        <is>
+          <t>KORNET STRACC.&amp;SUMSKO VOCE 73G</t>
+        </is>
+      </c>
+      <c r="D4738" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4739">
+      <c r="A4739" t="n">
+        <v>4738</v>
+      </c>
+      <c r="B4739" t="inlineStr">
+        <is>
+          <t>3850116782409</t>
+        </is>
+      </c>
+      <c r="C4739" t="inlineStr">
+        <is>
+          <t>LEDO FRESCO POMFRIT 1KG</t>
+        </is>
+      </c>
+      <c r="D4739" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4740">
+      <c r="A4740" t="n">
+        <v>4739</v>
+      </c>
+      <c r="B4740" t="inlineStr">
+        <is>
+          <t>3877000105076</t>
+        </is>
+      </c>
+      <c r="C4740" t="inlineStr">
+        <is>
+          <t>BOJANIC RUZA MALA</t>
+        </is>
+      </c>
+      <c r="D4740" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4740"/>
+  <dimension ref="A1:D4788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="103">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>8.130000000000001</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="298">
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="410">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="463">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="518">
@@ -9741,7 +9741,7 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="519">
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="D613" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="614">
@@ -11573,11 +11573,11 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>FINI JELLY BERRIES 100 G</t>
+          <t>FINI JELLY BERRIES 90G</t>
         </is>
       </c>
       <c r="D620" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="621">
@@ -11753,11 +11753,11 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>FINI GUMENE BOMBONE JAGODA KRUG 100 G</t>
+          <t>FINI JAGODA KRUG 90G</t>
         </is>
       </c>
       <c r="D630" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="631">
@@ -11843,11 +11843,11 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>FINI GUMENE BOMBONE JAGODA POLJUBAC 100 G</t>
+          <t>FINI JAGODA POLJUBAC 90G</t>
         </is>
       </c>
       <c r="D635" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="636">
@@ -12189,7 +12189,7 @@
         </is>
       </c>
       <c r="D654" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="655">
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="D730" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="731">
@@ -14061,7 +14061,7 @@
         </is>
       </c>
       <c r="D758" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="759">
@@ -16041,7 +16041,7 @@
         </is>
       </c>
       <c r="D868" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="869">
@@ -17139,7 +17139,7 @@
         </is>
       </c>
       <c r="D929" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="930">
@@ -23727,7 +23727,7 @@
         </is>
       </c>
       <c r="D1295" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="1296">
@@ -24285,7 +24285,7 @@
         </is>
       </c>
       <c r="D1326" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="1327">
@@ -25527,7 +25527,7 @@
         </is>
       </c>
       <c r="D1395" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="1396">
@@ -25545,7 +25545,7 @@
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="1397">
@@ -25599,7 +25599,7 @@
         </is>
       </c>
       <c r="D1399" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="1400">
@@ -25959,7 +25959,7 @@
         </is>
       </c>
       <c r="D1419" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="1420">
@@ -26949,7 +26949,7 @@
         </is>
       </c>
       <c r="D1474" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="1475">
@@ -29073,7 +29073,7 @@
         </is>
       </c>
       <c r="D1592" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="1593">
@@ -32205,7 +32205,7 @@
         </is>
       </c>
       <c r="D1766" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1767">
@@ -32259,7 +32259,7 @@
         </is>
       </c>
       <c r="D1769" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="1770">
@@ -32745,7 +32745,7 @@
         </is>
       </c>
       <c r="D1796" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="1797">
@@ -33321,7 +33321,7 @@
         </is>
       </c>
       <c r="D1828" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="1829">
@@ -33897,7 +33897,7 @@
         </is>
       </c>
       <c r="D1860" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1861">
@@ -34275,7 +34275,7 @@
         </is>
       </c>
       <c r="D1881" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="1882">
@@ -34779,7 +34779,7 @@
         </is>
       </c>
       <c r="D1909" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="1910">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="C2000" t="inlineStr">
         <is>
-          <t>BONZITA KAJSIJA</t>
+          <t>BONZITA KAJSIJA 25G</t>
         </is>
       </c>
       <c r="D2000" t="n">
@@ -36935,11 +36935,11 @@
       </c>
       <c r="C2029" t="inlineStr">
         <is>
-          <t>FINI MELLOWS</t>
+          <t>FINI MELLOWS 80G</t>
         </is>
       </c>
       <c r="D2029" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2030">
@@ -36971,11 +36971,11 @@
       </c>
       <c r="C2031" t="inlineStr">
         <is>
-          <t>FINI NEON BEARS</t>
+          <t>FINI NEON BEARS 90G</t>
         </is>
       </c>
       <c r="D2031" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2032">
@@ -37605,7 +37605,7 @@
         </is>
       </c>
       <c r="D2066" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="2067">
@@ -44441,11 +44441,11 @@
       </c>
       <c r="C2446" t="inlineStr">
         <is>
-          <t>FINI MAGIC CARPETS</t>
+          <t>FINI MAGIC CARPETS 90G</t>
         </is>
       </c>
       <c r="D2446" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2447">
@@ -44459,11 +44459,11 @@
       </c>
       <c r="C2447" t="inlineStr">
         <is>
-          <t>FINI JELLY BANANAS</t>
+          <t>FINI JELLY BANANAS 90G</t>
         </is>
       </c>
       <c r="D2447" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2448">
@@ -44477,11 +44477,11 @@
       </c>
       <c r="C2448" t="inlineStr">
         <is>
-          <t>FINI JELLY SHARKS</t>
+          <t>FINI JELLY SHARKS 90G</t>
         </is>
       </c>
       <c r="D2448" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2449">
@@ -44733,7 +44733,7 @@
         </is>
       </c>
       <c r="D2462" t="n">
-        <v>12.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="2463">
@@ -53801,7 +53801,7 @@
       </c>
       <c r="C2966" t="inlineStr">
         <is>
-          <t>CHUPA CHUPS MAGIC CUBES</t>
+          <t>CHUPA CHUPS MAGIC CUBES 86G</t>
         </is>
       </c>
       <c r="D2966" t="n">
@@ -53985,7 +53985,7 @@
         </is>
       </c>
       <c r="D2976" t="n">
-        <v>10.8</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="2977">
@@ -54003,7 +54003,7 @@
         </is>
       </c>
       <c r="D2977" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="2978">
@@ -56073,7 +56073,7 @@
         </is>
       </c>
       <c r="D3092" t="n">
-        <v>10.8</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="3093">
@@ -56127,7 +56127,7 @@
         </is>
       </c>
       <c r="D3095" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3096">
@@ -56145,7 +56145,7 @@
         </is>
       </c>
       <c r="D3096" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3097">
@@ -56663,7 +56663,7 @@
       </c>
       <c r="C3125" t="inlineStr">
         <is>
-          <t>FINI ROLLER 20G</t>
+          <t>FINI ROLLER FANTASIA 20G</t>
         </is>
       </c>
       <c r="D3125" t="n">
@@ -60645,7 +60645,7 @@
         </is>
       </c>
       <c r="D3346" t="n">
-        <v>12.5</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="3347">
@@ -67305,7 +67305,7 @@
         </is>
       </c>
       <c r="D3716" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="3717">
@@ -70905,7 +70905,7 @@
         </is>
       </c>
       <c r="D3916" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3917">
@@ -71967,7 +71967,7 @@
         </is>
       </c>
       <c r="D3975" t="n">
-        <v>10.8</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="3976">
@@ -76089,7 +76089,7 @@
         </is>
       </c>
       <c r="D4204" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4205">
@@ -81975,7 +81975,7 @@
         </is>
       </c>
       <c r="D4531" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="4532">
@@ -82457,7 +82457,7 @@
       </c>
       <c r="C4558" t="inlineStr">
         <is>
-          <t>GROAN COKOL. BAR SA JAG. 32G</t>
+          <t>GROAN COKOL. BAR SA JAG. 35G</t>
         </is>
       </c>
       <c r="D4558" t="n">
@@ -85738,6 +85738,870 @@
       </c>
       <c r="D4740" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4741">
+      <c r="A4741" t="n">
+        <v>4740</v>
+      </c>
+      <c r="B4741" t="inlineStr">
+        <is>
+          <t>8697462212397</t>
+        </is>
+      </c>
+      <c r="C4741" t="inlineStr">
+        <is>
+          <t>ANTAT SPECIAL SELECTION BOMB. 200G</t>
+        </is>
+      </c>
+      <c r="D4741" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="4742">
+      <c r="A4742" t="n">
+        <v>4741</v>
+      </c>
+      <c r="B4742" t="inlineStr">
+        <is>
+          <t>8682276682801</t>
+        </is>
+      </c>
+      <c r="C4742" t="inlineStr">
+        <is>
+          <t>ANTAT TROFY VOCNE PUNJ. BOMB. 400G</t>
+        </is>
+      </c>
+      <c r="D4742" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="4743">
+      <c r="A4743" t="n">
+        <v>4742</v>
+      </c>
+      <c r="B4743" t="inlineStr">
+        <is>
+          <t>8600012502640</t>
+        </is>
+      </c>
+      <c r="C4743" t="inlineStr">
+        <is>
+          <t>CA. SRPSKA KOBASICA 310G</t>
+        </is>
+      </c>
+      <c r="D4743" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="4744">
+      <c r="A4744" t="n">
+        <v>4743</v>
+      </c>
+      <c r="B4744" t="inlineStr">
+        <is>
+          <t>3870281014808</t>
+        </is>
+      </c>
+      <c r="C4744" t="inlineStr">
+        <is>
+          <t>BONITO KECAP BLAGI 460G</t>
+        </is>
+      </c>
+      <c r="D4744" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="4745">
+      <c r="A4745" t="n">
+        <v>4744</v>
+      </c>
+      <c r="B4745" t="inlineStr">
+        <is>
+          <t>3870281014846</t>
+        </is>
+      </c>
+      <c r="C4745" t="inlineStr">
+        <is>
+          <t>BONITO KECAP PIZZA 460G</t>
+        </is>
+      </c>
+      <c r="D4745" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="4746">
+      <c r="A4746" t="n">
+        <v>4745</v>
+      </c>
+      <c r="B4746" t="inlineStr">
+        <is>
+          <t>86061022870398</t>
+        </is>
+      </c>
+      <c r="C4746" t="inlineStr">
+        <is>
+          <t>PERFEX TOALET PAPIR 24/1 3SL</t>
+        </is>
+      </c>
+      <c r="D4746" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="4747">
+      <c r="A4747" t="n">
+        <v>4746</v>
+      </c>
+      <c r="B4747" t="inlineStr">
+        <is>
+          <t>8606102287435</t>
+        </is>
+      </c>
+      <c r="C4747" t="inlineStr">
+        <is>
+          <t>PERFEX TOALET PAPIR 24/1 3SL</t>
+        </is>
+      </c>
+      <c r="D4747" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="4748">
+      <c r="A4748" t="n">
+        <v>4747</v>
+      </c>
+      <c r="B4748" t="inlineStr">
+        <is>
+          <t>800649000427</t>
+        </is>
+      </c>
+      <c r="C4748" t="inlineStr">
+        <is>
+          <t>ZAJECARSKO 0,5L LIMENKA</t>
+        </is>
+      </c>
+      <c r="D4748" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4749">
+      <c r="A4749" t="n">
+        <v>4748</v>
+      </c>
+      <c r="B4749" t="inlineStr">
+        <is>
+          <t>8690997090522</t>
+        </is>
+      </c>
+      <c r="C4749" t="inlineStr">
+        <is>
+          <t>JEDNOROG LIZALO SA IGRACKOM 11G</t>
+        </is>
+      </c>
+      <c r="D4749" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4750">
+      <c r="A4750" t="n">
+        <v>4749</v>
+      </c>
+      <c r="B4750" t="inlineStr">
+        <is>
+          <t>8690997190529</t>
+        </is>
+      </c>
+      <c r="C4750" t="inlineStr">
+        <is>
+          <t>JEDNOROG LIZALO SA IGRACKOM 11G</t>
+        </is>
+      </c>
+      <c r="D4750" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4751">
+      <c r="A4751" t="n">
+        <v>4750</v>
+      </c>
+      <c r="B4751" t="inlineStr">
+        <is>
+          <t>8683749042405</t>
+        </is>
+      </c>
+      <c r="C4751" t="inlineStr">
+        <is>
+          <t>PINKI POP IGRACKA SA LIZALOM 33G</t>
+        </is>
+      </c>
+      <c r="D4751" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="4752">
+      <c r="A4752" t="n">
+        <v>4751</v>
+      </c>
+      <c r="B4752" t="inlineStr">
+        <is>
+          <t>88683749142402</t>
+        </is>
+      </c>
+      <c r="C4752" t="inlineStr">
+        <is>
+          <t>PINKI POP IGRACKA SA LIZALOM 33G</t>
+        </is>
+      </c>
+      <c r="D4752" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="4753">
+      <c r="A4753" t="n">
+        <v>4752</v>
+      </c>
+      <c r="B4753" t="inlineStr">
+        <is>
+          <t>8684707780377</t>
+        </is>
+      </c>
+      <c r="C4753" t="inlineStr">
+        <is>
+          <t>GROAN COKOL. BAR SA JAG. 35G</t>
+        </is>
+      </c>
+      <c r="D4753" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4754">
+      <c r="A4754" t="n">
+        <v>4753</v>
+      </c>
+      <c r="B4754" t="inlineStr">
+        <is>
+          <t>8680618405835</t>
+        </is>
+      </c>
+      <c r="C4754" t="inlineStr">
+        <is>
+          <t>GALAXY JAGODA 11G</t>
+        </is>
+      </c>
+      <c r="D4754" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4755">
+      <c r="A4755" t="n">
+        <v>4754</v>
+      </c>
+      <c r="B4755" t="inlineStr">
+        <is>
+          <t>8680618405927</t>
+        </is>
+      </c>
+      <c r="C4755" t="inlineStr">
+        <is>
+          <t>GALAXY JAGODA 11G</t>
+        </is>
+      </c>
+      <c r="D4755" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4756">
+      <c r="A4756" t="n">
+        <v>4755</v>
+      </c>
+      <c r="B4756" t="inlineStr">
+        <is>
+          <t>08690997290342</t>
+        </is>
+      </c>
+      <c r="C4756" t="inlineStr">
+        <is>
+          <t>MAGICNI KARAMEL PRSTICI 7G</t>
+        </is>
+      </c>
+      <c r="D4756" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4757">
+      <c r="A4757" t="n">
+        <v>4756</v>
+      </c>
+      <c r="B4757" t="inlineStr">
+        <is>
+          <t>8680618407938</t>
+        </is>
+      </c>
+      <c r="C4757" t="inlineStr">
+        <is>
+          <t>STARLINE LIZALO 15G</t>
+        </is>
+      </c>
+      <c r="D4757" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4758">
+      <c r="A4758" t="n">
+        <v>4757</v>
+      </c>
+      <c r="B4758" t="inlineStr">
+        <is>
+          <t>8606100820092</t>
+        </is>
+      </c>
+      <c r="C4758" t="inlineStr">
+        <is>
+          <t>FRESH PAP. MAR. EXTRA LAVANDA 10/1</t>
+        </is>
+      </c>
+      <c r="D4758" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4759">
+      <c r="A4759" t="n">
+        <v>4758</v>
+      </c>
+      <c r="B4759" t="inlineStr">
+        <is>
+          <t>8437011503060</t>
+        </is>
+      </c>
+      <c r="C4759" t="inlineStr">
+        <is>
+          <t>DELISUN TORTILJA 360G 6/1</t>
+        </is>
+      </c>
+      <c r="D4759" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4760">
+      <c r="A4760" t="n">
+        <v>4759</v>
+      </c>
+      <c r="B4760" t="inlineStr">
+        <is>
+          <t>8410031965056</t>
+        </is>
+      </c>
+      <c r="C4760" t="inlineStr">
+        <is>
+          <t>CHUPA CHUPS LIZALO MIX 108G</t>
+        </is>
+      </c>
+      <c r="D4760" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4761">
+      <c r="A4761" t="n">
+        <v>4760</v>
+      </c>
+      <c r="B4761" t="inlineStr">
+        <is>
+          <t>80757061</t>
+        </is>
+      </c>
+      <c r="C4761" t="inlineStr">
+        <is>
+          <t>BIG BABOL JAGODA 20/1</t>
+        </is>
+      </c>
+      <c r="D4761" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4762">
+      <c r="A4762" t="n">
+        <v>4761</v>
+      </c>
+      <c r="B4762" t="inlineStr">
+        <is>
+          <t>80929246</t>
+        </is>
+      </c>
+      <c r="C4762" t="inlineStr">
+        <is>
+          <t>CHUPA CHUPS MAGIC CUBES 86G</t>
+        </is>
+      </c>
+      <c r="D4762" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4763">
+      <c r="A4763" t="n">
+        <v>4762</v>
+      </c>
+      <c r="B4763" t="inlineStr">
+        <is>
+          <t>8410525247569</t>
+        </is>
+      </c>
+      <c r="C4763" t="inlineStr">
+        <is>
+          <t>FINI SOUR TROPICAL MIX 90G</t>
+        </is>
+      </c>
+      <c r="D4763" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4764">
+      <c r="A4764" t="n">
+        <v>4763</v>
+      </c>
+      <c r="B4764" t="inlineStr">
+        <is>
+          <t>5999571058129</t>
+        </is>
+      </c>
+      <c r="C4764" t="inlineStr">
+        <is>
+          <t>XIXO MOJITO LEMONADE 250ML</t>
+        </is>
+      </c>
+      <c r="D4764" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4765">
+      <c r="A4765" t="n">
+        <v>4764</v>
+      </c>
+      <c r="B4765" t="inlineStr">
+        <is>
+          <t>8690705064043</t>
+        </is>
+      </c>
+      <c r="C4765" t="inlineStr">
+        <is>
+          <t>SARAY MIX SOFT PUNJ. BOMB. 100G</t>
+        </is>
+      </c>
+      <c r="D4765" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="4766">
+      <c r="A4766" t="n">
+        <v>4765</v>
+      </c>
+      <c r="B4766" t="inlineStr">
+        <is>
+          <t>7622202376016</t>
+        </is>
+      </c>
+      <c r="C4766" t="inlineStr">
+        <is>
+          <t>7D MAX CROISSANT FOREST FRUIT 80G</t>
+        </is>
+      </c>
+      <c r="D4766" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4767">
+      <c r="A4767" t="n">
+        <v>4766</v>
+      </c>
+      <c r="B4767" t="inlineStr">
+        <is>
+          <t>8606027635212</t>
+        </is>
+      </c>
+      <c r="C4767" t="inlineStr">
+        <is>
+          <t>JACOBS CAPPUCCINO VANILLA 12GX10</t>
+        </is>
+      </c>
+      <c r="D4767" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4768">
+      <c r="A4768" t="n">
+        <v>4767</v>
+      </c>
+      <c r="B4768" t="inlineStr">
+        <is>
+          <t>8600043033472</t>
+        </is>
+      </c>
+      <c r="C4768" t="inlineStr">
+        <is>
+          <t>PLAZMA MINI COKO TUTI FRUTI 45G</t>
+        </is>
+      </c>
+      <c r="D4768" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4769">
+      <c r="A4769" t="n">
+        <v>4768</v>
+      </c>
+      <c r="B4769" t="inlineStr">
+        <is>
+          <t>8600046004240</t>
+        </is>
+      </c>
+      <c r="C4769" t="inlineStr">
+        <is>
+          <t>BONZITA BRUSNICA 25G</t>
+        </is>
+      </c>
+      <c r="D4769" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4770">
+      <c r="A4770" t="n">
+        <v>4769</v>
+      </c>
+      <c r="B4770" t="inlineStr">
+        <is>
+          <t>3850105190635</t>
+        </is>
+      </c>
+      <c r="C4770" t="inlineStr">
+        <is>
+          <t>FAKS AQUA 3,15KG</t>
+        </is>
+      </c>
+      <c r="D4770" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="4771">
+      <c r="A4771" t="n">
+        <v>4770</v>
+      </c>
+      <c r="B4771" t="inlineStr">
+        <is>
+          <t>3860105174925</t>
+        </is>
+      </c>
+      <c r="C4771" t="inlineStr">
+        <is>
+          <t>ARF WC 5 DROPS LEMON 3X55G</t>
+        </is>
+      </c>
+      <c r="D4771" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="4772">
+      <c r="A4772" t="n">
+        <v>4771</v>
+      </c>
+      <c r="B4772" t="inlineStr">
+        <is>
+          <t>5319990227317</t>
+        </is>
+      </c>
+      <c r="C4772" t="inlineStr">
+        <is>
+          <t>VITAGO VOCNI SOK 0,2L BRESKVA</t>
+        </is>
+      </c>
+      <c r="D4772" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4773">
+      <c r="A4773" t="n">
+        <v>4772</v>
+      </c>
+      <c r="B4773" t="inlineStr">
+        <is>
+          <t>5319990227300</t>
+        </is>
+      </c>
+      <c r="C4773" t="inlineStr">
+        <is>
+          <t>VITAGO VOCNI SOK 0,2L JABUKA</t>
+        </is>
+      </c>
+      <c r="D4773" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4774">
+      <c r="A4774" t="n">
+        <v>4773</v>
+      </c>
+      <c r="B4774" t="inlineStr">
+        <is>
+          <t>3871331003230</t>
+        </is>
+      </c>
+      <c r="C4774" t="inlineStr">
+        <is>
+          <t>HAPPY C. CASE 350CC 50/1</t>
+        </is>
+      </c>
+      <c r="D4774" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="4775">
+      <c r="A4775" t="n">
+        <v>4774</v>
+      </c>
+      <c r="B4775" t="inlineStr">
+        <is>
+          <t>3872292005417</t>
+        </is>
+      </c>
+      <c r="C4775" t="inlineStr">
+        <is>
+          <t>HELLENA TEC. SAPUN PL.CVIJECE 0.5L</t>
+        </is>
+      </c>
+      <c r="D4775" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="4776">
+      <c r="A4776" t="n">
+        <v>4775</v>
+      </c>
+      <c r="B4776" t="inlineStr">
+        <is>
+          <t>3872292016420</t>
+        </is>
+      </c>
+      <c r="C4776" t="inlineStr">
+        <is>
+          <t>HELLENA PRO. PERUTI CITRUS 300ML</t>
+        </is>
+      </c>
+      <c r="D4776" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="4777">
+      <c r="A4777" t="n">
+        <v>4776</v>
+      </c>
+      <c r="B4777" t="inlineStr">
+        <is>
+          <t>3872292016444</t>
+        </is>
+      </c>
+      <c r="C4777" t="inlineStr">
+        <is>
+          <t>HELLENA PRO. PERUTI CLASSIC 300ML</t>
+        </is>
+      </c>
+      <c r="D4777" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="4778">
+      <c r="A4778" t="n">
+        <v>4777</v>
+      </c>
+      <c r="B4778" t="inlineStr">
+        <is>
+          <t>3872292016000</t>
+        </is>
+      </c>
+      <c r="C4778" t="inlineStr">
+        <is>
+          <t>HELENA KR. ZA RUKE PANTHENOL 100ML</t>
+        </is>
+      </c>
+      <c r="D4778" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="4779">
+      <c r="A4779" t="n">
+        <v>4778</v>
+      </c>
+      <c r="B4779" t="inlineStr">
+        <is>
+          <t>3872292015966</t>
+        </is>
+      </c>
+      <c r="C4779" t="inlineStr">
+        <is>
+          <t>HELLENA KREMA GEL GLYCERIN 100ML</t>
+        </is>
+      </c>
+      <c r="D4779" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="4780">
+      <c r="A4780" t="n">
+        <v>4779</v>
+      </c>
+      <c r="B4780" t="inlineStr">
+        <is>
+          <t>3872292003727</t>
+        </is>
+      </c>
+      <c r="C4780" t="inlineStr">
+        <is>
+          <t>MAX CLEAN ABRAZIV LAVANDA 450ML</t>
+        </is>
+      </c>
+      <c r="D4780" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4781">
+      <c r="A4781" t="n">
+        <v>4780</v>
+      </c>
+      <c r="B4781" t="inlineStr">
+        <is>
+          <t>3872292016062</t>
+        </is>
+      </c>
+      <c r="C4781" t="inlineStr">
+        <is>
+          <t>MC WC GEL 0,75L</t>
+        </is>
+      </c>
+      <c r="D4781" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="4782">
+      <c r="A4782" t="n">
+        <v>4781</v>
+      </c>
+      <c r="B4782" t="inlineStr">
+        <is>
+          <t>3872292008401</t>
+        </is>
+      </c>
+      <c r="C4782" t="inlineStr">
+        <is>
+          <t>MC WC FRESH. QUATRO LAVANDER 50G</t>
+        </is>
+      </c>
+      <c r="D4782" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4783">
+      <c r="A4783" t="n">
+        <v>4782</v>
+      </c>
+      <c r="B4783" t="inlineStr">
+        <is>
+          <t>3872292008432</t>
+        </is>
+      </c>
+      <c r="C4783" t="inlineStr">
+        <is>
+          <t>MC WC FRESH. QUATRO LEMON 3X50G</t>
+        </is>
+      </c>
+      <c r="D4783" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="4784">
+      <c r="A4784" t="n">
+        <v>4783</v>
+      </c>
+      <c r="B4784" t="inlineStr">
+        <is>
+          <t>8606015849409</t>
+        </is>
+      </c>
+      <c r="C4784" t="inlineStr">
+        <is>
+          <t>DUEL PURPLE DREAM 1,6L</t>
+        </is>
+      </c>
+      <c r="D4784" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="4785">
+      <c r="A4785" t="n">
+        <v>4784</v>
+      </c>
+      <c r="B4785" t="inlineStr">
+        <is>
+          <t>8606035993670</t>
+        </is>
+      </c>
+      <c r="C4785" t="inlineStr">
+        <is>
+          <t>DEUL ADRIATIC SENSE 1,6L</t>
+        </is>
+      </c>
+      <c r="D4785" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4786">
+      <c r="A4786" t="n">
+        <v>4785</v>
+      </c>
+      <c r="B4786" t="inlineStr">
+        <is>
+          <t>8606035993793</t>
+        </is>
+      </c>
+      <c r="C4786" t="inlineStr">
+        <is>
+          <t>DUEL GOLDEN COASR 1,6L</t>
+        </is>
+      </c>
+      <c r="D4786" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4787">
+      <c r="A4787" t="n">
+        <v>4786</v>
+      </c>
+      <c r="B4787" t="inlineStr">
+        <is>
+          <t>8606035993762</t>
+        </is>
+      </c>
+      <c r="C4787" t="inlineStr">
+        <is>
+          <t>DUEL AURORA BOREALIS 1,6L</t>
+        </is>
+      </c>
+      <c r="D4787" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4788">
+      <c r="A4788" t="n">
+        <v>4787</v>
+      </c>
+      <c r="B4788" t="inlineStr">
+        <is>
+          <t>3850116053103</t>
+        </is>
+      </c>
+      <c r="C4788" t="inlineStr">
+        <is>
+          <t>BROKULA 400G 16/1</t>
+        </is>
+      </c>
+      <c r="D4788" t="n">
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4788"/>
+  <dimension ref="A1:D4867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -971,7 +971,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SARANSAK - BIJELI LUK  POVRCE</t>
+          <t>SARANSAK - BIJELI LUK POVRCE</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="37">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="103">
@@ -2573,11 +2573,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GERSLO</t>
+          <t>SETI GERSLO 800G</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="121">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="163">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="164">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="221">
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="283">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>KUKURUZ KOKICAR</t>
+          <t>SETI KUKURUZ KOKICAR 500G</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -6263,11 +6263,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>NIVEA DEZODORANS</t>
+          <t>NIVEA DEO PEA&amp;BEA 150ML</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="326">
@@ -6947,11 +6947,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>ELF BALZAM ZA KOSU</t>
+          <t>ELF BALZAM ZA KOSU 500ML</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="375">
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>GUD KIKIRIKI 80 G</t>
+          <t>GUD KIKIRIKI PRZENI SLANI 80G</t>
         </is>
       </c>
       <c r="D523" t="n">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="D761" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="762">
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="D809" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="810">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="D810" t="n">
-        <v>12.6</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="811">
@@ -16955,11 +16955,11 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>PUDING BONITO VANILIJA 40 G</t>
+          <t>PUDING BONITO VANILIJA 40G</t>
         </is>
       </c>
       <c r="D919" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="920">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="D1002" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1003">
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="D1099" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1100">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>RIDE TRAKE ZA MUVE 4/1</t>
+          <t>RAID TRAKE ZA MUVE 4/1</t>
         </is>
       </c>
       <c r="D1114" t="n">
@@ -21203,11 +21203,11 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>PALMOLIVE SAPUN</t>
+          <t>PALMOLIVE SAPUN GREEN TEA 90G</t>
         </is>
       </c>
       <c r="D1155" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1156">
@@ -21621,7 +21621,7 @@
         </is>
       </c>
       <c r="D1178" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="1179">
@@ -23259,7 +23259,7 @@
         </is>
       </c>
       <c r="D1269" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="1270">
@@ -24605,7 +24605,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>STOLJNJAK 140X200</t>
+          <t>STOLNJAK 140X200</t>
         </is>
       </c>
       <c r="D1344" t="n">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C1345" t="inlineStr">
         <is>
-          <t>STOLJNJAK 140X220</t>
+          <t>STOLNJAK 140X220</t>
         </is>
       </c>
       <c r="D1345" t="n">
@@ -24875,11 +24875,11 @@
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>STOLJNJAK 140X160</t>
+          <t>STOLNJAK 140X160</t>
         </is>
       </c>
       <c r="D1359" t="n">
-        <v>12</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="1360">
@@ -26459,7 +26459,7 @@
       </c>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>EURO VAFEL 180 G</t>
+          <t>EURO VAFEL 180G</t>
         </is>
       </c>
       <c r="D1447" t="n">
@@ -26585,7 +26585,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>RIZA SETI 800 G</t>
+          <t>SETI RIZA 800 G</t>
         </is>
       </c>
       <c r="D1454" t="n">
@@ -28155,7 +28155,7 @@
         </is>
       </c>
       <c r="D1541" t="n">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="1542">
@@ -28659,7 +28659,7 @@
         </is>
       </c>
       <c r="D1569" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1570">
@@ -29145,7 +29145,7 @@
         </is>
       </c>
       <c r="D1596" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="1597">
@@ -29199,7 +29199,7 @@
         </is>
       </c>
       <c r="D1599" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="1600">
@@ -29595,7 +29595,7 @@
         </is>
       </c>
       <c r="D1621" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="1622">
@@ -30243,7 +30243,7 @@
         </is>
       </c>
       <c r="D1657" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="1658">
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="D1658" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="1659">
@@ -30963,7 +30963,7 @@
         </is>
       </c>
       <c r="D1697" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1698">
@@ -31053,7 +31053,7 @@
         </is>
       </c>
       <c r="D1702" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1703">
@@ -31917,7 +31917,7 @@
         </is>
       </c>
       <c r="D1750" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1751">
@@ -32277,7 +32277,7 @@
         </is>
       </c>
       <c r="D1770" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="1771">
@@ -32511,7 +32511,7 @@
         </is>
       </c>
       <c r="D1783" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1784">
@@ -32547,7 +32547,7 @@
         </is>
       </c>
       <c r="D1785" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="1786">
@@ -32561,11 +32561,11 @@
       </c>
       <c r="C1786" t="inlineStr">
         <is>
-          <t>DR MILK KAJMAKO 250</t>
+          <t>DR MILK KAJMAKO 250G</t>
         </is>
       </c>
       <c r="D1786" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1787">
@@ -32979,7 +32979,7 @@
         </is>
       </c>
       <c r="D1809" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1810">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="C1828" t="inlineStr">
         <is>
-          <t>POLIMAR MAJONEZ DELIKATES 280 ML</t>
+          <t>POLIMARK MAJONEZ DELIKATES 280 ML</t>
         </is>
       </c>
       <c r="D1828" t="n">
@@ -33771,7 +33771,7 @@
         </is>
       </c>
       <c r="D1853" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1854">
@@ -34869,7 +34869,7 @@
         </is>
       </c>
       <c r="D1914" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1915">
@@ -35949,7 +35949,7 @@
         </is>
       </c>
       <c r="D1974" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="1975">
@@ -37421,7 +37421,7 @@
       </c>
       <c r="C2056" t="inlineStr">
         <is>
-          <t>MALA VEKNA  DUBRAVE</t>
+          <t>MALA VEKNA DUBRAVE</t>
         </is>
       </c>
       <c r="D2056" t="n">
@@ -37587,7 +37587,7 @@
         </is>
       </c>
       <c r="D2065" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="2066">
@@ -39441,7 +39441,7 @@
         </is>
       </c>
       <c r="D2168" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="2169">
@@ -39725,7 +39725,7 @@
       </c>
       <c r="C2184" t="inlineStr">
         <is>
-          <t>GUD KIKIRIKI CHILI 80G</t>
+          <t>GUD KIKIRIKI PRZENI CHILI 80G</t>
         </is>
       </c>
       <c r="D2184" t="n">
@@ -40859,7 +40859,7 @@
       </c>
       <c r="C2247" t="inlineStr">
         <is>
-          <t>SETI PAPRIKA</t>
+          <t>SETI PAPRIKA SLATKA CRVENA 100G</t>
         </is>
       </c>
       <c r="D2247" t="n">
@@ -43779,7 +43779,7 @@
         </is>
       </c>
       <c r="D2409" t="n">
-        <v>3.8</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="2410">
@@ -44045,11 +44045,11 @@
       </c>
       <c r="C2424" t="inlineStr">
         <is>
-          <t>FRESH ANTISMOKE</t>
+          <t>FRESH ANTISMOKE 250ML</t>
         </is>
       </c>
       <c r="D2424" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="2425">
@@ -44099,11 +44099,11 @@
       </c>
       <c r="C2427" t="inlineStr">
         <is>
-          <t>LADYS SECRET PARADISE 250ML</t>
+          <t>LADY'S SECRET PARADISE 250ML</t>
         </is>
       </c>
       <c r="D2427" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="2428">
@@ -44517,7 +44517,7 @@
         </is>
       </c>
       <c r="D2450" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="2451">
@@ -45669,7 +45669,7 @@
         </is>
       </c>
       <c r="D2514" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="2515">
@@ -46223,11 +46223,11 @@
       </c>
       <c r="C2545" t="inlineStr">
         <is>
-          <t>CAMELIA</t>
+          <t>CAMELIA SALVETE 100/1</t>
         </is>
       </c>
       <c r="D2545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2546">
@@ -49031,7 +49031,7 @@
       </c>
       <c r="C2701" t="inlineStr">
         <is>
-          <t>FINE DROPS</t>
+          <t>FINE DROPS VOCNI MIX 200G</t>
         </is>
       </c>
       <c r="D2701" t="n">
@@ -50160,7 +50160,7 @@
       </c>
       <c r="B2764" t="inlineStr">
         <is>
-          <t>7702018621279</t>
+          <t>8410031918700</t>
         </is>
       </c>
       <c r="C2764" t="inlineStr">
@@ -50178,7 +50178,7 @@
       </c>
       <c r="B2765" t="inlineStr">
         <is>
-          <t>77020018621293</t>
+          <t>7702018621279</t>
         </is>
       </c>
       <c r="C2765" t="inlineStr">
@@ -50583,7 +50583,7 @@
         </is>
       </c>
       <c r="D2787" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="2788">
@@ -50601,7 +50601,7 @@
         </is>
       </c>
       <c r="D2788" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="2789">
@@ -51375,7 +51375,7 @@
         </is>
       </c>
       <c r="D2831" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="2832">
@@ -51915,7 +51915,7 @@
         </is>
       </c>
       <c r="D2861" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="2862">
@@ -55083,7 +55083,7 @@
         </is>
       </c>
       <c r="D3037" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="3038">
@@ -55713,7 +55713,7 @@
         </is>
       </c>
       <c r="D3072" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3073">
@@ -55983,7 +55983,7 @@
         </is>
       </c>
       <c r="D3087" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3088">
@@ -56361,7 +56361,7 @@
         </is>
       </c>
       <c r="D3108" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3109">
@@ -57297,7 +57297,7 @@
         </is>
       </c>
       <c r="D3160" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3161">
@@ -57657,7 +57657,7 @@
         </is>
       </c>
       <c r="D3180" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3181">
@@ -57833,7 +57833,7 @@
       </c>
       <c r="C3190" t="inlineStr">
         <is>
-          <t>KASIKA EKSPRESO</t>
+          <t>KASIKA ESPRESSO</t>
         </is>
       </c>
       <c r="D3190" t="n">
@@ -58503,7 +58503,7 @@
         </is>
       </c>
       <c r="D3227" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="3228">
@@ -60177,7 +60177,7 @@
         </is>
       </c>
       <c r="D3320" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3321">
@@ -60659,7 +60659,7 @@
       </c>
       <c r="C3347" t="inlineStr">
         <is>
-          <t>CEDEVITA BOMBON NARANDZA 18G</t>
+          <t>CEDEVITA BOMBON NARANDZA 19.5G</t>
         </is>
       </c>
       <c r="D3347" t="n">
@@ -60965,7 +60965,7 @@
       </c>
       <c r="C3364" t="inlineStr">
         <is>
-          <t>YUMIS POPCORN  150G</t>
+          <t>YUMIS POPCORN 150G</t>
         </is>
       </c>
       <c r="D3364" t="n">
@@ -61779,7 +61779,7 @@
         </is>
       </c>
       <c r="D3409" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3410">
@@ -62499,7 +62499,7 @@
         </is>
       </c>
       <c r="D3449" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3450">
@@ -62769,7 +62769,7 @@
         </is>
       </c>
       <c r="D3464" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3465">
@@ -62868,12 +62868,12 @@
       </c>
       <c r="B3470" t="inlineStr">
         <is>
-          <t>8410031918700</t>
+          <t>7702018621293</t>
         </is>
       </c>
       <c r="C3470" t="inlineStr">
         <is>
-          <t>LIZALO  CLASSIC</t>
+          <t>LIZALO CLASSIC</t>
         </is>
       </c>
       <c r="D3470" t="n">
@@ -63237,7 +63237,7 @@
         </is>
       </c>
       <c r="D3490" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3491">
@@ -63273,7 +63273,7 @@
         </is>
       </c>
       <c r="D3492" t="n">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="3493">
@@ -63381,7 +63381,7 @@
         </is>
       </c>
       <c r="D3498" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3499">
@@ -64043,11 +64043,11 @@
       </c>
       <c r="C3535" t="inlineStr">
         <is>
-          <t>LADY`S SECRETR AFTER PARTY ANGEL</t>
+          <t>LADY'S SECRET AFTER PARTY ANGEL</t>
         </is>
       </c>
       <c r="D3535" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3536">
@@ -65280,7 +65280,7 @@
       </c>
       <c r="B3604" t="inlineStr">
         <is>
-          <t>3870187000202</t>
+          <t>3870187000200</t>
         </is>
       </c>
       <c r="C3604" t="inlineStr">
@@ -66603,7 +66603,7 @@
         </is>
       </c>
       <c r="D3677" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3678">
@@ -68133,7 +68133,7 @@
         </is>
       </c>
       <c r="D3762" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="3763">
@@ -68511,7 +68511,7 @@
         </is>
       </c>
       <c r="D3783" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3784">
@@ -69717,7 +69717,7 @@
         </is>
       </c>
       <c r="D3850" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3851">
@@ -70815,7 +70815,7 @@
         </is>
       </c>
       <c r="D3911" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3912">
@@ -71463,7 +71463,7 @@
         </is>
       </c>
       <c r="D3947" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3948">
@@ -73173,7 +73173,7 @@
         </is>
       </c>
       <c r="D4042" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="4043">
@@ -74037,7 +74037,7 @@
         </is>
       </c>
       <c r="D4090" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="4091">
@@ -75225,7 +75225,7 @@
         </is>
       </c>
       <c r="D4156" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4157">
@@ -75261,7 +75261,7 @@
         </is>
       </c>
       <c r="D4158" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4159">
@@ -75369,7 +75369,7 @@
         </is>
       </c>
       <c r="D4164" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4165">
@@ -77178,7 +77178,7 @@
       </c>
       <c r="B4265" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>8741789880525</t>
         </is>
       </c>
       <c r="C4265" t="inlineStr">
@@ -78213,7 +78213,7 @@
         </is>
       </c>
       <c r="D4322" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4323">
@@ -78879,7 +78879,7 @@
         </is>
       </c>
       <c r="D4359" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4360">
@@ -80985,7 +80985,7 @@
         </is>
       </c>
       <c r="D4476" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4477">
@@ -81831,7 +81831,7 @@
         </is>
       </c>
       <c r="D4523" t="n">
-        <v>27.8</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="4524">
@@ -82011,7 +82011,7 @@
         </is>
       </c>
       <c r="D4533" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4534">
@@ -82029,7 +82029,7 @@
         </is>
       </c>
       <c r="D4534" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4535">
@@ -82047,7 +82047,7 @@
         </is>
       </c>
       <c r="D4535" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4536">
@@ -82065,7 +82065,7 @@
         </is>
       </c>
       <c r="D4536" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4537">
@@ -82083,7 +82083,7 @@
         </is>
       </c>
       <c r="D4537" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4538">
@@ -83487,7 +83487,7 @@
         </is>
       </c>
       <c r="D4615" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4616">
@@ -84207,7 +84207,7 @@
         </is>
       </c>
       <c r="D4655" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4656">
@@ -86043,7 +86043,7 @@
         </is>
       </c>
       <c r="D4757" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4758">
@@ -86561,7 +86561,7 @@
       </c>
       <c r="C4786" t="inlineStr">
         <is>
-          <t>DUEL GOLDEN COASR 1,6L</t>
+          <t>DUEL GOLDEN COAST 1,6L</t>
         </is>
       </c>
       <c r="D4786" t="n">
@@ -86602,6 +86602,1428 @@
       </c>
       <c r="D4788" t="n">
         <v>3.6</v>
+      </c>
+    </row>
+    <row r="4789">
+      <c r="A4789" t="n">
+        <v>4788</v>
+      </c>
+      <c r="B4789" t="inlineStr">
+        <is>
+          <t>3850116107233</t>
+        </is>
+      </c>
+      <c r="C4789" t="inlineStr">
+        <is>
+          <t>CEDEVITA</t>
+        </is>
+      </c>
+      <c r="D4789" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4790">
+      <c r="A4790" t="n">
+        <v>4789</v>
+      </c>
+      <c r="B4790" t="inlineStr">
+        <is>
+          <t>3850104019173</t>
+        </is>
+      </c>
+      <c r="C4790" t="inlineStr">
+        <is>
+          <t>FANT ZA RIBLJU C. I PAPRIKAS 60G</t>
+        </is>
+      </c>
+      <c r="D4790" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4791">
+      <c r="A4791" t="n">
+        <v>4790</v>
+      </c>
+      <c r="B4791" t="inlineStr">
+        <is>
+          <t>3856020287337</t>
+        </is>
+      </c>
+      <c r="C4791" t="inlineStr">
+        <is>
+          <t>LINO FRUT.BIO JAB.JAG.BOR.KUP.100G</t>
+        </is>
+      </c>
+      <c r="D4791" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4792">
+      <c r="A4792" t="n">
+        <v>4791</v>
+      </c>
+      <c r="B4792" t="inlineStr">
+        <is>
+          <t>3856020248154</t>
+        </is>
+      </c>
+      <c r="C4792" t="inlineStr">
+        <is>
+          <t>LINO FRUT.BIO VOC. SA ZOB. 100G</t>
+        </is>
+      </c>
+      <c r="D4792" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4793">
+      <c r="A4793" t="n">
+        <v>4792</v>
+      </c>
+      <c r="B4793" t="inlineStr">
+        <is>
+          <t>02142323</t>
+        </is>
+      </c>
+      <c r="C4793" t="inlineStr">
+        <is>
+          <t>KULEN RINFUZA</t>
+        </is>
+      </c>
+      <c r="D4793" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="4794">
+      <c r="A4794" t="n">
+        <v>4793</v>
+      </c>
+      <c r="B4794" t="inlineStr">
+        <is>
+          <t>02102066</t>
+        </is>
+      </c>
+      <c r="C4794" t="inlineStr">
+        <is>
+          <t>ZIMSKA KOBASICA</t>
+        </is>
+      </c>
+      <c r="D4794" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="4795">
+      <c r="A4795" t="n">
+        <v>4794</v>
+      </c>
+      <c r="B4795" t="inlineStr">
+        <is>
+          <t>6974009540666</t>
+        </is>
+      </c>
+      <c r="C4795" t="inlineStr">
+        <is>
+          <t>COOL MATE CET. ZA ZUBE DEEP C.P.</t>
+        </is>
+      </c>
+      <c r="D4795" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4796">
+      <c r="A4796" t="n">
+        <v>4795</v>
+      </c>
+      <c r="B4796" t="inlineStr">
+        <is>
+          <t>6974009540635</t>
+        </is>
+      </c>
+      <c r="C4796" t="inlineStr">
+        <is>
+          <t>COOL MATE CET. ZA ZUBE WHITE 5X</t>
+        </is>
+      </c>
+      <c r="D4796" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4797">
+      <c r="A4797" t="n">
+        <v>4796</v>
+      </c>
+      <c r="B4797" t="inlineStr">
+        <is>
+          <t>4015400876380</t>
+        </is>
+      </c>
+      <c r="C4797" t="inlineStr">
+        <is>
+          <t>FAIRY PLATINUM 72/1 TAB. ZA SUDJE</t>
+        </is>
+      </c>
+      <c r="D4797" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="4798">
+      <c r="A4798" t="n">
+        <v>4797</v>
+      </c>
+      <c r="B4798" t="inlineStr">
+        <is>
+          <t>8700216456395</t>
+        </is>
+      </c>
+      <c r="C4798" t="inlineStr">
+        <is>
+          <t>FAIRY ORIGINAL 100/1 TAB. ZA SUDJE</t>
+        </is>
+      </c>
+      <c r="D4798" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4799">
+      <c r="A4799" t="n">
+        <v>4798</v>
+      </c>
+      <c r="B4799" t="inlineStr">
+        <is>
+          <t>8015353001866</t>
+        </is>
+      </c>
+      <c r="C4799" t="inlineStr">
+        <is>
+          <t>FRESH ORANGE 250ML</t>
+        </is>
+      </c>
+      <c r="D4799" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4800">
+      <c r="A4800" t="n">
+        <v>4799</v>
+      </c>
+      <c r="B4800" t="inlineStr">
+        <is>
+          <t>8015353001965</t>
+        </is>
+      </c>
+      <c r="C4800" t="inlineStr">
+        <is>
+          <t>FRESH CHANEL 250ML</t>
+        </is>
+      </c>
+      <c r="D4800" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4801">
+      <c r="A4801" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B4801" t="inlineStr">
+        <is>
+          <t>8015353001989</t>
+        </is>
+      </c>
+      <c r="C4801" t="inlineStr">
+        <is>
+          <t>FRESH MILLION 250ML</t>
+        </is>
+      </c>
+      <c r="D4801" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4802">
+      <c r="A4802" t="n">
+        <v>4801</v>
+      </c>
+      <c r="B4802" t="inlineStr">
+        <is>
+          <t>8699009449662</t>
+        </is>
+      </c>
+      <c r="C4802" t="inlineStr">
+        <is>
+          <t>LADY'S SECRET BODY MIST 250ML</t>
+        </is>
+      </c>
+      <c r="D4802" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4803">
+      <c r="A4803" t="n">
+        <v>4802</v>
+      </c>
+      <c r="B4803" t="inlineStr">
+        <is>
+          <t>8683749043174</t>
+        </is>
+      </c>
+      <c r="C4803" t="inlineStr">
+        <is>
+          <t>SVJETSKO PRVENSTVO COK. JAJE 20G</t>
+        </is>
+      </c>
+      <c r="D4803" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4804">
+      <c r="A4804" t="n">
+        <v>4803</v>
+      </c>
+      <c r="B4804" t="inlineStr">
+        <is>
+          <t>8683749143171</t>
+        </is>
+      </c>
+      <c r="C4804" t="inlineStr">
+        <is>
+          <t>SVJETSKO PRVENSTVO COK. JAJE 20G</t>
+        </is>
+      </c>
+      <c r="D4804" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4805">
+      <c r="A4805" t="n">
+        <v>4804</v>
+      </c>
+      <c r="B4805" t="inlineStr">
+        <is>
+          <t>8683749040647</t>
+        </is>
+      </c>
+      <c r="C4805" t="inlineStr">
+        <is>
+          <t>BONART LOPTA LIZALO 11G</t>
+        </is>
+      </c>
+      <c r="D4805" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4806">
+      <c r="A4806" t="n">
+        <v>4805</v>
+      </c>
+      <c r="B4806" t="inlineStr">
+        <is>
+          <t>8683749140644</t>
+        </is>
+      </c>
+      <c r="C4806" t="inlineStr">
+        <is>
+          <t>BONART LOPTA LIZALO 11G</t>
+        </is>
+      </c>
+      <c r="D4806" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4807">
+      <c r="A4807" t="n">
+        <v>4806</v>
+      </c>
+      <c r="B4807" t="inlineStr">
+        <is>
+          <t>5449000004864</t>
+        </is>
+      </c>
+      <c r="C4807" t="inlineStr">
+        <is>
+          <t>SPRITE 2L</t>
+        </is>
+      </c>
+      <c r="D4807" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4808">
+      <c r="A4808" t="n">
+        <v>4807</v>
+      </c>
+      <c r="B4808" t="inlineStr">
+        <is>
+          <t>8600102672255</t>
+        </is>
+      </c>
+      <c r="C4808" t="inlineStr">
+        <is>
+          <t>TUBORG GREEN 0.33</t>
+        </is>
+      </c>
+      <c r="D4808" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="4809">
+      <c r="A4809" t="n">
+        <v>4808</v>
+      </c>
+      <c r="B4809" t="inlineStr">
+        <is>
+          <t>5903355085690</t>
+        </is>
+      </c>
+      <c r="C4809" t="inlineStr">
+        <is>
+          <t>YORK PROZIRNA FOLIJA 20M</t>
+        </is>
+      </c>
+      <c r="D4809" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4810">
+      <c r="A4810" t="n">
+        <v>4809</v>
+      </c>
+      <c r="B4810" t="inlineStr">
+        <is>
+          <t>5903355112402</t>
+        </is>
+      </c>
+      <c r="C4810" t="inlineStr">
+        <is>
+          <t>YORK METLA ECO 120CM</t>
+        </is>
+      </c>
+      <c r="D4810" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="4811">
+      <c r="A4811" t="n">
+        <v>4810</v>
+      </c>
+      <c r="B4811" t="inlineStr">
+        <is>
+          <t>8413178004084</t>
+        </is>
+      </c>
+      <c r="C4811" t="inlineStr">
+        <is>
+          <t>VIDAL ROLLA BELTA JAGODA 20G</t>
+        </is>
+      </c>
+      <c r="D4811" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4812">
+      <c r="A4812" t="n">
+        <v>4811</v>
+      </c>
+      <c r="B4812" t="inlineStr">
+        <is>
+          <t>8413178206754</t>
+        </is>
+      </c>
+      <c r="C4812" t="inlineStr">
+        <is>
+          <t>VIDAL ROLLA BELTA DUGA 20G</t>
+        </is>
+      </c>
+      <c r="D4812" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4813">
+      <c r="A4813" t="n">
+        <v>4812</v>
+      </c>
+      <c r="B4813" t="inlineStr">
+        <is>
+          <t>8413178402859</t>
+        </is>
+      </c>
+      <c r="C4813" t="inlineStr">
+        <is>
+          <t>VIDAL PUNJENA PIZZA 90G</t>
+        </is>
+      </c>
+      <c r="D4813" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4814">
+      <c r="A4814" t="n">
+        <v>4813</v>
+      </c>
+      <c r="B4814" t="inlineStr">
+        <is>
+          <t>8001090586032</t>
+        </is>
+      </c>
+      <c r="C4814" t="inlineStr">
+        <is>
+          <t>NATURELLA ULTRA MAXI DUO</t>
+        </is>
+      </c>
+      <c r="D4814" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4815">
+      <c r="A4815" t="n">
+        <v>4814</v>
+      </c>
+      <c r="B4815" t="inlineStr">
+        <is>
+          <t>3870048000136</t>
+        </is>
+      </c>
+      <c r="C4815" t="inlineStr">
+        <is>
+          <t>HEDAL PROZIRNA FOLIJA 50M</t>
+        </is>
+      </c>
+      <c r="D4815" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4816">
+      <c r="A4816" t="n">
+        <v>4815</v>
+      </c>
+      <c r="B4816" t="inlineStr">
+        <is>
+          <t>3870048000709</t>
+        </is>
+      </c>
+      <c r="C4816" t="inlineStr">
+        <is>
+          <t>HEDAL KREP TRAKA AUTO 38X50</t>
+        </is>
+      </c>
+      <c r="D4816" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="4817">
+      <c r="A4817" t="n">
+        <v>4816</v>
+      </c>
+      <c r="B4817" t="inlineStr">
+        <is>
+          <t>4260616920796</t>
+        </is>
+      </c>
+      <c r="C4817" t="inlineStr">
+        <is>
+          <t>ALPENWIESE NAMAZ MASNI 800G</t>
+        </is>
+      </c>
+      <c r="D4817" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="4818">
+      <c r="A4818" t="n">
+        <v>4817</v>
+      </c>
+      <c r="B4818" t="inlineStr">
+        <is>
+          <t>3875000184664</t>
+        </is>
+      </c>
+      <c r="C4818" t="inlineStr">
+        <is>
+          <t>SARAJEVSKI KISELJAK NARANDZADA 0.5</t>
+        </is>
+      </c>
+      <c r="D4818" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="4819">
+      <c r="A4819" t="n">
+        <v>4818</v>
+      </c>
+      <c r="B4819" t="inlineStr">
+        <is>
+          <t>3875001253802</t>
+        </is>
+      </c>
+      <c r="C4819" t="inlineStr">
+        <is>
+          <t>PESKIR 50X90</t>
+        </is>
+      </c>
+      <c r="D4819" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="4820">
+      <c r="A4820" t="n">
+        <v>4819</v>
+      </c>
+      <c r="B4820" t="inlineStr">
+        <is>
+          <t>3875001256582</t>
+        </is>
+      </c>
+      <c r="C4820" t="inlineStr">
+        <is>
+          <t>DJECIJI PESKIR 60X120</t>
+        </is>
+      </c>
+      <c r="D4820" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4821">
+      <c r="A4821" t="n">
+        <v>4820</v>
+      </c>
+      <c r="B4821" t="inlineStr">
+        <is>
+          <t>3875001251600</t>
+        </is>
+      </c>
+      <c r="C4821" t="inlineStr">
+        <is>
+          <t>STOLNJAK 140X140</t>
+        </is>
+      </c>
+      <c r="D4821" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4822">
+      <c r="A4822" t="n">
+        <v>4821</v>
+      </c>
+      <c r="B4822" t="inlineStr">
+        <is>
+          <t>8693495033770</t>
+        </is>
+      </c>
+      <c r="C4822" t="inlineStr">
+        <is>
+          <t>PALMOLIVE SAPUN KAMILICA 90G</t>
+        </is>
+      </c>
+      <c r="D4822" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="4823">
+      <c r="A4823" t="n">
+        <v>4822</v>
+      </c>
+      <c r="B4823" t="inlineStr">
+        <is>
+          <t>5949152121667</t>
+        </is>
+      </c>
+      <c r="C4823" t="inlineStr">
+        <is>
+          <t>VANISH 1L OXI ACTION CRYSTAL WHITE</t>
+        </is>
+      </c>
+      <c r="D4823" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4824">
+      <c r="A4824" t="n">
+        <v>4823</v>
+      </c>
+      <c r="B4824" t="inlineStr">
+        <is>
+          <t>8600102236752</t>
+        </is>
+      </c>
+      <c r="C4824" t="inlineStr">
+        <is>
+          <t>SAFARI POPS LIZALO IGRACKA 9G</t>
+        </is>
+      </c>
+      <c r="D4824" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4825">
+      <c r="A4825" t="n">
+        <v>4824</v>
+      </c>
+      <c r="B4825" t="inlineStr">
+        <is>
+          <t>8606106952179</t>
+        </is>
+      </c>
+      <c r="C4825" t="inlineStr">
+        <is>
+          <t>SAFARI POPS LIZALO IGRACKA 9G</t>
+        </is>
+      </c>
+      <c r="D4825" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4826">
+      <c r="A4826" t="n">
+        <v>4825</v>
+      </c>
+      <c r="B4826" t="inlineStr">
+        <is>
+          <t>5907654440020</t>
+        </is>
+      </c>
+      <c r="C4826" t="inlineStr">
+        <is>
+          <t>SECERNA VUNA 20G EXPLODING</t>
+        </is>
+      </c>
+      <c r="D4826" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4827">
+      <c r="A4827" t="n">
+        <v>4826</v>
+      </c>
+      <c r="B4827" t="inlineStr">
+        <is>
+          <t>5907654410610</t>
+        </is>
+      </c>
+      <c r="C4827" t="inlineStr">
+        <is>
+          <t>SECERNA VUNA 30G JAGODA</t>
+        </is>
+      </c>
+      <c r="D4827" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4828">
+      <c r="A4828" t="n">
+        <v>4827</v>
+      </c>
+      <c r="B4828" t="inlineStr">
+        <is>
+          <t>4008496608881</t>
+        </is>
+      </c>
+      <c r="C4828" t="inlineStr">
+        <is>
+          <t>VARTA AA</t>
+        </is>
+      </c>
+      <c r="D4828" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4829">
+      <c r="A4829" t="n">
+        <v>4828</v>
+      </c>
+      <c r="B4829" t="inlineStr">
+        <is>
+          <t>000394142381</t>
+        </is>
+      </c>
+      <c r="C4829" t="inlineStr">
+        <is>
+          <t>DURACELL AA 1/1</t>
+        </is>
+      </c>
+      <c r="D4829" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4830">
+      <c r="A4830" t="n">
+        <v>4829</v>
+      </c>
+      <c r="B4830" t="inlineStr">
+        <is>
+          <t>9005800343839</t>
+        </is>
+      </c>
+      <c r="C4830" t="inlineStr">
+        <is>
+          <t>NIVEA DEO PEA&amp;BEA 150ML</t>
+        </is>
+      </c>
+      <c r="D4830" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4831">
+      <c r="A4831" t="n">
+        <v>4830</v>
+      </c>
+      <c r="B4831" t="inlineStr">
+        <is>
+          <t>6925374539625</t>
+        </is>
+      </c>
+      <c r="C4831" t="inlineStr">
+        <is>
+          <t>YOLODUCK SUPER SOUR CANDY 30G</t>
+        </is>
+      </c>
+      <c r="D4831" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4832">
+      <c r="A4832" t="n">
+        <v>4831</v>
+      </c>
+      <c r="B4832" t="inlineStr">
+        <is>
+          <t>6925374539632</t>
+        </is>
+      </c>
+      <c r="C4832" t="inlineStr">
+        <is>
+          <t>YOLODUCK SUPER SOUR CANDY 30G</t>
+        </is>
+      </c>
+      <c r="D4832" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4833">
+      <c r="A4833" t="n">
+        <v>4832</v>
+      </c>
+      <c r="B4833" t="inlineStr">
+        <is>
+          <t>8605062103748</t>
+        </is>
+      </c>
+      <c r="C4833" t="inlineStr">
+        <is>
+          <t>LOPTCA SARENA SPUZVASTA</t>
+        </is>
+      </c>
+      <c r="D4833" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4834">
+      <c r="A4834" t="n">
+        <v>4833</v>
+      </c>
+      <c r="B4834" t="inlineStr">
+        <is>
+          <t>8605062103755</t>
+        </is>
+      </c>
+      <c r="C4834" t="inlineStr">
+        <is>
+          <t>LOPTCA SARENA SPUZVASTA</t>
+        </is>
+      </c>
+      <c r="D4834" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4835">
+      <c r="A4835" t="n">
+        <v>4834</v>
+      </c>
+      <c r="B4835" t="inlineStr">
+        <is>
+          <t>660852001992</t>
+        </is>
+      </c>
+      <c r="C4835" t="inlineStr">
+        <is>
+          <t>SIDEQ LUCKY OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4835" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4836">
+      <c r="A4836" t="n">
+        <v>4835</v>
+      </c>
+      <c r="B4836" t="inlineStr">
+        <is>
+          <t>8410202801114</t>
+        </is>
+      </c>
+      <c r="C4836" t="inlineStr">
+        <is>
+          <t>LD LITTLE BOTTLE 4,5ML</t>
+        </is>
+      </c>
+      <c r="D4836" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4837">
+      <c r="A4837" t="n">
+        <v>4836</v>
+      </c>
+      <c r="B4837" t="inlineStr">
+        <is>
+          <t>660852831124</t>
+        </is>
+      </c>
+      <c r="C4837" t="inlineStr">
+        <is>
+          <t>LD ORG.VISNJA OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4837" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4838">
+      <c r="A4838" t="n">
+        <v>4837</v>
+      </c>
+      <c r="B4838" t="inlineStr">
+        <is>
+          <t>8410202330119</t>
+        </is>
+      </c>
+      <c r="C4838" t="inlineStr">
+        <is>
+          <t>LD ORG.VISNJA OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4838" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4839">
+      <c r="A4839" t="n">
+        <v>4838</v>
+      </c>
+      <c r="B4839" t="inlineStr">
+        <is>
+          <t>660852831094</t>
+        </is>
+      </c>
+      <c r="C4839" t="inlineStr">
+        <is>
+          <t>LD ORG.RUZA OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4839" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4840">
+      <c r="A4840" t="n">
+        <v>4839</v>
+      </c>
+      <c r="B4840" t="inlineStr">
+        <is>
+          <t>8410202330089</t>
+        </is>
+      </c>
+      <c r="C4840" t="inlineStr">
+        <is>
+          <t>LD ORG.RUZA OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4840" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4841">
+      <c r="A4841" t="n">
+        <v>4840</v>
+      </c>
+      <c r="B4841" t="inlineStr">
+        <is>
+          <t>660852831056</t>
+        </is>
+      </c>
+      <c r="C4841" t="inlineStr">
+        <is>
+          <t>LD ORG.LAVANDA OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4841" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4842">
+      <c r="A4842" t="n">
+        <v>4841</v>
+      </c>
+      <c r="B4842" t="inlineStr">
+        <is>
+          <t>8410202330065</t>
+        </is>
+      </c>
+      <c r="C4842" t="inlineStr">
+        <is>
+          <t>LD ORG.LAVANDA OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4842" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4843">
+      <c r="A4843" t="n">
+        <v>4842</v>
+      </c>
+      <c r="B4843" t="inlineStr">
+        <is>
+          <t>660852831087</t>
+        </is>
+      </c>
+      <c r="C4843" t="inlineStr">
+        <is>
+          <t>LD ORG.JABUKA OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4843" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4844">
+      <c r="A4844" t="n">
+        <v>4843</v>
+      </c>
+      <c r="B4844" t="inlineStr">
+        <is>
+          <t>8410202330072</t>
+        </is>
+      </c>
+      <c r="C4844" t="inlineStr">
+        <is>
+          <t>LD ORG.JABUKA OSVJEZIVAC</t>
+        </is>
+      </c>
+      <c r="D4844" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4845">
+      <c r="A4845" t="n">
+        <v>4844</v>
+      </c>
+      <c r="B4845" t="inlineStr">
+        <is>
+          <t>8606106348897</t>
+        </is>
+      </c>
+      <c r="C4845" t="inlineStr">
+        <is>
+          <t>MIRISNA SPUZVA 2/1 LIMUN</t>
+        </is>
+      </c>
+      <c r="D4845" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4846">
+      <c r="A4846" t="n">
+        <v>4845</v>
+      </c>
+      <c r="B4846" t="inlineStr">
+        <is>
+          <t>8606106348880</t>
+        </is>
+      </c>
+      <c r="C4846" t="inlineStr">
+        <is>
+          <t>MIRISNA SPUZVA 2/1 SIPAK</t>
+        </is>
+      </c>
+      <c r="D4846" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4847">
+      <c r="A4847" t="n">
+        <v>4846</v>
+      </c>
+      <c r="B4847" t="inlineStr">
+        <is>
+          <t>8606106348903</t>
+        </is>
+      </c>
+      <c r="C4847" t="inlineStr">
+        <is>
+          <t>MIRISNA SPUZVA 2,/4 NARANDZA</t>
+        </is>
+      </c>
+      <c r="D4847" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4848">
+      <c r="A4848" t="n">
+        <v>4847</v>
+      </c>
+      <c r="B4848" t="inlineStr">
+        <is>
+          <t>8600102934801</t>
+        </is>
+      </c>
+      <c r="C4848" t="inlineStr">
+        <is>
+          <t>KENDO ZICA INOX 2/1</t>
+        </is>
+      </c>
+      <c r="D4848" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4849">
+      <c r="A4849" t="n">
+        <v>4848</v>
+      </c>
+      <c r="B4849" t="inlineStr">
+        <is>
+          <t>8606112009300</t>
+        </is>
+      </c>
+      <c r="C4849" t="inlineStr">
+        <is>
+          <t>PACCO FOLIJA PRIJANJAJUCA 30M</t>
+        </is>
+      </c>
+      <c r="D4849" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4850">
+      <c r="A4850" t="n">
+        <v>4849</v>
+      </c>
+      <c r="B4850" t="inlineStr">
+        <is>
+          <t>6972885419748</t>
+        </is>
+      </c>
+      <c r="C4850" t="inlineStr">
+        <is>
+          <t>BEAR MARSHMALLOW LIZALO 35G</t>
+        </is>
+      </c>
+      <c r="D4850" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4851">
+      <c r="A4851" t="n">
+        <v>4850</v>
+      </c>
+      <c r="B4851" t="inlineStr">
+        <is>
+          <t>6972885412794</t>
+        </is>
+      </c>
+      <c r="C4851" t="inlineStr">
+        <is>
+          <t>BEAR MARSHMALLOW LIZALO 35G</t>
+        </is>
+      </c>
+      <c r="D4851" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4852">
+      <c r="A4852" t="n">
+        <v>4851</v>
+      </c>
+      <c r="B4852" t="inlineStr">
+        <is>
+          <t>6975043142106</t>
+        </is>
+      </c>
+      <c r="C4852" t="inlineStr">
+        <is>
+          <t>HAMBURGER GUMMY LOLLIPOP 15G</t>
+        </is>
+      </c>
+      <c r="D4852" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4853">
+      <c r="A4853" t="n">
+        <v>4852</v>
+      </c>
+      <c r="B4853" t="inlineStr">
+        <is>
+          <t>6975043142113</t>
+        </is>
+      </c>
+      <c r="C4853" t="inlineStr">
+        <is>
+          <t>HAMBURGER GUMMY LOLLIPOP 15G</t>
+        </is>
+      </c>
+      <c r="D4853" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4854">
+      <c r="A4854" t="n">
+        <v>4853</v>
+      </c>
+      <c r="B4854" t="inlineStr">
+        <is>
+          <t>6940332300178</t>
+        </is>
+      </c>
+      <c r="C4854" t="inlineStr">
+        <is>
+          <t>ICE CREAM MARSHMALLOW 12G</t>
+        </is>
+      </c>
+      <c r="D4854" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4855">
+      <c r="A4855" t="n">
+        <v>4854</v>
+      </c>
+      <c r="B4855" t="inlineStr">
+        <is>
+          <t>6925374532114</t>
+        </is>
+      </c>
+      <c r="C4855" t="inlineStr">
+        <is>
+          <t>CHIPSALOCA POPPING CANDY 10G</t>
+        </is>
+      </c>
+      <c r="D4855" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4856">
+      <c r="A4856" t="n">
+        <v>4855</v>
+      </c>
+      <c r="B4856" t="inlineStr">
+        <is>
+          <t>6925374539267</t>
+        </is>
+      </c>
+      <c r="C4856" t="inlineStr">
+        <is>
+          <t>CHIPSALOCA POPPING CANDY 10G</t>
+        </is>
+      </c>
+      <c r="D4856" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4857">
+      <c r="A4857" t="n">
+        <v>4856</v>
+      </c>
+      <c r="B4857" t="inlineStr">
+        <is>
+          <t>5319991697904</t>
+        </is>
+      </c>
+      <c r="C4857" t="inlineStr">
+        <is>
+          <t>PRINC CRVENA PEC. PAPRIKA 2500ML</t>
+        </is>
+      </c>
+      <c r="D4857" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="4858">
+      <c r="A4858" t="n">
+        <v>4857</v>
+      </c>
+      <c r="B4858" t="inlineStr">
+        <is>
+          <t>02141760</t>
+        </is>
+      </c>
+      <c r="C4858" t="inlineStr">
+        <is>
+          <t>WIME EDAMER 40% MM</t>
+        </is>
+      </c>
+      <c r="D4858" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="4859">
+      <c r="A4859" t="n">
+        <v>4858</v>
+      </c>
+      <c r="B4859" t="inlineStr">
+        <is>
+          <t>3877000041589</t>
+        </is>
+      </c>
+      <c r="C4859" t="inlineStr">
+        <is>
+          <t>ADRIA TULUMBA U SAFTU 500G</t>
+        </is>
+      </c>
+      <c r="D4859" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="4860">
+      <c r="A4860" t="n">
+        <v>4859</v>
+      </c>
+      <c r="B4860" t="inlineStr">
+        <is>
+          <t>3871945000137</t>
+        </is>
+      </c>
+      <c r="C4860" t="inlineStr">
+        <is>
+          <t>ADRIA ZELE KOCKE 200G</t>
+        </is>
+      </c>
+      <c r="D4860" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4861">
+      <c r="A4861" t="n">
+        <v>4860</v>
+      </c>
+      <c r="B4861" t="inlineStr">
+        <is>
+          <t>3870404002521</t>
+        </is>
+      </c>
+      <c r="C4861" t="inlineStr">
+        <is>
+          <t>RAMPART BISKVIT SA CIMETOM 300G</t>
+        </is>
+      </c>
+      <c r="D4861" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4862">
+      <c r="A4862" t="n">
+        <v>4861</v>
+      </c>
+      <c r="B4862" t="inlineStr">
+        <is>
+          <t>3870174001083</t>
+        </is>
+      </c>
+      <c r="C4862" t="inlineStr">
+        <is>
+          <t>SETI ZELENI CAJ-PLUS 40G</t>
+        </is>
+      </c>
+      <c r="D4862" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4863">
+      <c r="A4863" t="n">
+        <v>4862</v>
+      </c>
+      <c r="B4863" t="inlineStr">
+        <is>
+          <t>3870174000581</t>
+        </is>
+      </c>
+      <c r="C4863" t="inlineStr">
+        <is>
+          <t>SETI ORIGANO 5G</t>
+        </is>
+      </c>
+      <c r="D4863" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4864">
+      <c r="A4864" t="n">
+        <v>4863</v>
+      </c>
+      <c r="B4864" t="inlineStr">
+        <is>
+          <t>3870174000802</t>
+        </is>
+      </c>
+      <c r="C4864" t="inlineStr">
+        <is>
+          <t>SETI ORIGANO 60G</t>
+        </is>
+      </c>
+      <c r="D4864" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="4865">
+      <c r="A4865" t="n">
+        <v>4864</v>
+      </c>
+      <c r="B4865" t="inlineStr">
+        <is>
+          <t>3870174000819</t>
+        </is>
+      </c>
+      <c r="C4865" t="inlineStr">
+        <is>
+          <t>SETI PERSUN LIST 50G</t>
+        </is>
+      </c>
+      <c r="D4865" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4866">
+      <c r="A4866" t="n">
+        <v>4865</v>
+      </c>
+      <c r="B4866" t="inlineStr">
+        <is>
+          <t>3870174000611</t>
+        </is>
+      </c>
+      <c r="C4866" t="inlineStr">
+        <is>
+          <t>SETI SJEME TIKVE 100G</t>
+        </is>
+      </c>
+      <c r="D4866" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="4867">
+      <c r="A4867" t="n">
+        <v>4866</v>
+      </c>
+      <c r="B4867" t="inlineStr">
+        <is>
+          <t>3870174000390</t>
+        </is>
+      </c>
+      <c r="C4867" t="inlineStr">
+        <is>
+          <t>SETI SJEME TIKVE 50G</t>
+        </is>
+      </c>
+      <c r="D4867" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4867"/>
+  <dimension ref="A1:D4929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ELLA GEL ZA KOSU</t>
+          <t>ELLA GEL ZA KOSU PLAVI 250ML</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="364">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>26</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="437">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>STARK KAKAO KEKSICI 220 G</t>
+          <t>STARK KAKAO KEKSICI 220G</t>
         </is>
       </c>
       <c r="D466" t="n">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>BAJADERA 300 G</t>
+          <t>BAJADERA 300G</t>
         </is>
       </c>
       <c r="D475" t="n">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>KIKI 100 G</t>
+          <t>KIKI 100G</t>
         </is>
       </c>
       <c r="D612" t="n">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>BELA MENTA 100 G</t>
+          <t>BELA MENTA 100G</t>
         </is>
       </c>
       <c r="D615" t="n">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>SMOKI 40 G</t>
+          <t>SMOKI STARK 40G</t>
         </is>
       </c>
       <c r="D679" t="n">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>SMOKI STARK 130 G</t>
+          <t>SMOKI STARK 130G</t>
         </is>
       </c>
       <c r="D700" t="n">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>DESERTNI PRELJEV OD COKOLADE 350 G</t>
+          <t>DESERTNI PRELIV OD COKOLADE 350G</t>
         </is>
       </c>
       <c r="D855" t="n">
@@ -16275,7 +16275,7 @@
         </is>
       </c>
       <c r="D881" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="882">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="D1177" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1178">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>ALU FOLIJA 1 KG</t>
+          <t>FRESH ALU FOLIJA  290MM 1KG</t>
         </is>
       </c>
       <c r="D1202" t="n">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>BRONHI BOMBONE 100 G</t>
+          <t>BRONHI BOMBONE 100G</t>
         </is>
       </c>
       <c r="D1333" t="n">
@@ -24659,11 +24659,11 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>MEKSIKANA SALATA SA TUNJEVINOM TREND 160 G</t>
+          <t>TREND MEKS. SALATA SA TUNJ. 160G</t>
         </is>
       </c>
       <c r="D1347" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="1348">
@@ -25253,11 +25253,11 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>SLAG U SPREJU</t>
+          <t>MONTARE SLAG U SPREJU 250G</t>
         </is>
       </c>
       <c r="D1380" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="1381">
@@ -30113,7 +30113,7 @@
       </c>
       <c r="C1650" t="inlineStr">
         <is>
-          <t>COCA-COLA ZERO 0,5 L</t>
+          <t>COCA-COLA ZERO 0,5L</t>
         </is>
       </c>
       <c r="D1650" t="n">
@@ -30347,7 +30347,7 @@
       </c>
       <c r="C1663" t="inlineStr">
         <is>
-          <t>VODA PROLOM 0,5 L</t>
+          <t>VODA PROLOM 0,5L</t>
         </is>
       </c>
       <c r="D1663" t="n">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>JANA VITAMIN LIMUN IMUNO 0,5 L</t>
+          <t>JANA VITAMIN LIMUN IMUNO 0,5L</t>
         </is>
       </c>
       <c r="D1685" t="n">
@@ -31157,7 +31157,7 @@
       </c>
       <c r="C1708" t="inlineStr">
         <is>
-          <t>JUICY FRUITS MULTIVITAMIN 2 L</t>
+          <t>JUICY FRUITS MULTIVITAMIN 2L</t>
         </is>
       </c>
       <c r="D1708" t="n">
@@ -33591,7 +33591,7 @@
         </is>
       </c>
       <c r="D1843" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="1844">
@@ -35603,11 +35603,11 @@
       </c>
       <c r="C1955" t="inlineStr">
         <is>
-          <t>POSUDA 1,7 L</t>
+          <t>POSUDA 1,7L DRINA</t>
         </is>
       </c>
       <c r="D1955" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1956">
@@ -40665,7 +40665,7 @@
         </is>
       </c>
       <c r="D2236" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2237">
@@ -43901,7 +43901,7 @@
       </c>
       <c r="C2416" t="inlineStr">
         <is>
-          <t>FRUTEK JABUKA</t>
+          <t>FRUTEK JABUKA 125ML</t>
         </is>
       </c>
       <c r="D2416" t="n">
@@ -44639,7 +44639,7 @@
       </c>
       <c r="C2457" t="inlineStr">
         <is>
-          <t>GRIL PREMIUM BRIKETI 2,50</t>
+          <t>GRIL PREMIUM BRIKETI 2,50KG</t>
         </is>
       </c>
       <c r="D2457" t="n">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="C2609" t="inlineStr">
         <is>
-          <t>ELLA GEL ZA KOSU</t>
+          <t>ELLA GEL ZA KOSU BIJELI 250ML</t>
         </is>
       </c>
       <c r="D2609" t="n">
@@ -50799,7 +50799,7 @@
         </is>
       </c>
       <c r="D2799" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2800">
@@ -58341,7 +58341,7 @@
         </is>
       </c>
       <c r="D3218" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3219">
@@ -58413,7 +58413,7 @@
         </is>
       </c>
       <c r="D3222" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3223">
@@ -59705,11 +59705,11 @@
       </c>
       <c r="C3294" t="inlineStr">
         <is>
-          <t>POSUDA 2,5L</t>
+          <t>POSUDA 2,5L DRINA</t>
         </is>
       </c>
       <c r="D3294" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3295">
@@ -82767,7 +82767,7 @@
         </is>
       </c>
       <c r="D4575" t="n">
-        <v>6.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="4576">
@@ -87659,7 +87659,7 @@
       </c>
       <c r="C4847" t="inlineStr">
         <is>
-          <t>MIRISNA SPUZVA 2,/4 NARANDZA</t>
+          <t>MIRISNA SPUZVA 2/4 NARANDZA</t>
         </is>
       </c>
       <c r="D4847" t="n">
@@ -88024,6 +88024,1122 @@
       </c>
       <c r="D4867" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4868">
+      <c r="A4868" t="n">
+        <v>4867</v>
+      </c>
+      <c r="B4868" t="inlineStr">
+        <is>
+          <t>3838945004042</t>
+        </is>
+      </c>
+      <c r="C4868" t="inlineStr">
+        <is>
+          <t>DVOJNI C INSTANT LIMUN 200G</t>
+        </is>
+      </c>
+      <c r="D4868" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4869">
+      <c r="A4869" t="n">
+        <v>4868</v>
+      </c>
+      <c r="B4869" t="inlineStr">
+        <is>
+          <t>3838945044035</t>
+        </is>
+      </c>
+      <c r="C4869" t="inlineStr">
+        <is>
+          <t>DVOJNI C INSTANT NARANDZA 500G</t>
+        </is>
+      </c>
+      <c r="D4869" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="4870">
+      <c r="A4870" t="n">
+        <v>4869</v>
+      </c>
+      <c r="B4870" t="inlineStr">
+        <is>
+          <t>3871862002696</t>
+        </is>
+      </c>
+      <c r="C4870" t="inlineStr">
+        <is>
+          <t>TREND DJUVEC 850G</t>
+        </is>
+      </c>
+      <c r="D4870" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="4871">
+      <c r="A4871" t="n">
+        <v>4870</v>
+      </c>
+      <c r="B4871" t="inlineStr">
+        <is>
+          <t>8714800011426</t>
+        </is>
+      </c>
+      <c r="C4871" t="inlineStr">
+        <is>
+          <t>BAVARIA 0.5L BEZALKOHOLO PIVO</t>
+        </is>
+      </c>
+      <c r="D4871" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4872">
+      <c r="A4872" t="n">
+        <v>4871</v>
+      </c>
+      <c r="B4872" t="inlineStr">
+        <is>
+          <t>3870343000619</t>
+        </is>
+      </c>
+      <c r="C4872" t="inlineStr">
+        <is>
+          <t>SOCIVICA 800G MALPAK</t>
+        </is>
+      </c>
+      <c r="D4872" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="4873">
+      <c r="A4873" t="n">
+        <v>4872</v>
+      </c>
+      <c r="B4873" t="inlineStr">
+        <is>
+          <t>8032793344308</t>
+        </is>
+      </c>
+      <c r="C4873" t="inlineStr">
+        <is>
+          <t>POMI PASIRANA RAJCICA 200G</t>
+        </is>
+      </c>
+      <c r="D4873" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="4874">
+      <c r="A4874" t="n">
+        <v>4873</v>
+      </c>
+      <c r="B4874" t="inlineStr">
+        <is>
+          <t>8606012145122</t>
+        </is>
+      </c>
+      <c r="C4874" t="inlineStr">
+        <is>
+          <t>KOSILI SP.P.UB.KOM. I KRP. 100ML</t>
+        </is>
+      </c>
+      <c r="D4874" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4875">
+      <c r="A4875" t="n">
+        <v>4874</v>
+      </c>
+      <c r="B4875" t="inlineStr">
+        <is>
+          <t>8606012145092</t>
+        </is>
+      </c>
+      <c r="C4875" t="inlineStr">
+        <is>
+          <t>LMX SP. PR. KOM. I KRPELJA 100ML</t>
+        </is>
+      </c>
+      <c r="D4875" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="4876">
+      <c r="A4876" t="n">
+        <v>4875</v>
+      </c>
+      <c r="B4876" t="inlineStr">
+        <is>
+          <t>8007150901951</t>
+        </is>
+      </c>
+      <c r="C4876" t="inlineStr">
+        <is>
+          <t>OLITALIA ACETO BALSAMICO 500ML</t>
+        </is>
+      </c>
+      <c r="D4876" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4877">
+      <c r="A4877" t="n">
+        <v>4876</v>
+      </c>
+      <c r="B4877" t="inlineStr">
+        <is>
+          <t>3870254000845</t>
+        </is>
+      </c>
+      <c r="C4877" t="inlineStr">
+        <is>
+          <t>SALBOS SO ZA MASINU LIMUN 1.5KG</t>
+        </is>
+      </c>
+      <c r="D4877" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="4878">
+      <c r="A4878" t="n">
+        <v>4877</v>
+      </c>
+      <c r="B4878" t="inlineStr">
+        <is>
+          <t>3870254000593</t>
+        </is>
+      </c>
+      <c r="C4878" t="inlineStr">
+        <is>
+          <t>SALBON SO ZA MASINU 1.5KG</t>
+        </is>
+      </c>
+      <c r="D4878" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4879">
+      <c r="A4879" t="n">
+        <v>4878</v>
+      </c>
+      <c r="B4879" t="inlineStr">
+        <is>
+          <t>3870022005188</t>
+        </is>
+      </c>
+      <c r="C4879" t="inlineStr">
+        <is>
+          <t>DITA DESTILOVANA VODA 1L</t>
+        </is>
+      </c>
+      <c r="D4879" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="4880">
+      <c r="A4880" t="n">
+        <v>4879</v>
+      </c>
+      <c r="B4880" t="inlineStr">
+        <is>
+          <t>3870022005065</t>
+        </is>
+      </c>
+      <c r="C4880" t="inlineStr">
+        <is>
+          <t>DITA DESTILOVANA VODA 5L</t>
+        </is>
+      </c>
+      <c r="D4880" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4881">
+      <c r="A4881" t="n">
+        <v>4880</v>
+      </c>
+      <c r="B4881" t="inlineStr">
+        <is>
+          <t>8606112009515</t>
+        </is>
+      </c>
+      <c r="C4881" t="inlineStr">
+        <is>
+          <t>EP PAPIR ZA PECENJE 16/1 42X38</t>
+        </is>
+      </c>
+      <c r="D4881" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4882">
+      <c r="A4882" t="n">
+        <v>4881</v>
+      </c>
+      <c r="B4882" t="inlineStr">
+        <is>
+          <t>8605062104554</t>
+        </is>
+      </c>
+      <c r="C4882" t="inlineStr">
+        <is>
+          <t>VODENI PISTOLJ DELFIN</t>
+        </is>
+      </c>
+      <c r="D4882" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4883">
+      <c r="A4883" t="n">
+        <v>4882</v>
+      </c>
+      <c r="B4883" t="inlineStr">
+        <is>
+          <t>3850104295096</t>
+        </is>
+      </c>
+      <c r="C4883" t="inlineStr">
+        <is>
+          <t>FANT TJEST. SA 4 VRSTE SIRA 53G</t>
+        </is>
+      </c>
+      <c r="D4883" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4884">
+      <c r="A4884" t="n">
+        <v>4883</v>
+      </c>
+      <c r="B4884" t="inlineStr">
+        <is>
+          <t>3838945040815</t>
+        </is>
+      </c>
+      <c r="C4884" t="inlineStr">
+        <is>
+          <t>DVOJNI C 0.25L LIMENKA</t>
+        </is>
+      </c>
+      <c r="D4884" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4885">
+      <c r="A4885" t="n">
+        <v>4884</v>
+      </c>
+      <c r="B4885" t="inlineStr">
+        <is>
+          <t>3838945503013</t>
+        </is>
+      </c>
+      <c r="C4885" t="inlineStr">
+        <is>
+          <t>FRTUEK KASICA 120G JABUKA</t>
+        </is>
+      </c>
+      <c r="D4885" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4886">
+      <c r="A4886" t="n">
+        <v>4885</v>
+      </c>
+      <c r="B4886" t="inlineStr">
+        <is>
+          <t>5999563941248</t>
+        </is>
+      </c>
+      <c r="C4886" t="inlineStr">
+        <is>
+          <t>KING HRANA ZA PSE PILETINA 1240G</t>
+        </is>
+      </c>
+      <c r="D4886" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4887">
+      <c r="A4887" t="n">
+        <v>4886</v>
+      </c>
+      <c r="B4887" t="inlineStr">
+        <is>
+          <t>3856016327284</t>
+        </is>
+      </c>
+      <c r="C4887" t="inlineStr">
+        <is>
+          <t>MARGO NOVA MARG. 225G</t>
+        </is>
+      </c>
+      <c r="D4887" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4888">
+      <c r="A4888" t="n">
+        <v>4887</v>
+      </c>
+      <c r="B4888" t="inlineStr">
+        <is>
+          <t>3838945521161</t>
+        </is>
+      </c>
+      <c r="C4888" t="inlineStr">
+        <is>
+          <t>FRUCTAL NATURA CVEKLA 100% 700ML</t>
+        </is>
+      </c>
+      <c r="D4888" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4889">
+      <c r="A4889" t="n">
+        <v>4888</v>
+      </c>
+      <c r="B4889" t="inlineStr">
+        <is>
+          <t>3838945044028</t>
+        </is>
+      </c>
+      <c r="C4889" t="inlineStr">
+        <is>
+          <t>DVOJNI C INSTANT NARANDZA 200G</t>
+        </is>
+      </c>
+      <c r="D4889" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4890">
+      <c r="A4890" t="n">
+        <v>4889</v>
+      </c>
+      <c r="B4890" t="inlineStr">
+        <is>
+          <t>8600169500022</t>
+        </is>
+      </c>
+      <c r="C4890" t="inlineStr">
+        <is>
+          <t>PROLOM VODA 1.5</t>
+        </is>
+      </c>
+      <c r="D4890" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4891">
+      <c r="A4891" t="n">
+        <v>4890</v>
+      </c>
+      <c r="B4891" t="inlineStr">
+        <is>
+          <t>3872216000008</t>
+        </is>
+      </c>
+      <c r="C4891" t="inlineStr">
+        <is>
+          <t>ARGETA KOKOSIJA PASTETA 95G</t>
+        </is>
+      </c>
+      <c r="D4891" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4892">
+      <c r="A4892" t="n">
+        <v>4891</v>
+      </c>
+      <c r="B4892" t="inlineStr">
+        <is>
+          <t>3600114011248</t>
+        </is>
+      </c>
+      <c r="C4892" t="inlineStr">
+        <is>
+          <t>JAFFA NAPOL. COKO&amp;NAR. 160G</t>
+        </is>
+      </c>
+      <c r="D4892" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4893">
+      <c r="A4893" t="n">
+        <v>4892</v>
+      </c>
+      <c r="B4893" t="inlineStr">
+        <is>
+          <t>185988858336</t>
+        </is>
+      </c>
+      <c r="C4893" t="inlineStr">
+        <is>
+          <t>ABC SIRNI NAMAZ 200G</t>
+        </is>
+      </c>
+      <c r="D4893" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4894">
+      <c r="A4894" t="n">
+        <v>4893</v>
+      </c>
+      <c r="B4894" t="inlineStr">
+        <is>
+          <t>3858890674044</t>
+        </is>
+      </c>
+      <c r="C4894" t="inlineStr">
+        <is>
+          <t>JANA VITAM. HAPPY NARANDZA 1,5L</t>
+        </is>
+      </c>
+      <c r="D4894" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4895">
+      <c r="A4895" t="n">
+        <v>4894</v>
+      </c>
+      <c r="B4895" t="inlineStr">
+        <is>
+          <t>8500169600022</t>
+        </is>
+      </c>
+      <c r="C4895" t="inlineStr">
+        <is>
+          <t>PROLOM VODA 1,5L</t>
+        </is>
+      </c>
+      <c r="D4895" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4896">
+      <c r="A4896" t="n">
+        <v>4895</v>
+      </c>
+      <c r="B4896" t="inlineStr">
+        <is>
+          <t>4250443474654</t>
+        </is>
+      </c>
+      <c r="C4896" t="inlineStr">
+        <is>
+          <t>HOLZKOHLE DRVENI UGALJ 2,25KG</t>
+        </is>
+      </c>
+      <c r="D4896" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4897">
+      <c r="A4897" t="n">
+        <v>4896</v>
+      </c>
+      <c r="B4897" t="inlineStr">
+        <is>
+          <t>4250443474661</t>
+        </is>
+      </c>
+      <c r="C4897" t="inlineStr">
+        <is>
+          <t>HOLZKOHLE DRVENI UGALJ 2,25KG</t>
+        </is>
+      </c>
+      <c r="D4897" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4898">
+      <c r="A4898" t="n">
+        <v>4897</v>
+      </c>
+      <c r="B4898" t="inlineStr">
+        <is>
+          <t>3871862004706</t>
+        </is>
+      </c>
+      <c r="C4898" t="inlineStr">
+        <is>
+          <t>LUMAX DRVENI UGALJ 2KG</t>
+        </is>
+      </c>
+      <c r="D4898" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="4899">
+      <c r="A4899" t="n">
+        <v>4898</v>
+      </c>
+      <c r="B4899" t="inlineStr">
+        <is>
+          <t>3859888141179</t>
+        </is>
+      </c>
+      <c r="C4899" t="inlineStr">
+        <is>
+          <t>MR. FIRE GRILL BRIKTER 2,5KG</t>
+        </is>
+      </c>
+      <c r="D4899" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="4900">
+      <c r="A4900" t="n">
+        <v>4899</v>
+      </c>
+      <c r="B4900" t="inlineStr">
+        <is>
+          <t>8600104004540</t>
+        </is>
+      </c>
+      <c r="C4900" t="inlineStr">
+        <is>
+          <t>STRUDLE KAJSIJA 240G</t>
+        </is>
+      </c>
+      <c r="D4900" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4901">
+      <c r="A4901" t="n">
+        <v>4900</v>
+      </c>
+      <c r="B4901" t="inlineStr">
+        <is>
+          <t>8600104004632</t>
+        </is>
+      </c>
+      <c r="C4901" t="inlineStr">
+        <is>
+          <t>STRUDLE VISNJA 2,40G</t>
+        </is>
+      </c>
+      <c r="D4901" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4902">
+      <c r="A4902" t="n">
+        <v>4901</v>
+      </c>
+      <c r="B4902" t="inlineStr">
+        <is>
+          <t>600104004748</t>
+        </is>
+      </c>
+      <c r="C4902" t="inlineStr">
+        <is>
+          <t>STRUDLE MIJESANA 360G</t>
+        </is>
+      </c>
+      <c r="D4902" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4903">
+      <c r="A4903" t="n">
+        <v>4902</v>
+      </c>
+      <c r="B4903" t="inlineStr">
+        <is>
+          <t>8600046004844</t>
+        </is>
+      </c>
+      <c r="C4903" t="inlineStr">
+        <is>
+          <t>BONZITA MALINA JOGURT 28G</t>
+        </is>
+      </c>
+      <c r="D4903" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4904">
+      <c r="A4904" t="n">
+        <v>4903</v>
+      </c>
+      <c r="B4904" t="inlineStr">
+        <is>
+          <t>3870398907208</t>
+        </is>
+      </c>
+      <c r="C4904" t="inlineStr">
+        <is>
+          <t>CVJETACA 400G</t>
+        </is>
+      </c>
+      <c r="D4904" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4905">
+      <c r="A4905" t="n">
+        <v>4904</v>
+      </c>
+      <c r="B4905" t="inlineStr">
+        <is>
+          <t>5948351012875</t>
+        </is>
+      </c>
+      <c r="C4905" t="inlineStr">
+        <is>
+          <t>POK. VREC RIBE PLAVA</t>
+        </is>
+      </c>
+      <c r="D4905" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4906">
+      <c r="A4906" t="n">
+        <v>4905</v>
+      </c>
+      <c r="B4906" t="inlineStr">
+        <is>
+          <t>5900928007264</t>
+        </is>
+      </c>
+      <c r="C4906" t="inlineStr">
+        <is>
+          <t>DIJO GRILLED TORTILJA 250G</t>
+        </is>
+      </c>
+      <c r="D4906" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="4907">
+      <c r="A4907" t="n">
+        <v>4906</v>
+      </c>
+      <c r="B4907" t="inlineStr">
+        <is>
+          <t>8610056050212</t>
+        </is>
+      </c>
+      <c r="C4907" t="inlineStr">
+        <is>
+          <t>SET KERAMICKIH ZDJELICA 4/1</t>
+        </is>
+      </c>
+      <c r="D4907" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="4908">
+      <c r="A4908" t="n">
+        <v>4907</v>
+      </c>
+      <c r="B4908" t="inlineStr">
+        <is>
+          <t>8610056049476</t>
+        </is>
+      </c>
+      <c r="C4908" t="inlineStr">
+        <is>
+          <t>SET KER. ZDJ. SA KASICICAMA 4/1</t>
+        </is>
+      </c>
+      <c r="D4908" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="4909">
+      <c r="A4909" t="n">
+        <v>4908</v>
+      </c>
+      <c r="B4909" t="inlineStr">
+        <is>
+          <t>8610056049544</t>
+        </is>
+      </c>
+      <c r="C4909" t="inlineStr">
+        <is>
+          <t>SET KER. OVALA 2/1</t>
+        </is>
+      </c>
+      <c r="D4909" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4910">
+      <c r="A4910" t="n">
+        <v>4909</v>
+      </c>
+      <c r="B4910" t="inlineStr">
+        <is>
+          <t>7988896535895</t>
+        </is>
+      </c>
+      <c r="C4910" t="inlineStr">
+        <is>
+          <t>TAVA ZA PALACINKE 24CM</t>
+        </is>
+      </c>
+      <c r="D4910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4911">
+      <c r="A4911" t="n">
+        <v>4910</v>
+      </c>
+      <c r="B4911" t="inlineStr">
+        <is>
+          <t>6260361069250</t>
+        </is>
+      </c>
+      <c r="C4911" t="inlineStr">
+        <is>
+          <t>BOKAL MAYA 2000ML</t>
+        </is>
+      </c>
+      <c r="D4911" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="4912">
+      <c r="A4912" t="n">
+        <v>4911</v>
+      </c>
+      <c r="B4912" t="inlineStr">
+        <is>
+          <t>8610056048615</t>
+        </is>
+      </c>
+      <c r="C4912" t="inlineStr">
+        <is>
+          <t>ZDJELA 2500ML 25X9CM</t>
+        </is>
+      </c>
+      <c r="D4912" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4913">
+      <c r="A4913" t="n">
+        <v>4912</v>
+      </c>
+      <c r="B4913" t="inlineStr">
+        <is>
+          <t>8610056048622</t>
+        </is>
+      </c>
+      <c r="C4913" t="inlineStr">
+        <is>
+          <t>ZDJELA 1500ML 20X7,5CM</t>
+        </is>
+      </c>
+      <c r="D4913" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4914">
+      <c r="A4914" t="n">
+        <v>4913</v>
+      </c>
+      <c r="B4914" t="inlineStr">
+        <is>
+          <t>8610056048608</t>
+        </is>
+      </c>
+      <c r="C4914" t="inlineStr">
+        <is>
+          <t>ZDJELA 4400ML 30X10,7CM</t>
+        </is>
+      </c>
+      <c r="D4914" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4915">
+      <c r="A4915" t="n">
+        <v>4914</v>
+      </c>
+      <c r="B4915" t="inlineStr">
+        <is>
+          <t>6943750903624</t>
+        </is>
+      </c>
+      <c r="C4915" t="inlineStr">
+        <is>
+          <t>KOMPOT OD BRESKVE 4X120GR</t>
+        </is>
+      </c>
+      <c r="D4915" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="4916">
+      <c r="A4916" t="n">
+        <v>4915</v>
+      </c>
+      <c r="B4916" t="inlineStr">
+        <is>
+          <t>8610056035028</t>
+        </is>
+      </c>
+      <c r="C4916" t="inlineStr">
+        <is>
+          <t>PEKAC 34,5X24X8CM</t>
+        </is>
+      </c>
+      <c r="D4916" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="4917">
+      <c r="A4917" t="n">
+        <v>4916</v>
+      </c>
+      <c r="B4917" t="inlineStr">
+        <is>
+          <t>6924565931255</t>
+        </is>
+      </c>
+      <c r="C4917" t="inlineStr">
+        <is>
+          <t>BRIJAC MUSKI 1/1</t>
+        </is>
+      </c>
+      <c r="D4917" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4918">
+      <c r="A4918" t="n">
+        <v>4917</v>
+      </c>
+      <c r="B4918" t="inlineStr">
+        <is>
+          <t>6924565930340</t>
+        </is>
+      </c>
+      <c r="C4918" t="inlineStr">
+        <is>
+          <t>BRIJAC ZENSKI 1/1</t>
+        </is>
+      </c>
+      <c r="D4918" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4919">
+      <c r="A4919" t="n">
+        <v>4918</v>
+      </c>
+      <c r="B4919" t="inlineStr">
+        <is>
+          <t>5997844301095</t>
+        </is>
+      </c>
+      <c r="C4919" t="inlineStr">
+        <is>
+          <t>PLASTICNA ZICA SA SUDJE 3/1</t>
+        </is>
+      </c>
+      <c r="D4919" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4920">
+      <c r="A4920" t="n">
+        <v>4919</v>
+      </c>
+      <c r="B4920" t="inlineStr">
+        <is>
+          <t>8696630115546</t>
+        </is>
+      </c>
+      <c r="C4920" t="inlineStr">
+        <is>
+          <t>ALBA COSMETIC SPREJ ZA INS. 400ML</t>
+        </is>
+      </c>
+      <c r="D4920" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="4921">
+      <c r="A4921" t="n">
+        <v>4920</v>
+      </c>
+      <c r="B4921" t="inlineStr">
+        <is>
+          <t>8606003591006</t>
+        </is>
+      </c>
+      <c r="C4921" t="inlineStr">
+        <is>
+          <t>VANGLA 3L DRINA</t>
+        </is>
+      </c>
+      <c r="D4921" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4922">
+      <c r="A4922" t="n">
+        <v>4921</v>
+      </c>
+      <c r="B4922" t="inlineStr">
+        <is>
+          <t>8606003592256</t>
+        </is>
+      </c>
+      <c r="C4922" t="inlineStr">
+        <is>
+          <t>MIX PUSUDA 5L DRINA</t>
+        </is>
+      </c>
+      <c r="D4922" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="4923">
+      <c r="A4923" t="n">
+        <v>4922</v>
+      </c>
+      <c r="B4923" t="inlineStr">
+        <is>
+          <t>3850105101075</t>
+        </is>
+      </c>
+      <c r="C4923" t="inlineStr">
+        <is>
+          <t>ARF SRED. ZA CIS. SA PRSKAL. 650ML</t>
+        </is>
+      </c>
+      <c r="D4923" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4924">
+      <c r="A4924" t="n">
+        <v>4923</v>
+      </c>
+      <c r="B4924" t="inlineStr">
+        <is>
+          <t>3850105109545</t>
+        </is>
+      </c>
+      <c r="C4924" t="inlineStr">
+        <is>
+          <t>ARF SRED. ZA CIS. SA PRSKAL. 650ML</t>
+        </is>
+      </c>
+      <c r="D4924" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4925">
+      <c r="A4925" t="n">
+        <v>4924</v>
+      </c>
+      <c r="B4925" t="inlineStr">
+        <is>
+          <t>3875010513476</t>
+        </is>
+      </c>
+      <c r="C4925" t="inlineStr">
+        <is>
+          <t>ARF SRED. ZA CIS. SA PRSKAL. 650ML</t>
+        </is>
+      </c>
+      <c r="D4925" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4926">
+      <c r="A4926" t="n">
+        <v>4925</v>
+      </c>
+      <c r="B4926" t="inlineStr">
+        <is>
+          <t>9000101832990</t>
+        </is>
+      </c>
+      <c r="C4926" t="inlineStr">
+        <is>
+          <t>PERSIL DET. ZA VES PRASK. 9KG</t>
+        </is>
+      </c>
+      <c r="D4926" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="4927">
+      <c r="A4927" t="n">
+        <v>4926</v>
+      </c>
+      <c r="B4927" t="inlineStr">
+        <is>
+          <t>3875000031470</t>
+        </is>
+      </c>
+      <c r="C4927" t="inlineStr">
+        <is>
+          <t>EXOTIC ORANGE LIMENKA 0,33L</t>
+        </is>
+      </c>
+      <c r="D4927" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="4928">
+      <c r="A4928" t="n">
+        <v>4927</v>
+      </c>
+      <c r="B4928" t="inlineStr">
+        <is>
+          <t>8445291643796</t>
+        </is>
+      </c>
+      <c r="C4928" t="inlineStr">
+        <is>
+          <t>NES VANILIJA MEGA PACK 14X14G</t>
+        </is>
+      </c>
+      <c r="D4928" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="4929">
+      <c r="A4929" t="n">
+        <v>4928</v>
+      </c>
+      <c r="B4929" t="inlineStr">
+        <is>
+          <t>3870598331851</t>
+        </is>
+      </c>
+      <c r="C4929" t="inlineStr">
+        <is>
+          <t>BLA BLA BLA</t>
+        </is>
+      </c>
+      <c r="D4929" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -89130,16 +89130,16 @@
       </c>
       <c r="B4929" t="inlineStr">
         <is>
-          <t>3870598331851</t>
+          <t>3870379090424</t>
         </is>
       </c>
       <c r="C4929" t="inlineStr">
         <is>
-          <t>BLA BLA BLA</t>
+          <t>TOPINGO CHOCO ORANGE BISCUITS 112G</t>
         </is>
       </c>
       <c r="D4929" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -22049,7 +22049,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>FRESH ALU FOLIJA  290MM 1KG</t>
+          <t>FRESH ALU FOLIJA 290MM 1KG</t>
         </is>
       </c>
       <c r="D1202" t="n">
@@ -87137,7 +87137,7 @@
       </c>
       <c r="C4818" t="inlineStr">
         <is>
-          <t>SARAJEVSKI KISELJAK NARANDZADA 0.5</t>
+          <t>SARAJ. KISELJAK NARANDZADA 0.5L</t>
         </is>
       </c>
       <c r="D4818" t="n">
@@ -87321,7 +87321,7 @@
         </is>
       </c>
       <c r="D4828" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4829">
@@ -88275,7 +88275,7 @@
         </is>
       </c>
       <c r="D4881" t="n">
-        <v>100</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4882">
@@ -88365,7 +88365,7 @@
         </is>
       </c>
       <c r="D4886" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4887">
@@ -88383,7 +88383,7 @@
         </is>
       </c>
       <c r="D4887" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4888">
@@ -88401,7 +88401,7 @@
         </is>
       </c>
       <c r="D4888" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4889">
@@ -88419,7 +88419,7 @@
         </is>
       </c>
       <c r="D4889" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4890">
@@ -88433,11 +88433,11 @@
       </c>
       <c r="C4890" t="inlineStr">
         <is>
-          <t>PROLOM VODA 1.5</t>
+          <t>PROLOM VODA 1.5L</t>
         </is>
       </c>
       <c r="D4890" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4891">
@@ -88455,7 +88455,7 @@
         </is>
       </c>
       <c r="D4891" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4892">
@@ -88473,7 +88473,7 @@
         </is>
       </c>
       <c r="D4892" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4893">
@@ -88491,7 +88491,7 @@
         </is>
       </c>
       <c r="D4893" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4894">
@@ -88527,7 +88527,7 @@
         </is>
       </c>
       <c r="D4895" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4896">
@@ -88595,7 +88595,7 @@
       </c>
       <c r="C4899" t="inlineStr">
         <is>
-          <t>MR. FIRE GRILL BRIKTER 2,5KG</t>
+          <t>MR. FIRE GRILL BRIKETE 2,5KG</t>
         </is>
       </c>
       <c r="D4899" t="n">
@@ -88631,7 +88631,7 @@
       </c>
       <c r="C4901" t="inlineStr">
         <is>
-          <t>STRUDLE VISNJA 2,40G</t>
+          <t>STRUDLE VISNJA 240G</t>
         </is>
       </c>
       <c r="D4901" t="n">
@@ -88685,7 +88685,7 @@
       </c>
       <c r="C4904" t="inlineStr">
         <is>
-          <t>CVJETACA 400G</t>
+          <t>LEDO CVJETACA 400G</t>
         </is>
       </c>
       <c r="D4904" t="n">
@@ -88923,7 +88923,7 @@
         </is>
       </c>
       <c r="D4917" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4918">
@@ -88941,7 +88941,7 @@
         </is>
       </c>
       <c r="D4918" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4919">

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4929"/>
+  <dimension ref="A1:D4934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>KREM KAFA 200 G</t>
+          <t>KREM KAFA 200G</t>
         </is>
       </c>
       <c r="D1360" t="n">
@@ -39963,7 +39963,7 @@
         </is>
       </c>
       <c r="D2197" t="n">
-        <v>6.3</v>
+        <v>6.799999999999999</v>
       </c>
     </row>
     <row r="2198">
@@ -40629,7 +40629,7 @@
         </is>
       </c>
       <c r="D2234" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="2235">
@@ -53391,7 +53391,7 @@
         </is>
       </c>
       <c r="D2943" t="n">
-        <v>5.84</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="2944">
@@ -64605,7 +64605,7 @@
         </is>
       </c>
       <c r="D3566" t="n">
-        <v>16</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="3567">
@@ -89139,7 +89139,97 @@
         </is>
       </c>
       <c r="D4929" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4930">
+      <c r="A4930" t="n">
+        <v>4929</v>
+      </c>
+      <c r="B4930" t="inlineStr">
+        <is>
+          <t>8600046007159</t>
+        </is>
+      </c>
+      <c r="C4930" t="inlineStr">
+        <is>
+          <t>SLANI PERECI 75G</t>
+        </is>
+      </c>
+      <c r="D4930" t="n">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="4931">
+      <c r="A4931" t="n">
+        <v>4930</v>
+      </c>
+      <c r="B4931" t="inlineStr">
+        <is>
+          <t>8600046007173</t>
+        </is>
+      </c>
+      <c r="C4931" t="inlineStr">
+        <is>
+          <t>SLANI PERECI 120G</t>
+        </is>
+      </c>
+      <c r="D4931" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4932">
+      <c r="A4932" t="n">
+        <v>4931</v>
+      </c>
+      <c r="B4932" t="inlineStr">
+        <is>
+          <t>3850105180674</t>
+        </is>
+      </c>
+      <c r="C4932" t="inlineStr">
+        <is>
+          <t>ORNEL CLAMING 3.75L</t>
+        </is>
+      </c>
+      <c r="D4932" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="4933">
+      <c r="A4933" t="n">
+        <v>4932</v>
+      </c>
+      <c r="B4933" t="inlineStr">
+        <is>
+          <t>3850105180643</t>
+        </is>
+      </c>
+      <c r="C4933" t="inlineStr">
+        <is>
+          <t>ORNEL GOLDEN DREAM 3.75L</t>
+        </is>
+      </c>
+      <c r="D4933" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="4934">
+      <c r="A4934" t="n">
+        <v>4933</v>
+      </c>
+      <c r="B4934" t="inlineStr">
+        <is>
+          <t>3850105166111</t>
+        </is>
+      </c>
+      <c r="C4934" t="inlineStr">
+        <is>
+          <t>BIS PURE LEMON 400ML SAPONIA</t>
+        </is>
+      </c>
+      <c r="D4934" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4934"/>
+  <dimension ref="A1:D4938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>KREM KAFA 500 G</t>
+          <t>KREM KAFA 500G</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>NEGRO BOMBONE 100 G</t>
+          <t>NEGRO 100G</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>16.2</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="476">
@@ -16095,7 +16095,7 @@
         </is>
       </c>
       <c r="D871" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="872">
@@ -22143,7 +22143,7 @@
         </is>
       </c>
       <c r="D1207" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1208">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="C1712" t="inlineStr">
         <is>
-          <t>KOKTA 1,5 L</t>
+          <t>COCTA 1,5L</t>
         </is>
       </c>
       <c r="D1712" t="n">
@@ -39797,7 +39797,7 @@
       </c>
       <c r="C2188" t="inlineStr">
         <is>
-          <t>MAX PRICE I VALUE</t>
+          <t>HRANA ZA PSE PILETINA MAX 1240G</t>
         </is>
       </c>
       <c r="D2188" t="n">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="D2347" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="2348">
@@ -43361,11 +43361,11 @@
       </c>
       <c r="C2386" t="inlineStr">
         <is>
-          <t>FEFERONI LJUTI 370ML</t>
+          <t>FEFERONI LJUTI 370ML VEGA MIX</t>
         </is>
       </c>
       <c r="D2386" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="2387">
@@ -49049,7 +49049,7 @@
       </c>
       <c r="C2702" t="inlineStr">
         <is>
-          <t>NESCAFE 3U1</t>
+          <t>NESCAFE 3U1 10/1</t>
         </is>
       </c>
       <c r="D2702" t="n">
@@ -65069,11 +65069,11 @@
       </c>
       <c r="C3592" t="inlineStr">
         <is>
-          <t>KESE ZA SMECE 35L</t>
+          <t>KESE ZA SMECE 35L 15/1 CRNA PRIMO</t>
         </is>
       </c>
       <c r="D3592" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3593">
@@ -67373,11 +67373,11 @@
       </c>
       <c r="C3720" t="inlineStr">
         <is>
-          <t>KESE ZA SMECE 60L</t>
+          <t>KESE ZA SMECE 60L 10/1 CRNA PRIMO</t>
         </is>
       </c>
       <c r="D3720" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3721">
@@ -75297,7 +75297,7 @@
         </is>
       </c>
       <c r="D4160" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4161">
@@ -88797,7 +88797,7 @@
         </is>
       </c>
       <c r="D4910" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="4911">
@@ -88833,7 +88833,7 @@
         </is>
       </c>
       <c r="D4912" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4913">
@@ -88851,7 +88851,7 @@
         </is>
       </c>
       <c r="D4913" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4914">
@@ -88869,7 +88869,7 @@
         </is>
       </c>
       <c r="D4914" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="4915">
@@ -89157,7 +89157,7 @@
         </is>
       </c>
       <c r="D4930" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4931">
@@ -89229,7 +89229,79 @@
         </is>
       </c>
       <c r="D4934" t="n">
-        <v>12</v>
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="4935">
+      <c r="A4935" t="n">
+        <v>4934</v>
+      </c>
+      <c r="B4935" t="inlineStr">
+        <is>
+          <t>3870022004006</t>
+        </is>
+      </c>
+      <c r="C4935" t="inlineStr">
+        <is>
+          <t>DITA MONIA TEC.S. SILKY TOUCH 1L</t>
+        </is>
+      </c>
+      <c r="D4935" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4936">
+      <c r="A4936" t="n">
+        <v>4935</v>
+      </c>
+      <c r="B4936" t="inlineStr">
+        <is>
+          <t>38700200403</t>
+        </is>
+      </c>
+      <c r="C4936" t="inlineStr">
+        <is>
+          <t>DITA MONIA TEC.S. ORCHID SENS. 1L</t>
+        </is>
+      </c>
+      <c r="D4936" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4937">
+      <c r="A4937" t="n">
+        <v>4936</v>
+      </c>
+      <c r="B4937" t="inlineStr">
+        <is>
+          <t>3870379090073</t>
+        </is>
+      </c>
+      <c r="C4937" t="inlineStr">
+        <is>
+          <t>TUNA U KOMADU 170G OLD SAILOR</t>
+        </is>
+      </c>
+      <c r="D4937" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4938">
+      <c r="A4938" t="n">
+        <v>4937</v>
+      </c>
+      <c r="B4938" t="inlineStr">
+        <is>
+          <t>3870254000326</t>
+        </is>
+      </c>
+      <c r="C4938" t="inlineStr">
+        <is>
+          <t>FEFERONI LJUTI 720ML VEGA MIX</t>
+        </is>
+      </c>
+      <c r="D4938" t="n">
+        <v>4.9</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4938"/>
+  <dimension ref="A1:D4940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58661,11 +58661,11 @@
       </c>
       <c r="C3236" t="inlineStr">
         <is>
-          <t>MIRODJIJA 5G</t>
+          <t>MIRODJIJA 5G STAMENKOVIC</t>
         </is>
       </c>
       <c r="D3236" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3237">
@@ -89302,6 +89302,42 @@
       </c>
       <c r="D4938" t="n">
         <v>4.9</v>
+      </c>
+    </row>
+    <row r="4939">
+      <c r="A4939" t="n">
+        <v>4938</v>
+      </c>
+      <c r="B4939" t="inlineStr">
+        <is>
+          <t>8600101550446</t>
+        </is>
+      </c>
+      <c r="C4939" t="inlineStr">
+        <is>
+          <t>ZELATIN 10G UNIJAPAK</t>
+        </is>
+      </c>
+      <c r="D4939" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4940">
+      <c r="A4940" t="n">
+        <v>4939</v>
+      </c>
+      <c r="B4940" t="inlineStr">
+        <is>
+          <t>3871305003471</t>
+        </is>
+      </c>
+      <c r="C4940" t="inlineStr">
+        <is>
+          <t>AMETISTA CARAPE</t>
+        </is>
+      </c>
+      <c r="D4940" t="n">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4940"/>
+  <dimension ref="A1:D4957"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="170">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>VEGETA 250 G</t>
+          <t>VEGETA 250G</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -6677,11 +6677,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>COKOLINO 200 G</t>
+          <t>COKOLINO 200G</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="349">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="518">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="527">
@@ -10349,11 +10349,11 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>ZLATNI PEK 630 G</t>
+          <t>ZLATNI PEK 630G</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="553">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>ZLATNI PEK 420 G</t>
+          <t>ZLATNI PEK 420G</t>
         </is>
       </c>
       <c r="D553" t="n">
@@ -11789,11 +11789,11 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>SUMI KARAMELA 74 G</t>
+          <t>SUMI KARAMELA 74G</t>
         </is>
       </c>
       <c r="D632" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="633">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>ORIGINALNA PAVLOVICEVA MAST ZA BEBE 100ML</t>
+          <t>ORIG. PAVLOV. MAST ZA BEBE 100ML</t>
         </is>
       </c>
       <c r="D822" t="n">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>LIBRESSE MAX NIGHT 2X10</t>
+          <t>LIBRESSE MAXI NIGHT 20/1</t>
         </is>
       </c>
       <c r="D1216" t="n">
@@ -22373,7 +22373,7 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>LIBRESE PROTECTION 8 KOM</t>
+          <t>LIBRESEULTRA SUPER 8/1</t>
         </is>
       </c>
       <c r="D1220" t="n">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>LIBRESE ULTRA LARGE 16 KOM</t>
+          <t>LIBRESSE ULTRA GN. DUO 16/1</t>
         </is>
       </c>
       <c r="D1224" t="n">
@@ -25271,11 +25271,11 @@
       </c>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>FANT ZA GRAH I VARIVA 60 G</t>
+          <t>FANT ZA GRAH I VARIVA 60G</t>
         </is>
       </c>
       <c r="D1381" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1382">
@@ -25451,11 +25451,11 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>SLAG KREMA VANILIJA 45G</t>
+          <t>SLAG KREMA VANILIJA 45G DOLCELA</t>
         </is>
       </c>
       <c r="D1391" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="1392">
@@ -27305,11 +27305,11 @@
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>ZDENKA CLASSIC 140 G</t>
+          <t>ZDENKA CLASSIC 35%MM 140G</t>
         </is>
       </c>
       <c r="D1494" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="1495">
@@ -28691,11 +28691,11 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>FLIPS 60G VISPAK</t>
+          <t>FLIPS 72G KIKIRIKI VISPAK</t>
         </is>
       </c>
       <c r="D1571" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="1572">
@@ -32147,11 +32147,11 @@
       </c>
       <c r="C1763" t="inlineStr">
         <is>
-          <t>ARLA DANSKI BIJELI 500 G</t>
+          <t>ARLA DANSKI BIJELI 500G</t>
         </is>
       </c>
       <c r="D1763" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="1764">
@@ -34379,7 +34379,7 @@
       </c>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>CEDEVITA NARANDZA 340 ML</t>
+          <t>CEDEVITA GO NARANDZ. 340ML</t>
         </is>
       </c>
       <c r="D1887" t="n">
@@ -37929,7 +37929,7 @@
         </is>
       </c>
       <c r="D2084" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="2085">
@@ -41957,11 +41957,11 @@
       </c>
       <c r="C2308" t="inlineStr">
         <is>
-          <t>PIVRTNA KOCKA 110G</t>
+          <t>POVRTNA KOCKA 110G VISPAK</t>
         </is>
       </c>
       <c r="D2308" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="2309">
@@ -49751,11 +49751,11 @@
       </c>
       <c r="C2741" t="inlineStr">
         <is>
-          <t>RAFAELO 150G</t>
+          <t>FERRERO RAFAELO 150G</t>
         </is>
       </c>
       <c r="D2741" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="2742">
@@ -55821,7 +55821,7 @@
         </is>
       </c>
       <c r="D3078" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3079">
@@ -57081,7 +57081,7 @@
         </is>
       </c>
       <c r="D3148" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3149">
@@ -61761,7 +61761,7 @@
         </is>
       </c>
       <c r="D3408" t="n">
-        <v>15.4</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="3409">
@@ -68075,11 +68075,11 @@
       </c>
       <c r="C3759" t="inlineStr">
         <is>
-          <t>DETERDZENT FAIRY 2X900ML</t>
+          <t>DETERDZENT FAIRY LEMON 2X900ML</t>
         </is>
       </c>
       <c r="D3759" t="n">
-        <v>11.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3760">
@@ -75891,7 +75891,7 @@
         </is>
       </c>
       <c r="D4193" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4194">
@@ -83595,7 +83595,7 @@
         </is>
       </c>
       <c r="D4621" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4622">
@@ -89338,6 +89338,312 @@
       </c>
       <c r="D4940" t="n">
         <v>3.3</v>
+      </c>
+    </row>
+    <row r="4941">
+      <c r="A4941" t="n">
+        <v>4940</v>
+      </c>
+      <c r="B4941" t="inlineStr">
+        <is>
+          <t>3871607000628</t>
+        </is>
+      </c>
+      <c r="C4941" t="inlineStr">
+        <is>
+          <t>SVINJSKA MAST 1000G</t>
+        </is>
+      </c>
+      <c r="D4941" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4942">
+      <c r="A4942" t="n">
+        <v>4941</v>
+      </c>
+      <c r="B4942" t="inlineStr">
+        <is>
+          <t>3879000017656</t>
+        </is>
+      </c>
+      <c r="C4942" t="inlineStr">
+        <is>
+          <t>SIRCE 1L 9% ALK. IMBRO</t>
+        </is>
+      </c>
+      <c r="D4942" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="4943">
+      <c r="A4943" t="n">
+        <v>4942</v>
+      </c>
+      <c r="B4943" t="inlineStr">
+        <is>
+          <t>3850120290204</t>
+        </is>
+      </c>
+      <c r="C4943" t="inlineStr">
+        <is>
+          <t>JADRO ORIGINAL 200G</t>
+        </is>
+      </c>
+      <c r="D4943" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="4944">
+      <c r="A4944" t="n">
+        <v>4943</v>
+      </c>
+      <c r="B4944" t="inlineStr">
+        <is>
+          <t>385012029520</t>
+        </is>
+      </c>
+      <c r="C4944" t="inlineStr">
+        <is>
+          <t>JADRO ORIGINAL 200G</t>
+        </is>
+      </c>
+      <c r="D4944" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="4945">
+      <c r="A4945" t="n">
+        <v>4944</v>
+      </c>
+      <c r="B4945" t="inlineStr">
+        <is>
+          <t>38503220113373</t>
+        </is>
+      </c>
+      <c r="C4945" t="inlineStr">
+        <is>
+          <t>CEDEVITA GO NARANDZ. 340ML</t>
+        </is>
+      </c>
+      <c r="D4945" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4946">
+      <c r="A4946" t="n">
+        <v>4945</v>
+      </c>
+      <c r="B4946" t="inlineStr">
+        <is>
+          <t>5996358010714</t>
+        </is>
+      </c>
+      <c r="C4946" t="inlineStr">
+        <is>
+          <t>DOMESTOS PINK FRESH 750ML</t>
+        </is>
+      </c>
+      <c r="D4946" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4947">
+      <c r="A4947" t="n">
+        <v>4946</v>
+      </c>
+      <c r="B4947" t="inlineStr">
+        <is>
+          <t>8683130078532</t>
+        </is>
+      </c>
+      <c r="C4947" t="inlineStr">
+        <is>
+          <t>DOMESTOS PINK FRESH 750ML</t>
+        </is>
+      </c>
+      <c r="D4947" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4948">
+      <c r="A4948" t="n">
+        <v>4947</v>
+      </c>
+      <c r="B4948" t="inlineStr">
+        <is>
+          <t>869063785095</t>
+        </is>
+      </c>
+      <c r="C4948" t="inlineStr">
+        <is>
+          <t>DOMESTOS PINK FRESH 750ML</t>
+        </is>
+      </c>
+      <c r="D4948" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4949">
+      <c r="A4949" t="n">
+        <v>4948</v>
+      </c>
+      <c r="B4949" t="inlineStr">
+        <is>
+          <t>5000186481018</t>
+        </is>
+      </c>
+      <c r="C4949" t="inlineStr">
+        <is>
+          <t>DOMESTOS PINE FRESH 750ML</t>
+        </is>
+      </c>
+      <c r="D4949" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4950">
+      <c r="A4950" t="n">
+        <v>4949</v>
+      </c>
+      <c r="B4950" t="inlineStr">
+        <is>
+          <t>869052101519</t>
+        </is>
+      </c>
+      <c r="C4950" t="inlineStr">
+        <is>
+          <t>DOMESTOS PINE FRESH 750ML</t>
+        </is>
+      </c>
+      <c r="D4950" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4951">
+      <c r="A4951" t="n">
+        <v>4950</v>
+      </c>
+      <c r="B4951" t="inlineStr">
+        <is>
+          <t>8005090021401</t>
+        </is>
+      </c>
+      <c r="C4951" t="inlineStr">
+        <is>
+          <t>DOPLA CASA PP 350ML 50/1</t>
+        </is>
+      </c>
+      <c r="D4951" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4952">
+      <c r="A4952" t="n">
+        <v>4951</v>
+      </c>
+      <c r="B4952" t="inlineStr">
+        <is>
+          <t>8008650023600</t>
+        </is>
+      </c>
+      <c r="C4952" t="inlineStr">
+        <is>
+          <t>DOPLA CASA PP 200CC 50/1</t>
+        </is>
+      </c>
+      <c r="D4952" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4953">
+      <c r="A4953" t="n">
+        <v>4952</v>
+      </c>
+      <c r="B4953" t="inlineStr">
+        <is>
+          <t>7622202214110</t>
+        </is>
+      </c>
+      <c r="C4953" t="inlineStr">
+        <is>
+          <t>7D MINI DOUBLE COCOA&amp;VANILLA 60GR</t>
+        </is>
+      </c>
+      <c r="D4953" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4954">
+      <c r="A4954" t="n">
+        <v>4953</v>
+      </c>
+      <c r="B4954" t="inlineStr">
+        <is>
+          <t>8606019650186</t>
+        </is>
+      </c>
+      <c r="C4954" t="inlineStr">
+        <is>
+          <t>NUTRINO LAB JAB&amp;BOR&amp;VIS 180G</t>
+        </is>
+      </c>
+      <c r="D4954" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4955">
+      <c r="A4955" t="n">
+        <v>4954</v>
+      </c>
+      <c r="B4955" t="inlineStr">
+        <is>
+          <t>8606019650209</t>
+        </is>
+      </c>
+      <c r="C4955" t="inlineStr">
+        <is>
+          <t>NUTRINO LAB POWER MIX 180G</t>
+        </is>
+      </c>
+      <c r="D4955" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4956">
+      <c r="A4956" t="n">
+        <v>4955</v>
+      </c>
+      <c r="B4956" t="inlineStr">
+        <is>
+          <t>46085351</t>
+        </is>
+      </c>
+      <c r="C4956" t="inlineStr">
+        <is>
+          <t>SOBRANIE GOLD KS</t>
+        </is>
+      </c>
+      <c r="D4956" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="4957">
+      <c r="A4957" t="n">
+        <v>4956</v>
+      </c>
+      <c r="B4957" t="inlineStr">
+        <is>
+          <t>3838700540741</t>
+        </is>
+      </c>
+      <c r="C4957" t="inlineStr">
+        <is>
+          <t>ZP GRIS BEBE PS PLAVI 450G</t>
+        </is>
+      </c>
+      <c r="D4957" t="n">
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4957"/>
+  <dimension ref="A1:D4959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>COCA-COLA 0,5 L</t>
+          <t>COCA-COLA 0,5L</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -14061,7 +14061,7 @@
         </is>
       </c>
       <c r="D758" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="759">
@@ -25523,7 +25523,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>BIO NACIN 1000 G</t>
+          <t>BIO NACIN 1000G</t>
         </is>
       </c>
       <c r="D1395" t="n">
@@ -25541,11 +25541,11 @@
       </c>
       <c r="C1396" t="inlineStr">
         <is>
-          <t>BIO NACIN 500 G</t>
+          <t>BIO NACIN 500G</t>
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="1397">
@@ -26931,7 +26931,7 @@
         </is>
       </c>
       <c r="D1473" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="1474">
@@ -30329,11 +30329,11 @@
       </c>
       <c r="C1662" t="inlineStr">
         <is>
-          <t>VODA ROSA 0,5 L</t>
+          <t>VODA ROSA 0,5L</t>
         </is>
       </c>
       <c r="D1662" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1663">
@@ -32061,7 +32061,7 @@
         </is>
       </c>
       <c r="D1758" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="1759">
@@ -33339,7 +33339,7 @@
         </is>
       </c>
       <c r="D1829" t="n">
-        <v>5.2</v>
+        <v>5.100000000000001</v>
       </c>
     </row>
     <row r="1830">
@@ -86547,7 +86547,7 @@
         </is>
       </c>
       <c r="D4785" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4786">
@@ -89644,6 +89644,42 @@
       </c>
       <c r="D4957" t="n">
         <v>2.8</v>
+      </c>
+    </row>
+    <row r="4958">
+      <c r="A4958" t="n">
+        <v>4957</v>
+      </c>
+      <c r="B4958" t="inlineStr">
+        <is>
+          <t>8606106174274</t>
+        </is>
+      </c>
+      <c r="C4958" t="inlineStr">
+        <is>
+          <t>SOMERSBY JABUKA 0,33L</t>
+        </is>
+      </c>
+      <c r="D4958" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4959">
+      <c r="A4959" t="n">
+        <v>4958</v>
+      </c>
+      <c r="B4959" t="inlineStr">
+        <is>
+          <t>8600331002128</t>
+        </is>
+      </c>
+      <c r="C4959" t="inlineStr">
+        <is>
+          <t>SOMERSBY JAGODA 0.33L 0.0% ALK.</t>
+        </is>
+      </c>
+      <c r="D4959" t="n">
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4959"/>
+  <dimension ref="A1:D4960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56127,7 +56127,7 @@
         </is>
       </c>
       <c r="D3095" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3096">
@@ -56145,7 +56145,7 @@
         </is>
       </c>
       <c r="D3096" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3097">
@@ -56163,7 +56163,7 @@
         </is>
       </c>
       <c r="D3097" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3098">
@@ -89680,6 +89680,24 @@
       </c>
       <c r="D4959" t="n">
         <v>2.2</v>
+      </c>
+    </row>
+    <row r="4960">
+      <c r="A4960" t="n">
+        <v>4959</v>
+      </c>
+      <c r="B4960" t="inlineStr">
+        <is>
+          <t>8610056035332</t>
+        </is>
+      </c>
+      <c r="C4960" t="inlineStr">
+        <is>
+          <t>KORPA ZA HLJEB</t>
+        </is>
+      </c>
+      <c r="D4960" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -89031,7 +89031,7 @@
         </is>
       </c>
       <c r="D4923" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4924">
@@ -89049,7 +89049,7 @@
         </is>
       </c>
       <c r="D4924" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4925">
@@ -89067,7 +89067,7 @@
         </is>
       </c>
       <c r="D4925" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4926">

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4960"/>
+  <dimension ref="A1:D4967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="103">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>JUHA GOVEDJA 65G</t>
+          <t>JUHA GOVEDJA 65G PODRAVKA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>JUHA KOKOSIJA 62G</t>
+          <t>JUHA KOKOSIJA 62G PODRAVKA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TIROLSKA JUHA</t>
+          <t>TIROLSKA JUHA 67G PODRAVKA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>PISKOTE 210 G</t>
+          <t>PISKOTE 210G STARK</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -5975,11 +5975,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>VEGETA 250G</t>
+          <t>VEGETA 250G PODRAVKA</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="310">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>PRASAK ZA PECIVO 5/1</t>
+          <t>PRASAK ZA PECIVO 5/1 DOLCELA</t>
         </is>
       </c>
       <c r="D310" t="n">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>MANCHMALLOW 105 G</t>
+          <t>MANCHMALLOW 105G</t>
         </is>
       </c>
       <c r="D407" t="n">
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="410">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="448">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>4.8</v>
+        <v>4.899999999999999</v>
       </c>
     </row>
     <row r="511">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>COKO BANANA</t>
+          <t>SWISSLION CHOCO BANANA 18G</t>
         </is>
       </c>
       <c r="D605" t="n">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>CHIPSY PAPRIKA 25 G</t>
+          <t>CHIPSY PAPRIKA 25G</t>
         </is>
       </c>
       <c r="D648" t="n">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>CHIPSY CLASSIC 140 G</t>
+          <t>CHIPSY CLASSIC 140G</t>
         </is>
       </c>
       <c r="D661" t="n">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>KVIKI GRIC SLANI 100 G</t>
+          <t>KVIKI GRIC SLANI 100G</t>
         </is>
       </c>
       <c r="D689" t="n">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="D700" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="701">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>PARDON STAPICI 40 G</t>
+          <t>PARDON STAPICI 40G</t>
         </is>
       </c>
       <c r="D759" t="n">
@@ -20789,7 +20789,7 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>CHIPSY SLANI 27 G</t>
+          <t>CHIPSY SLANI 25G</t>
         </is>
       </c>
       <c r="D1132" t="n">
@@ -22373,7 +22373,7 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>LIBRESEULTRA SUPER 8/1</t>
+          <t>LIBRESE ULTRA SUPER 8/1</t>
         </is>
       </c>
       <c r="D1220" t="n">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>CHIPSY REBRASTI CILI 27G</t>
+          <t>CHIPSY REBRASTI CILI 25G</t>
         </is>
       </c>
       <c r="D1280" t="n">
@@ -24425,11 +24425,11 @@
       </c>
       <c r="C1334" t="inlineStr">
         <is>
-          <t>ARGETA PIKANT 95 G</t>
+          <t>ARGETA PIKANT 95G</t>
         </is>
       </c>
       <c r="D1334" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1335">
@@ -24771,7 +24771,7 @@
         </is>
       </c>
       <c r="D1353" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="1354">
@@ -24933,7 +24933,7 @@
         </is>
       </c>
       <c r="D1362" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="1363">
@@ -25109,7 +25109,7 @@
       </c>
       <c r="C1372" t="inlineStr">
         <is>
-          <t>SVATOVSKA JUHA 58 G</t>
+          <t>SVATOVSKA JUHA 58G PODRAVKA</t>
         </is>
       </c>
       <c r="D1372" t="n">
@@ -25307,11 +25307,11 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>FANT ZA CEVAPCICE I PLJESKAVICE 40 G</t>
+          <t>FANT ZA CEVAP I PLJESK. 40G PODR.</t>
         </is>
       </c>
       <c r="D1383" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1384">
@@ -25829,11 +25829,11 @@
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>LINO LADA 500 G</t>
+          <t>LINO LADA 500G PODRAVKA</t>
         </is>
       </c>
       <c r="D1412" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="1413">
@@ -25883,11 +25883,11 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>EUROKREM TAKOVO 80 G</t>
+          <t>EUROKREM 80G TAKOVO</t>
         </is>
       </c>
       <c r="D1415" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1416">
@@ -27309,7 +27309,7 @@
         </is>
       </c>
       <c r="D1494" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="1495">
@@ -27683,7 +27683,7 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>ARGETA TUNA 95 G</t>
+          <t>ARGETA TUNA 95G</t>
         </is>
       </c>
       <c r="D1515" t="n">
@@ -31323,7 +31323,7 @@
         </is>
       </c>
       <c r="D1717" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="1718">
@@ -31341,7 +31341,7 @@
         </is>
       </c>
       <c r="D1718" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1719">
@@ -31517,11 +31517,11 @@
       </c>
       <c r="C1728" t="inlineStr">
         <is>
-          <t>DVOJNI C 1 L</t>
+          <t>DVOJNI C 1L</t>
         </is>
       </c>
       <c r="D1728" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1729">
@@ -31535,7 +31535,7 @@
       </c>
       <c r="C1729" t="inlineStr">
         <is>
-          <t>FRUKTAL BOROVNICA 1 L</t>
+          <t>FRUKTAL BOROVNICA 1L</t>
         </is>
       </c>
       <c r="D1729" t="n">
@@ -31773,7 +31773,7 @@
         </is>
       </c>
       <c r="D1742" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1743">
@@ -32367,7 +32367,7 @@
         </is>
       </c>
       <c r="D1775" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="1776">
@@ -32381,7 +32381,7 @@
       </c>
       <c r="C1776" t="inlineStr">
         <is>
-          <t>GREKOS 150 G</t>
+          <t>GREKOS 150G</t>
         </is>
       </c>
       <c r="D1776" t="n">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="C1794" t="inlineStr">
         <is>
-          <t>GRASAK VEGI 400 G</t>
+          <t>GRASAK VEGI 400G</t>
         </is>
       </c>
       <c r="D1794" t="n">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="C1797" t="inlineStr">
         <is>
-          <t>VEGI MAHUNA ZUTA 400 G</t>
+          <t>VEGI MAHUNA ZUTA 400G</t>
         </is>
       </c>
       <c r="D1797" t="n">
@@ -38267,11 +38267,11 @@
       </c>
       <c r="C2103" t="inlineStr">
         <is>
-          <t>BANANKO 30G</t>
+          <t>KRAS BANANKO 30G</t>
         </is>
       </c>
       <c r="D2103" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="2104">
@@ -39423,7 +39423,7 @@
         </is>
       </c>
       <c r="D2167" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="2168">
@@ -40337,7 +40337,7 @@
       </c>
       <c r="C2218" t="inlineStr">
         <is>
-          <t>CHIPSY REBRASTI KETCHUP 95G</t>
+          <t>CHIPSY REBRASTI KECAP 95G</t>
         </is>
       </c>
       <c r="D2218" t="n">
@@ -42771,7 +42771,7 @@
         </is>
       </c>
       <c r="D2353" t="n">
-        <v>4.3</v>
+        <v>4.399999999999999</v>
       </c>
     </row>
     <row r="2354">
@@ -44301,7 +44301,7 @@
         </is>
       </c>
       <c r="D2438" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="2439">
@@ -44319,7 +44319,7 @@
         </is>
       </c>
       <c r="D2439" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2440">
@@ -44787,7 +44787,7 @@
         </is>
       </c>
       <c r="D2465" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="2466">
@@ -45561,7 +45561,7 @@
         </is>
       </c>
       <c r="D2508" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="2509">
@@ -48999,7 +48999,7 @@
         </is>
       </c>
       <c r="D2699" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="2700">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="C2723" t="inlineStr">
         <is>
-          <t>CLIPSY CHICKEN DRUMS MAX 30G</t>
+          <t>CLIPSY MAX PILETINA 30G</t>
         </is>
       </c>
       <c r="D2723" t="n">
@@ -50903,7 +50903,7 @@
       </c>
       <c r="C2805" t="inlineStr">
         <is>
-          <t>CLIPSY PEANUT 50G</t>
+          <t>CLIPSY KIKIRIKI 50G</t>
         </is>
       </c>
       <c r="D2805" t="n">
@@ -52887,7 +52887,7 @@
         </is>
       </c>
       <c r="D2915" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="2916">
@@ -52977,7 +52977,7 @@
         </is>
       </c>
       <c r="D2920" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="2921">
@@ -56195,7 +56195,7 @@
       </c>
       <c r="C3099" t="inlineStr">
         <is>
-          <t>PLAZMA CREAM KORNET</t>
+          <t>PLAZMA CREAM KORNET 120ML</t>
         </is>
       </c>
       <c r="D3099" t="n">
@@ -56267,7 +56267,7 @@
       </c>
       <c r="C3103" t="inlineStr">
         <is>
-          <t>MACHO BANANA CRUNCH STAPIC</t>
+          <t>MACHO BANANA CRUNCH STAPIC 75ML</t>
         </is>
       </c>
       <c r="D3103" t="n">
@@ -56861,7 +56861,7 @@
       </c>
       <c r="C3136" t="inlineStr">
         <is>
-          <t>ALPSKA JUHA 64G</t>
+          <t>ALPSKA JUHA 64G PODRAVKA</t>
         </is>
       </c>
       <c r="D3136" t="n">
@@ -57005,7 +57005,7 @@
       </c>
       <c r="C3144" t="inlineStr">
         <is>
-          <t>KONC.RAJCICE TUBA 120G</t>
+          <t>KONC.RAJCICE TUBA 120G PODRAVKA</t>
         </is>
       </c>
       <c r="D3144" t="n">
@@ -58989,7 +58989,7 @@
         </is>
       </c>
       <c r="D3254" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="3255">
@@ -59043,7 +59043,7 @@
         </is>
       </c>
       <c r="D3257" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3258">
@@ -60663,7 +60663,7 @@
         </is>
       </c>
       <c r="D3347" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3348">
@@ -60681,7 +60681,7 @@
         </is>
       </c>
       <c r="D3348" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3349">
@@ -60713,7 +60713,7 @@
       </c>
       <c r="C3350" t="inlineStr">
         <is>
-          <t>VINO CRNO VRANAC PLA1L</t>
+          <t>VINO CRNO VRANAC PLA 1L</t>
         </is>
       </c>
       <c r="D3350" t="n">
@@ -65667,7 +65667,7 @@
         </is>
       </c>
       <c r="D3625" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3626">
@@ -77835,7 +77835,7 @@
         </is>
       </c>
       <c r="D4301" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4302">
@@ -78735,7 +78735,7 @@
         </is>
       </c>
       <c r="D4351" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="4352">
@@ -86543,7 +86543,7 @@
       </c>
       <c r="C4785" t="inlineStr">
         <is>
-          <t>DEUL ADRIATIC SENSE 1,6L</t>
+          <t>DUEL ADRIATIC SENSE 1,6L</t>
         </is>
       </c>
       <c r="D4785" t="n">
@@ -89698,6 +89698,132 @@
       </c>
       <c r="D4960" t="n">
         <v>2.5</v>
+      </c>
+    </row>
+    <row r="4961">
+      <c r="A4961" t="n">
+        <v>4960</v>
+      </c>
+      <c r="B4961" t="inlineStr">
+        <is>
+          <t>3871262004416</t>
+        </is>
+      </c>
+      <c r="C4961" t="inlineStr">
+        <is>
+          <t>TREND ZEL. MASLINE OTKOS. 720G</t>
+        </is>
+      </c>
+      <c r="D4961" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="4962">
+      <c r="A4962" t="n">
+        <v>4961</v>
+      </c>
+      <c r="B4962" t="inlineStr">
+        <is>
+          <t>86019095</t>
+        </is>
+      </c>
+      <c r="C4962" t="inlineStr">
+        <is>
+          <t>EUROKREM 50G TAKOVO</t>
+        </is>
+      </c>
+      <c r="D4962" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4963">
+      <c r="A4963" t="n">
+        <v>4962</v>
+      </c>
+      <c r="B4963" t="inlineStr">
+        <is>
+          <t>7622202273452</t>
+        </is>
+      </c>
+      <c r="C4963" t="inlineStr">
+        <is>
+          <t>MILKA ALPSKO MLIJEKO 90G</t>
+        </is>
+      </c>
+      <c r="D4963" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4964">
+      <c r="A4964" t="n">
+        <v>4963</v>
+      </c>
+      <c r="B4964" t="inlineStr">
+        <is>
+          <t>8600939344088</t>
+        </is>
+      </c>
+      <c r="C4964" t="inlineStr">
+        <is>
+          <t>NAJLJEPSE ZELJE KEKS 250G</t>
+        </is>
+      </c>
+      <c r="D4964" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="4965">
+      <c r="A4965" t="n">
+        <v>4964</v>
+      </c>
+      <c r="B4965" t="inlineStr">
+        <is>
+          <t>3871862004430</t>
+        </is>
+      </c>
+      <c r="C4965" t="inlineStr">
+        <is>
+          <t>TREND MASLINE CRNE OTKOSTENE 720ML</t>
+        </is>
+      </c>
+      <c r="D4965" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="4966">
+      <c r="A4966" t="n">
+        <v>4965</v>
+      </c>
+      <c r="B4966" t="inlineStr">
+        <is>
+          <t>8600114011248</t>
+        </is>
+      </c>
+      <c r="C4966" t="inlineStr">
+        <is>
+          <t>JAFFA CHOCO ORANGE 160G</t>
+        </is>
+      </c>
+      <c r="D4966" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4967">
+      <c r="A4967" t="n">
+        <v>4966</v>
+      </c>
+      <c r="B4967" t="inlineStr">
+        <is>
+          <t>3850116677477</t>
+        </is>
+      </c>
+      <c r="C4967" t="inlineStr">
+        <is>
+          <t>SMRZNUTI POMFRIT 1KG LEDO</t>
+        </is>
+      </c>
+      <c r="D4967" t="n">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4967"/>
+  <dimension ref="A1:D4972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77583,7 +77583,7 @@
         </is>
       </c>
       <c r="D4287" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4288">
@@ -89824,6 +89824,96 @@
       </c>
       <c r="D4967" t="n">
         <v>6.8</v>
+      </c>
+    </row>
+    <row r="4968">
+      <c r="A4968" t="n">
+        <v>4967</v>
+      </c>
+      <c r="B4968" t="inlineStr">
+        <is>
+          <t>3875001978125</t>
+        </is>
+      </c>
+      <c r="C4968" t="inlineStr">
+        <is>
+          <t>SELOTEJP TRAKA 4.5CM</t>
+        </is>
+      </c>
+      <c r="D4968" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4969">
+      <c r="A4969" t="n">
+        <v>4968</v>
+      </c>
+      <c r="B4969" t="inlineStr">
+        <is>
+          <t>3875001471657</t>
+        </is>
+      </c>
+      <c r="C4969" t="inlineStr">
+        <is>
+          <t>UNO KARTE</t>
+        </is>
+      </c>
+      <c r="D4969" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4970">
+      <c r="A4970" t="n">
+        <v>4969</v>
+      </c>
+      <c r="B4970" t="inlineStr">
+        <is>
+          <t>3875001971263</t>
+        </is>
+      </c>
+      <c r="C4970" t="inlineStr">
+        <is>
+          <t>MUHOLOVKA</t>
+        </is>
+      </c>
+      <c r="D4970" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4971">
+      <c r="A4971" t="n">
+        <v>4970</v>
+      </c>
+      <c r="B4971" t="inlineStr">
+        <is>
+          <t>2345630642670</t>
+        </is>
+      </c>
+      <c r="C4971" t="inlineStr">
+        <is>
+          <t>STAKLENE CASE 6/1 430CC</t>
+        </is>
+      </c>
+      <c r="D4971" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="4972">
+      <c r="A4972" t="n">
+        <v>4971</v>
+      </c>
+      <c r="B4972" t="inlineStr">
+        <is>
+          <t>8606108887134</t>
+        </is>
+      </c>
+      <c r="C4972" t="inlineStr">
+        <is>
+          <t>CESTITKA NELA</t>
+        </is>
+      </c>
+      <c r="D4972" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4972"/>
+  <dimension ref="A1:D4975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89916,6 +89916,60 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4973">
+      <c r="A4973" t="n">
+        <v>4972</v>
+      </c>
+      <c r="B4973" t="inlineStr">
+        <is>
+          <t>3850116042350</t>
+        </is>
+      </c>
+      <c r="C4973" t="inlineStr">
+        <is>
+          <t>MACHO MIXBOX 6X75ML 450ML LEDO</t>
+        </is>
+      </c>
+      <c r="D4973" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4974">
+      <c r="A4974" t="n">
+        <v>4973</v>
+      </c>
+      <c r="B4974" t="inlineStr">
+        <is>
+          <t>3870398916583</t>
+        </is>
+      </c>
+      <c r="C4974" t="inlineStr">
+        <is>
+          <t>KAPRI STAPIC MIXBOX LEDO</t>
+        </is>
+      </c>
+      <c r="D4974" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4975">
+      <c r="A4975" t="n">
+        <v>4974</v>
+      </c>
+      <c r="B4975" t="inlineStr">
+        <is>
+          <t>3850116035543</t>
+        </is>
+      </c>
+      <c r="C4975" t="inlineStr">
+        <is>
+          <t>VANILIJA BOURBON 2L LEDO</t>
+        </is>
+      </c>
+      <c r="D4975" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4975"/>
+  <dimension ref="A1:D4976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89970,6 +89970,24 @@
         <v>10.9</v>
       </c>
     </row>
+    <row r="4976">
+      <c r="A4976" t="n">
+        <v>4975</v>
+      </c>
+      <c r="B4976" t="inlineStr">
+        <is>
+          <t>8606016593462</t>
+        </is>
+      </c>
+      <c r="C4976" t="inlineStr">
+        <is>
+          <t>BOHOR CLASSIC 3000ML</t>
+        </is>
+      </c>
+      <c r="D4976" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4976"/>
+  <dimension ref="A1:D4977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89988,6 +89988,24 @@
         <v>10.5</v>
       </c>
     </row>
+    <row r="4977">
+      <c r="A4977" t="n">
+        <v>4976</v>
+      </c>
+      <c r="B4977" t="inlineStr">
+        <is>
+          <t>8606016593448</t>
+        </is>
+      </c>
+      <c r="C4977" t="inlineStr">
+        <is>
+          <t>BOHOR AZURE 3000ML</t>
+        </is>
+      </c>
+      <c r="D4977" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4977"/>
+  <dimension ref="A1:D4985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="131">
@@ -17747,11 +17747,11 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>KOSILI MARAMICE 70</t>
+          <t>KOSILI MARAMICE PLAVE 70/1</t>
         </is>
       </c>
       <c r="D963" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="964">
@@ -17765,11 +17765,11 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>KOSILI I MARAMICE 70</t>
+          <t>KOSILI I MARAMICE ROZE 70/1</t>
         </is>
       </c>
       <c r="D964" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="965">
@@ -20901,7 +20901,7 @@
         </is>
       </c>
       <c r="D1138" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1139">
@@ -48455,7 +48455,7 @@
       </c>
       <c r="C2669" t="inlineStr">
         <is>
-          <t>ROSHEN MILK CHOC. BAR KIKIRIKI PUNJ. 38G</t>
+          <t>ROSHEN MILK CHOC. BAR KIKIRIKI 38G</t>
         </is>
       </c>
       <c r="D2669" t="n">
@@ -64515,7 +64515,7 @@
         </is>
       </c>
       <c r="D3561" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3562">
@@ -70743,7 +70743,7 @@
         </is>
       </c>
       <c r="D3907" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3908">
@@ -71175,7 +71175,7 @@
         </is>
       </c>
       <c r="D3931" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3932">
@@ -72543,7 +72543,7 @@
         </is>
       </c>
       <c r="D4007" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4008">
@@ -90004,6 +90004,150 @@
       </c>
       <c r="D4977" t="n">
         <v>10.5</v>
+      </c>
+    </row>
+    <row r="4978">
+      <c r="A4978" t="n">
+        <v>4977</v>
+      </c>
+      <c r="B4978" t="inlineStr">
+        <is>
+          <t>3830073000495</t>
+        </is>
+      </c>
+      <c r="C4978" t="inlineStr">
+        <is>
+          <t>IL CAP. HR. ZA MACKE ZIV&amp;DZIG 80G</t>
+        </is>
+      </c>
+      <c r="D4978" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4979">
+      <c r="A4979" t="n">
+        <v>4978</v>
+      </c>
+      <c r="B4979" t="inlineStr">
+        <is>
+          <t>3830073000518</t>
+        </is>
+      </c>
+      <c r="C4979" t="inlineStr">
+        <is>
+          <t>IL CAP. HR. ZA MACKE GOVEDINA 80G</t>
+        </is>
+      </c>
+      <c r="D4979" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4980">
+      <c r="A4980" t="n">
+        <v>4979</v>
+      </c>
+      <c r="B4980" t="inlineStr">
+        <is>
+          <t>4006795866155</t>
+        </is>
+      </c>
+      <c r="C4980" t="inlineStr">
+        <is>
+          <t>LA PERLA SARDINA U PAR. SOSU 125G</t>
+        </is>
+      </c>
+      <c r="D4980" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4981">
+      <c r="A4981" t="n">
+        <v>4980</v>
+      </c>
+      <c r="B4981" t="inlineStr">
+        <is>
+          <t>8606012140615</t>
+        </is>
+      </c>
+      <c r="C4981" t="inlineStr">
+        <is>
+          <t>LMX APARAT I TABL. PROT. INSEKATA</t>
+        </is>
+      </c>
+      <c r="D4981" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="4982">
+      <c r="A4982" t="n">
+        <v>4981</v>
+      </c>
+      <c r="B4982" t="inlineStr">
+        <is>
+          <t>8606012143340</t>
+        </is>
+      </c>
+      <c r="C4982" t="inlineStr">
+        <is>
+          <t>KOSILI BABY KREMA PLAVA 200ML</t>
+        </is>
+      </c>
+      <c r="D4982" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="4983">
+      <c r="A4983" t="n">
+        <v>4982</v>
+      </c>
+      <c r="B4983" t="inlineStr">
+        <is>
+          <t>8606012143326</t>
+        </is>
+      </c>
+      <c r="C4983" t="inlineStr">
+        <is>
+          <t>KOSILI BABY KREMA PLAVA 100ML</t>
+        </is>
+      </c>
+      <c r="D4983" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4984">
+      <c r="A4984" t="n">
+        <v>4983</v>
+      </c>
+      <c r="B4984" t="inlineStr">
+        <is>
+          <t>4904530108143</t>
+        </is>
+      </c>
+      <c r="C4984" t="inlineStr">
+        <is>
+          <t>TOSHIBA LITIJUM BATERIJA CR2032</t>
+        </is>
+      </c>
+      <c r="D4984" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4985">
+      <c r="A4985" t="n">
+        <v>4984</v>
+      </c>
+      <c r="B4985" t="inlineStr">
+        <is>
+          <t>8606012140592</t>
+        </is>
+      </c>
+      <c r="C4985" t="inlineStr">
+        <is>
+          <t>LMX TABLETE PROTIV KOMARACA EUKAL.</t>
+        </is>
+      </c>
+      <c r="D4985" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4985"/>
+  <dimension ref="A1:D5048"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HELENA SKIDAC LAKA ULJNI LAVANDA 100ML</t>
+          <t>HELENA SK. LAKA ULJNI LAVA. 100ML</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="141">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>HRANA EURODOG 1240GR</t>
+          <t>HRANA EURODOG GOVEDINA 1240GR</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>KINDER JOY 20 G</t>
+          <t>KINDER JOY 20G</t>
         </is>
       </c>
       <c r="D653" t="n">
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="D668" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="669">
@@ -15299,11 +15299,11 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>SODA BIKARBONA 500 G FRUKTA</t>
+          <t>SODA BIKARBONA 500G FRUKTA</t>
         </is>
       </c>
       <c r="D827" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="828">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>KREM ZA KUVANJE POLIMARK 200 G</t>
+          <t>KREM ZA KUVANJE 200ML POLIMARK</t>
         </is>
       </c>
       <c r="D846" t="n">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>KREM ZA KUVANJE POLIMARK 500 G</t>
+          <t>KREM ZA KUVANJE 500ML POLIMARK</t>
         </is>
       </c>
       <c r="D847" t="n">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>NIVEA ROLL-ON</t>
+          <t>NIVEA ROLL-ON MEN COOL KICK 50ML</t>
         </is>
       </c>
       <c r="D991" t="n">
@@ -21221,11 +21221,11 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>PALMOLIVE SAPUN</t>
+          <t>PALMOLIVE SAPUN 90G KAMIL&amp;VITAMIN</t>
         </is>
       </c>
       <c r="D1156" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1157">
@@ -25775,11 +25775,11 @@
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>NUTELLA 750 G</t>
+          <t>NUTELLA 750G</t>
         </is>
       </c>
       <c r="D1409" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="1410">
@@ -26963,7 +26963,7 @@
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>POLIMARK KECAP PIZZA 500 G</t>
+          <t>POLIMARK KECAP PIZZA 500G</t>
         </is>
       </c>
       <c r="D1475" t="n">
@@ -30351,7 +30351,7 @@
         </is>
       </c>
       <c r="D1663" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1664">
@@ -31233,7 +31233,7 @@
         </is>
       </c>
       <c r="D1712" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="1713">
@@ -38829,7 +38829,7 @@
         </is>
       </c>
       <c r="D2134" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="2135">
@@ -39113,7 +39113,7 @@
       </c>
       <c r="C2150" t="inlineStr">
         <is>
-          <t>JANA 0,50L</t>
+          <t>JANA 0,5L</t>
         </is>
       </c>
       <c r="D2150" t="n">
@@ -39185,7 +39185,7 @@
       </c>
       <c r="C2154" t="inlineStr">
         <is>
-          <t>JANA LEDENI CAJ BRESKVA 0,50L</t>
+          <t>JANA LEDENI CAJ BRESKVA 005L</t>
         </is>
       </c>
       <c r="D2154" t="n">
@@ -39689,7 +39689,7 @@
       </c>
       <c r="C2182" t="inlineStr">
         <is>
-          <t>MILKA WHOLE HAZELNUTS</t>
+          <t>MILKA WHOLE HAZELNUTS 250G</t>
         </is>
       </c>
       <c r="D2182" t="n">
@@ -40895,7 +40895,7 @@
       </c>
       <c r="C2249" t="inlineStr">
         <is>
-          <t>JANA VITAMIN LIMUN 0,5</t>
+          <t>JANA VITAMIN LIMUN 0,5L</t>
         </is>
       </c>
       <c r="D2249" t="n">
@@ -42947,7 +42947,7 @@
       </c>
       <c r="C2363" t="inlineStr">
         <is>
-          <t>VARTA AA</t>
+          <t>VARTA AA 1.5V</t>
         </is>
       </c>
       <c r="D2363" t="n">
@@ -45471,7 +45471,7 @@
         </is>
       </c>
       <c r="D2503" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="2504">
@@ -51353,7 +51353,7 @@
       </c>
       <c r="C2830" t="inlineStr">
         <is>
-          <t>JANA IMUNO LIMUN 1.5l</t>
+          <t>JANA IMUNO LIMUN 1,5L</t>
         </is>
       </c>
       <c r="D2830" t="n">
@@ -57293,11 +57293,11 @@
       </c>
       <c r="C3160" t="inlineStr">
         <is>
-          <t>OLD SPICE RICH SCENT 50ML</t>
+          <t>OLD SPICE ROLL-ON ORIGINAL 50ML</t>
         </is>
       </c>
       <c r="D3160" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3161">
@@ -58949,7 +58949,7 @@
       </c>
       <c r="C3252" t="inlineStr">
         <is>
-          <t>JANA VITAMIN ORANGE 500ML</t>
+          <t>JANA VITAMIN ORANGE 0,5L</t>
         </is>
       </c>
       <c r="D3252" t="n">
@@ -60951,7 +60951,7 @@
         </is>
       </c>
       <c r="D3363" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3364">
@@ -63899,7 +63899,7 @@
       </c>
       <c r="C3527" t="inlineStr">
         <is>
-          <t>LEDENI CAJ 0.5K SUM.VO.BRUS.</t>
+          <t>LEDENI CAJ SUM.V.&amp;BRUS. 0.5L</t>
         </is>
       </c>
       <c r="D3527" t="n">
@@ -64817,7 +64817,7 @@
       </c>
       <c r="C3578" t="inlineStr">
         <is>
-          <t>JANA VITAMIN MENTA LIMENA 0,5</t>
+          <t>JANA VITAMIN MENTA LIMENA 0,5L</t>
         </is>
       </c>
       <c r="D3578" t="n">
@@ -65915,7 +65915,7 @@
       </c>
       <c r="C3639" t="inlineStr">
         <is>
-          <t>KINDER JAJE 20G</t>
+          <t>KINDER JOY 20G</t>
         </is>
       </c>
       <c r="D3639" t="n">
@@ -71315,7 +71315,7 @@
       </c>
       <c r="C3939" t="inlineStr">
         <is>
-          <t>PALMOLIVE SAPUN 90G NOURISHING</t>
+          <t>PALMOLIVE SAPUN 90G ROSE</t>
         </is>
       </c>
       <c r="D3939" t="n">
@@ -81561,7 +81561,7 @@
         </is>
       </c>
       <c r="D4508" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4509">
@@ -87209,7 +87209,7 @@
       </c>
       <c r="C4822" t="inlineStr">
         <is>
-          <t>PALMOLIVE SAPUN KAMILICA 90G</t>
+          <t>PALMOLIVE SAPUN 90G KAMIL&amp;VITAMIN</t>
         </is>
       </c>
       <c r="D4822" t="n">
@@ -89967,7 +89967,7 @@
         </is>
       </c>
       <c r="D4975" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="4976">
@@ -90057,7 +90057,7 @@
         </is>
       </c>
       <c r="D4980" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4981">
@@ -90148,6 +90148,1140 @@
       </c>
       <c r="D4985" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="4986">
+      <c r="A4986" t="n">
+        <v>4985</v>
+      </c>
+      <c r="B4986" t="inlineStr">
+        <is>
+          <t>8606100389018</t>
+        </is>
+      </c>
+      <c r="C4986" t="inlineStr">
+        <is>
+          <t>JABUKOVO SIRCE 1L</t>
+        </is>
+      </c>
+      <c r="D4986" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="4987">
+      <c r="A4987" t="n">
+        <v>4986</v>
+      </c>
+      <c r="B4987" t="inlineStr">
+        <is>
+          <t>3872607000571</t>
+        </is>
+      </c>
+      <c r="C4987" t="inlineStr">
+        <is>
+          <t>RAKIJA LOZA KOSAC 0,10L</t>
+        </is>
+      </c>
+      <c r="D4987" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4988">
+      <c r="A4988" t="n">
+        <v>4987</v>
+      </c>
+      <c r="B4988" t="inlineStr">
+        <is>
+          <t>87316667</t>
+        </is>
+      </c>
+      <c r="C4988" t="inlineStr">
+        <is>
+          <t>BAVARIA BEZALKOHOLNO 0,25L</t>
+        </is>
+      </c>
+      <c r="D4988" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="4989">
+      <c r="A4989" t="n">
+        <v>4988</v>
+      </c>
+      <c r="B4989" t="inlineStr">
+        <is>
+          <t>8681554633252</t>
+        </is>
+      </c>
+      <c r="C4989" t="inlineStr">
+        <is>
+          <t>FAIRY VL. MAR. ZA MOP 50/1 LIMUN</t>
+        </is>
+      </c>
+      <c r="D4989" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="4990">
+      <c r="A4990" t="n">
+        <v>4989</v>
+      </c>
+      <c r="B4990" t="inlineStr">
+        <is>
+          <t>8681554633221</t>
+        </is>
+      </c>
+      <c r="C4990" t="inlineStr">
+        <is>
+          <t>FAIRY VL. MAR. ZA MOP 50/1 WHITE</t>
+        </is>
+      </c>
+      <c r="D4990" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="4991">
+      <c r="A4991" t="n">
+        <v>4990</v>
+      </c>
+      <c r="B4991" t="inlineStr">
+        <is>
+          <t>8999777004552</t>
+        </is>
+      </c>
+      <c r="C4991" t="inlineStr">
+        <is>
+          <t>NIVEA ROLL-ON BLACK &amp; WHITE 50ML</t>
+        </is>
+      </c>
+      <c r="D4991" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="4992">
+      <c r="A4992" t="n">
+        <v>4991</v>
+      </c>
+      <c r="B4992" t="inlineStr">
+        <is>
+          <t>8006540796269</t>
+        </is>
+      </c>
+      <c r="C4992" t="inlineStr">
+        <is>
+          <t>OLD SPICE DEO ORIGINAL 150ML</t>
+        </is>
+      </c>
+      <c r="D4992" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4993">
+      <c r="A4993" t="n">
+        <v>4992</v>
+      </c>
+      <c r="B4993" t="inlineStr">
+        <is>
+          <t>8602300205424</t>
+        </is>
+      </c>
+      <c r="C4993" t="inlineStr">
+        <is>
+          <t>PIONIR MONY RIZA 150G</t>
+        </is>
+      </c>
+      <c r="D4993" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4994">
+      <c r="A4994" t="n">
+        <v>4993</v>
+      </c>
+      <c r="B4994" t="inlineStr">
+        <is>
+          <t>3870379096525</t>
+        </is>
+      </c>
+      <c r="C4994" t="inlineStr">
+        <is>
+          <t>MAJONEZ TOMICO DELI. 285NL</t>
+        </is>
+      </c>
+      <c r="D4994" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="4995">
+      <c r="A4995" t="n">
+        <v>4994</v>
+      </c>
+      <c r="B4995" t="inlineStr">
+        <is>
+          <t>4005900640741</t>
+        </is>
+      </c>
+      <c r="C4995" t="inlineStr">
+        <is>
+          <t>NIVEA ROLL-ON DEEP BLACK CAR. 50ML</t>
+        </is>
+      </c>
+      <c r="D4995" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="4996">
+      <c r="A4996" t="n">
+        <v>4995</v>
+      </c>
+      <c r="B4996" t="inlineStr">
+        <is>
+          <t>8999777014315</t>
+        </is>
+      </c>
+      <c r="C4996" t="inlineStr">
+        <is>
+          <t>NIVEA ROLL-ON DEEP BLACK CAR. 50ML</t>
+        </is>
+      </c>
+      <c r="D4996" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="4997">
+      <c r="A4997" t="n">
+        <v>4996</v>
+      </c>
+      <c r="B4997" t="inlineStr">
+        <is>
+          <t>9005800379494</t>
+        </is>
+      </c>
+      <c r="C4997" t="inlineStr">
+        <is>
+          <t>NIVEA ROLL-ON DEEP BLACK CAR. 50ML</t>
+        </is>
+      </c>
+      <c r="D4997" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="4998">
+      <c r="A4998" t="n">
+        <v>4997</v>
+      </c>
+      <c r="B4998" t="inlineStr">
+        <is>
+          <t>9005800379685</t>
+        </is>
+      </c>
+      <c r="C4998" t="inlineStr">
+        <is>
+          <t>NIVEA ROLL-ON DEEP BLACK CAR. 50ML</t>
+        </is>
+      </c>
+      <c r="D4998" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="4999">
+      <c r="A4999" t="n">
+        <v>4998</v>
+      </c>
+      <c r="B4999" t="inlineStr">
+        <is>
+          <t>8999777016784</t>
+        </is>
+      </c>
+      <c r="C4999" t="inlineStr">
+        <is>
+          <t>NIVEA ROLL-ON MEN COOL KICK 50ML</t>
+        </is>
+      </c>
+      <c r="D4999" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="5000">
+      <c r="A5000" t="n">
+        <v>4999</v>
+      </c>
+      <c r="B5000" t="inlineStr">
+        <is>
+          <t>9005800390161</t>
+        </is>
+      </c>
+      <c r="C5000" t="inlineStr">
+        <is>
+          <t>NIVEA ROLL-ON MEN CON. SENS. 50ML</t>
+        </is>
+      </c>
+      <c r="D5000" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="5001">
+      <c r="A5001" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B5001" t="inlineStr">
+        <is>
+          <t>8000500168028</t>
+        </is>
+      </c>
+      <c r="C5001" t="inlineStr">
+        <is>
+          <t>KINDER JOY 20G</t>
+        </is>
+      </c>
+      <c r="D5001" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5002">
+      <c r="A5002" t="n">
+        <v>5001</v>
+      </c>
+      <c r="B5002" t="inlineStr">
+        <is>
+          <t>8000500168042</t>
+        </is>
+      </c>
+      <c r="C5002" t="inlineStr">
+        <is>
+          <t>KINDER JOY 20G</t>
+        </is>
+      </c>
+      <c r="D5002" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5003">
+      <c r="A5003" t="n">
+        <v>5002</v>
+      </c>
+      <c r="B5003" t="inlineStr">
+        <is>
+          <t>80135890</t>
+        </is>
+      </c>
+      <c r="C5003" t="inlineStr">
+        <is>
+          <t>KINDER JOY 20G</t>
+        </is>
+      </c>
+      <c r="D5003" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5004">
+      <c r="A5004" t="n">
+        <v>5003</v>
+      </c>
+      <c r="B5004" t="inlineStr">
+        <is>
+          <t>8690146159216</t>
+        </is>
+      </c>
+      <c r="C5004" t="inlineStr">
+        <is>
+          <t>BURGER GUMENI SLATKIS 10.5G</t>
+        </is>
+      </c>
+      <c r="D5004" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5005">
+      <c r="A5005" t="n">
+        <v>5004</v>
+      </c>
+      <c r="B5005" t="inlineStr">
+        <is>
+          <t>3903658680563</t>
+        </is>
+      </c>
+      <c r="C5005" t="inlineStr">
+        <is>
+          <t>BM S KEKS 400G</t>
+        </is>
+      </c>
+      <c r="D5005" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5006">
+      <c r="A5006" t="n">
+        <v>5005</v>
+      </c>
+      <c r="B5006" t="inlineStr">
+        <is>
+          <t>9002859063558</t>
+        </is>
+      </c>
+      <c r="C5006" t="inlineStr">
+        <is>
+          <t>GUNZ BOMBONJERA RUZA 180G</t>
+        </is>
+      </c>
+      <c r="D5006" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="5007">
+      <c r="A5007" t="n">
+        <v>5006</v>
+      </c>
+      <c r="B5007" t="inlineStr">
+        <is>
+          <t>3875000970625</t>
+        </is>
+      </c>
+      <c r="C5007" t="inlineStr">
+        <is>
+          <t>HRANA ZA PSE PILETINA 415G</t>
+        </is>
+      </c>
+      <c r="D5007" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="5008">
+      <c r="A5008" t="n">
+        <v>5007</v>
+      </c>
+      <c r="B5008" t="inlineStr">
+        <is>
+          <t>3875000974760</t>
+        </is>
+      </c>
+      <c r="C5008" t="inlineStr">
+        <is>
+          <t>BELLA DETERDZ. ZA POSUDJE 5L LIMUN</t>
+        </is>
+      </c>
+      <c r="D5008" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="5009">
+      <c r="A5009" t="n">
+        <v>5008</v>
+      </c>
+      <c r="B5009" t="inlineStr">
+        <is>
+          <t>8606003595509</t>
+        </is>
+      </c>
+      <c r="C5009" t="inlineStr">
+        <is>
+          <t>DJEVDJIR DRENATO DRINA</t>
+        </is>
+      </c>
+      <c r="D5009" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5010">
+      <c r="A5010" t="n">
+        <v>5009</v>
+      </c>
+      <c r="B5010" t="inlineStr">
+        <is>
+          <t>8606003593314</t>
+        </is>
+      </c>
+      <c r="C5010" t="inlineStr">
+        <is>
+          <t>POSUDA VIVO 2L DRINA</t>
+        </is>
+      </c>
+      <c r="D5010" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="5011">
+      <c r="A5011" t="n">
+        <v>5010</v>
+      </c>
+      <c r="B5011" t="inlineStr">
+        <is>
+          <t>3870028000842</t>
+        </is>
+      </c>
+      <c r="C5011" t="inlineStr">
+        <is>
+          <t>SARAJEVSKO BEZALKOHOLNO 0.50L</t>
+        </is>
+      </c>
+      <c r="D5011" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="5012">
+      <c r="A5012" t="n">
+        <v>5011</v>
+      </c>
+      <c r="B5012" t="inlineStr">
+        <is>
+          <t>3838700040319</t>
+        </is>
+      </c>
+      <c r="C5012" t="inlineStr">
+        <is>
+          <t>SUMI TVRDI VISOKI C 100G</t>
+        </is>
+      </c>
+      <c r="D5012" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="5013">
+      <c r="A5013" t="n">
+        <v>5012</v>
+      </c>
+      <c r="B5013" t="inlineStr">
+        <is>
+          <t>8600037003436</t>
+        </is>
+      </c>
+      <c r="C5013" t="inlineStr">
+        <is>
+          <t>KNJAZ MILOS AROM. NARANDZA 1.25L</t>
+        </is>
+      </c>
+      <c r="D5013" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="5014">
+      <c r="A5014" t="n">
+        <v>5013</v>
+      </c>
+      <c r="B5014" t="inlineStr">
+        <is>
+          <t>8600037002309</t>
+        </is>
+      </c>
+      <c r="C5014" t="inlineStr">
+        <is>
+          <t>KNJAZ MILOS AROM. BRESKVA 1.25L</t>
+        </is>
+      </c>
+      <c r="D5014" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="5015">
+      <c r="A5015" t="n">
+        <v>5014</v>
+      </c>
+      <c r="B5015" t="inlineStr">
+        <is>
+          <t>8710438029086</t>
+        </is>
+      </c>
+      <c r="C5015" t="inlineStr">
+        <is>
+          <t>MCCAIN POMFRIT C STAR 2.5KG</t>
+        </is>
+      </c>
+      <c r="D5015" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="5016">
+      <c r="A5016" t="n">
+        <v>5015</v>
+      </c>
+      <c r="B5016" t="inlineStr">
+        <is>
+          <t>3870174000970</t>
+        </is>
+      </c>
+      <c r="C5016" t="inlineStr">
+        <is>
+          <t>SETI BRUSNICA 50G</t>
+        </is>
+      </c>
+      <c r="D5016" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="5017">
+      <c r="A5017" t="n">
+        <v>5016</v>
+      </c>
+      <c r="B5017" t="inlineStr">
+        <is>
+          <t>3874002701312</t>
+        </is>
+      </c>
+      <c r="C5017" t="inlineStr">
+        <is>
+          <t>TOMICO KECAP BLAGI 1000G</t>
+        </is>
+      </c>
+      <c r="D5017" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="5018">
+      <c r="A5018" t="n">
+        <v>5017</v>
+      </c>
+      <c r="B5018" t="inlineStr">
+        <is>
+          <t>5050581060379</t>
+        </is>
+      </c>
+      <c r="C5018" t="inlineStr">
+        <is>
+          <t>MASLINE PINO ZELENE BEZ KOST. 670G</t>
+        </is>
+      </c>
+      <c r="D5018" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5019">
+      <c r="A5019" t="n">
+        <v>5018</v>
+      </c>
+      <c r="B5019" t="inlineStr">
+        <is>
+          <t>3650322007099</t>
+        </is>
+      </c>
+      <c r="C5019" t="inlineStr">
+        <is>
+          <t>CEDEVITA LIMUN 200G</t>
+        </is>
+      </c>
+      <c r="D5019" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="5020">
+      <c r="A5020" t="n">
+        <v>5019</v>
+      </c>
+      <c r="B5020" t="inlineStr">
+        <is>
+          <t>3838471007362</t>
+        </is>
+      </c>
+      <c r="C5020" t="inlineStr">
+        <is>
+          <t>ARGETA PIKANT 95G</t>
+        </is>
+      </c>
+      <c r="D5020" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5021">
+      <c r="A5021" t="n">
+        <v>5020</v>
+      </c>
+      <c r="B5021" t="inlineStr">
+        <is>
+          <t>8693495033817</t>
+        </is>
+      </c>
+      <c r="C5021" t="inlineStr">
+        <is>
+          <t>PALMOLIVE SAPUN 90G KAMIL&amp;VITAMIN</t>
+        </is>
+      </c>
+      <c r="D5021" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5022">
+      <c r="A5022" t="n">
+        <v>5021</v>
+      </c>
+      <c r="B5022" t="inlineStr">
+        <is>
+          <t>8693495033893</t>
+        </is>
+      </c>
+      <c r="C5022" t="inlineStr">
+        <is>
+          <t>PALMOLIVE SAPUN 90G KAMIL&amp;VITAMIN</t>
+        </is>
+      </c>
+      <c r="D5022" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5023">
+      <c r="A5023" t="n">
+        <v>5022</v>
+      </c>
+      <c r="B5023" t="inlineStr">
+        <is>
+          <t>8714789699110</t>
+        </is>
+      </c>
+      <c r="C5023" t="inlineStr">
+        <is>
+          <t>PALMOLIVE SAPUN 90G KAMIL&amp;VITAMIN</t>
+        </is>
+      </c>
+      <c r="D5023" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5024">
+      <c r="A5024" t="n">
+        <v>5023</v>
+      </c>
+      <c r="B5024" t="inlineStr">
+        <is>
+          <t>8714789702957</t>
+        </is>
+      </c>
+      <c r="C5024" t="inlineStr">
+        <is>
+          <t>PALMOLIVE SAPUN 90G KAMIL&amp;VITAMIN</t>
+        </is>
+      </c>
+      <c r="D5024" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5025">
+      <c r="A5025" t="n">
+        <v>5024</v>
+      </c>
+      <c r="B5025" t="inlineStr">
+        <is>
+          <t>8693495051149</t>
+        </is>
+      </c>
+      <c r="C5025" t="inlineStr">
+        <is>
+          <t>PALMOLIVE SAPUN 90G ROSE</t>
+        </is>
+      </c>
+      <c r="D5025" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5026">
+      <c r="A5026" t="n">
+        <v>5025</v>
+      </c>
+      <c r="B5026" t="inlineStr">
+        <is>
+          <t>8693495051156</t>
+        </is>
+      </c>
+      <c r="C5026" t="inlineStr">
+        <is>
+          <t>PALMOLIVE SAPUN 90G ROSE</t>
+        </is>
+      </c>
+      <c r="D5026" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5027">
+      <c r="A5027" t="n">
+        <v>5026</v>
+      </c>
+      <c r="B5027" t="inlineStr">
+        <is>
+          <t>662025091</t>
+        </is>
+      </c>
+      <c r="C5027" t="inlineStr">
+        <is>
+          <t>VRECICA PAPRINA ZA BOCE</t>
+        </is>
+      </c>
+      <c r="D5027" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5028">
+      <c r="A5028" t="n">
+        <v>5027</v>
+      </c>
+      <c r="B5028" t="inlineStr">
+        <is>
+          <t>6901040700049</t>
+        </is>
+      </c>
+      <c r="C5028" t="inlineStr">
+        <is>
+          <t>VRECICA PAPRINA ZA BOCE</t>
+        </is>
+      </c>
+      <c r="D5028" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5029">
+      <c r="A5029" t="n">
+        <v>5028</v>
+      </c>
+      <c r="B5029" t="inlineStr">
+        <is>
+          <t>6901040711229</t>
+        </is>
+      </c>
+      <c r="C5029" t="inlineStr">
+        <is>
+          <t>VRECICA PAPRINA ZA BOCE</t>
+        </is>
+      </c>
+      <c r="D5029" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5030">
+      <c r="A5030" t="n">
+        <v>5029</v>
+      </c>
+      <c r="B5030" t="inlineStr">
+        <is>
+          <t>6926682470259</t>
+        </is>
+      </c>
+      <c r="C5030" t="inlineStr">
+        <is>
+          <t>VRECICA PAPRINA ZA BOCE</t>
+        </is>
+      </c>
+      <c r="D5030" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5031">
+      <c r="A5031" t="n">
+        <v>5030</v>
+      </c>
+      <c r="B5031" t="inlineStr">
+        <is>
+          <t>6956702521272</t>
+        </is>
+      </c>
+      <c r="C5031" t="inlineStr">
+        <is>
+          <t>VRECICA PAPRINA ZA BOCE</t>
+        </is>
+      </c>
+      <c r="D5031" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5032">
+      <c r="A5032" t="n">
+        <v>5031</v>
+      </c>
+      <c r="B5032" t="inlineStr">
+        <is>
+          <t>6956702526017</t>
+        </is>
+      </c>
+      <c r="C5032" t="inlineStr">
+        <is>
+          <t>VRECICA PAPRINA ZA BOCE</t>
+        </is>
+      </c>
+      <c r="D5032" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5033">
+      <c r="A5033" t="n">
+        <v>5032</v>
+      </c>
+      <c r="B5033" t="inlineStr">
+        <is>
+          <t>690103940234</t>
+        </is>
+      </c>
+      <c r="C5033" t="inlineStr">
+        <is>
+          <t>VRECICA 27X33</t>
+        </is>
+      </c>
+      <c r="D5033" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5034">
+      <c r="A5034" t="n">
+        <v>5033</v>
+      </c>
+      <c r="B5034" t="inlineStr">
+        <is>
+          <t>6920230302023</t>
+        </is>
+      </c>
+      <c r="C5034" t="inlineStr">
+        <is>
+          <t>VRECICA 27X33</t>
+        </is>
+      </c>
+      <c r="D5034" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5035">
+      <c r="A5035" t="n">
+        <v>5034</v>
+      </c>
+      <c r="B5035" t="inlineStr">
+        <is>
+          <t>6956702529100</t>
+        </is>
+      </c>
+      <c r="C5035" t="inlineStr">
+        <is>
+          <t>VRECICA 27X33</t>
+        </is>
+      </c>
+      <c r="D5035" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5036">
+      <c r="A5036" t="n">
+        <v>5035</v>
+      </c>
+      <c r="B5036" t="inlineStr">
+        <is>
+          <t>6972513828423</t>
+        </is>
+      </c>
+      <c r="C5036" t="inlineStr">
+        <is>
+          <t>VRECICA 27X33</t>
+        </is>
+      </c>
+      <c r="D5036" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5037">
+      <c r="A5037" t="n">
+        <v>5036</v>
+      </c>
+      <c r="B5037" t="inlineStr">
+        <is>
+          <t>8610465888017</t>
+        </is>
+      </c>
+      <c r="C5037" t="inlineStr">
+        <is>
+          <t>VRECICA 27X33</t>
+        </is>
+      </c>
+      <c r="D5037" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5038">
+      <c r="A5038" t="n">
+        <v>5037</v>
+      </c>
+      <c r="B5038" t="inlineStr">
+        <is>
+          <t>9002859126264</t>
+        </is>
+      </c>
+      <c r="C5038" t="inlineStr">
+        <is>
+          <t>BUBAMARA COKOLADA 85G</t>
+        </is>
+      </c>
+      <c r="D5038" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="5039">
+      <c r="A5039" t="n">
+        <v>5038</v>
+      </c>
+      <c r="B5039" t="inlineStr">
+        <is>
+          <t>9002859133718</t>
+        </is>
+      </c>
+      <c r="C5039" t="inlineStr">
+        <is>
+          <t>BUBAMARA COKOLADA 85G</t>
+        </is>
+      </c>
+      <c r="D5039" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="5040">
+      <c r="A5040" t="n">
+        <v>5039</v>
+      </c>
+      <c r="B5040" t="inlineStr">
+        <is>
+          <t>3871354004894</t>
+        </is>
+      </c>
+      <c r="C5040" t="inlineStr">
+        <is>
+          <t>MASTER MLJEVENI KEKS 500G</t>
+        </is>
+      </c>
+      <c r="D5040" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="5041">
+      <c r="A5041" t="n">
+        <v>5040</v>
+      </c>
+      <c r="B5041" t="inlineStr">
+        <is>
+          <t>3870007064469</t>
+        </is>
+      </c>
+      <c r="C5041" t="inlineStr">
+        <is>
+          <t>VISPAK RIZOTO SA POVRCEM 375G</t>
+        </is>
+      </c>
+      <c r="D5041" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="5042">
+      <c r="A5042" t="n">
+        <v>5041</v>
+      </c>
+      <c r="B5042" t="inlineStr">
+        <is>
+          <t>3856020218706</t>
+        </is>
+      </c>
+      <c r="C5042" t="inlineStr">
+        <is>
+          <t>GULAS GOVEDJI 2X200G PODRAVKA</t>
+        </is>
+      </c>
+      <c r="D5042" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="5043">
+      <c r="A5043" t="n">
+        <v>5042</v>
+      </c>
+      <c r="B5043" t="inlineStr">
+        <is>
+          <t>8714789324821</t>
+        </is>
+      </c>
+      <c r="C5043" t="inlineStr">
+        <is>
+          <t>AJAX LILAC BREEZE 1L</t>
+        </is>
+      </c>
+      <c r="D5043" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5044">
+      <c r="A5044" t="n">
+        <v>5043</v>
+      </c>
+      <c r="B5044" t="inlineStr">
+        <is>
+          <t>8714789392813</t>
+        </is>
+      </c>
+      <c r="C5044" t="inlineStr">
+        <is>
+          <t>AJAX LILAC BREEZE 1L</t>
+        </is>
+      </c>
+      <c r="D5044" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5045">
+      <c r="A5045" t="n">
+        <v>5044</v>
+      </c>
+      <c r="B5045" t="inlineStr">
+        <is>
+          <t>871895127851</t>
+        </is>
+      </c>
+      <c r="C5045" t="inlineStr">
+        <is>
+          <t>AJAX LILAC BREEZE 1L</t>
+        </is>
+      </c>
+      <c r="D5045" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5046">
+      <c r="A5046" t="n">
+        <v>5045</v>
+      </c>
+      <c r="B5046" t="inlineStr">
+        <is>
+          <t>3875000184541</t>
+        </is>
+      </c>
+      <c r="C5046" t="inlineStr">
+        <is>
+          <t>SARAJEVSKI KISELJAK LIMUNADA 0,5L</t>
+        </is>
+      </c>
+      <c r="D5046" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="5047">
+      <c r="A5047" t="n">
+        <v>5046</v>
+      </c>
+      <c r="B5047" t="inlineStr">
+        <is>
+          <t>3830001715156</t>
+        </is>
+      </c>
+      <c r="C5047" t="inlineStr">
+        <is>
+          <t>HEINEKEN BEZALKOHOLNO 0,33L</t>
+        </is>
+      </c>
+      <c r="D5047" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5048">
+      <c r="A5048" t="n">
+        <v>5047</v>
+      </c>
+      <c r="B5048" t="inlineStr">
+        <is>
+          <t>3830054841802</t>
+        </is>
+      </c>
+      <c r="C5048" t="inlineStr">
+        <is>
+          <t>HEINEKEN BEZALK. LIMENKA 0,33L</t>
+        </is>
+      </c>
+      <c r="D5048" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -24087,7 +24087,7 @@
         </is>
       </c>
       <c r="D1315" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="1316">
@@ -53319,7 +53319,7 @@
         </is>
       </c>
       <c r="D2939" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="2940">
@@ -69339,7 +69339,7 @@
         </is>
       </c>
       <c r="D3829" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="3830">

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -24083,7 +24083,7 @@
       </c>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>GOVEDJI GULAS RANC 300 G</t>
+          <t>GOVEDJI GULAS 300G RANCH</t>
         </is>
       </c>
       <c r="D1315" t="n">

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -69335,7 +69335,7 @@
       </c>
       <c r="C3829" t="inlineStr">
         <is>
-          <t>GOVEDJE CUFTE U PAR.SOSU 300G RAN</t>
+          <t>GOVEDJE CUFTE PARAD.SOS RANCH 300G</t>
         </is>
       </c>
       <c r="D3829" t="n">

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -12437,7 +12437,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>TOFIX BOMBONE 700 G</t>
+          <t>TOFIX BOMBONE 700G</t>
         </is>
       </c>
       <c r="D668" t="n">
@@ -39185,7 +39185,7 @@
       </c>
       <c r="C2154" t="inlineStr">
         <is>
-          <t>JANA LEDENI CAJ BRESKVA 005L</t>
+          <t>JANA LEDENI CAJ BRESKVA 0,5L</t>
         </is>
       </c>
       <c r="D2154" t="n">
@@ -53315,7 +53315,7 @@
       </c>
       <c r="C2939" t="inlineStr">
         <is>
-          <t>SVINJSKI GULAS 300G</t>
+          <t>SVINJSKI GULAS 300G RANCH</t>
         </is>
       </c>
       <c r="D2939" t="n">
@@ -64817,7 +64817,7 @@
       </c>
       <c r="C3578" t="inlineStr">
         <is>
-          <t>JANA VITAMIN MENTA LIMENA 0,5L</t>
+          <t>JANA VITAMIN MENTA LIMETA 0,5L</t>
         </is>
       </c>
       <c r="D3578" t="n">
@@ -90129,7 +90129,7 @@
         </is>
       </c>
       <c r="D4984" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4985">
@@ -90305,7 +90305,7 @@
       </c>
       <c r="C4994" t="inlineStr">
         <is>
-          <t>MAJONEZ TOMICO DELI. 285NL</t>
+          <t>MAJONEZ TOMICO DELI. 285ML</t>
         </is>
       </c>
       <c r="D4994" t="n">

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5048"/>
+  <dimension ref="A1:D5053"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="141">
@@ -26585,7 +26585,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>SETI RIZA 800 G</t>
+          <t>SETI RIZA 800G</t>
         </is>
       </c>
       <c r="D1454" t="n">
@@ -46227,7 +46227,7 @@
         </is>
       </c>
       <c r="D2545" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="2546">
@@ -86907,7 +86907,7 @@
         </is>
       </c>
       <c r="D4805" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4806">
@@ -86925,7 +86925,7 @@
         </is>
       </c>
       <c r="D4806" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4807">
@@ -91282,6 +91282,96 @@
       </c>
       <c r="D5048" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="5049">
+      <c r="A5049" t="n">
+        <v>5048</v>
+      </c>
+      <c r="B5049" t="inlineStr">
+        <is>
+          <t>8683749137002</t>
+        </is>
+      </c>
+      <c r="C5049" t="inlineStr">
+        <is>
+          <t>MINI DOLL COKOLADNO JAJE 100G</t>
+        </is>
+      </c>
+      <c r="D5049" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5050">
+      <c r="A5050" t="n">
+        <v>5049</v>
+      </c>
+      <c r="B5050" t="inlineStr">
+        <is>
+          <t>8682134080053</t>
+        </is>
+      </c>
+      <c r="C5050" t="inlineStr">
+        <is>
+          <t>DIPPO CORNET 25G</t>
+        </is>
+      </c>
+      <c r="D5050" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5051">
+      <c r="A5051" t="n">
+        <v>5050</v>
+      </c>
+      <c r="B5051" t="inlineStr">
+        <is>
+          <t>8601300046051</t>
+        </is>
+      </c>
+      <c r="C5051" t="inlineStr">
+        <is>
+          <t>DANUBIUS BRASNO ZA RAZ. HLJEB 900G</t>
+        </is>
+      </c>
+      <c r="D5051" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="5052">
+      <c r="A5052" t="n">
+        <v>5051</v>
+      </c>
+      <c r="B5052" t="inlineStr">
+        <is>
+          <t>8601300046280</t>
+        </is>
+      </c>
+      <c r="C5052" t="inlineStr">
+        <is>
+          <t>DANUBIUS BRASNO ZA PIZZU 1KG</t>
+        </is>
+      </c>
+      <c r="D5052" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="5053">
+      <c r="A5053" t="n">
+        <v>5052</v>
+      </c>
+      <c r="B5053" t="inlineStr">
+        <is>
+          <t>02842034</t>
+        </is>
+      </c>
+      <c r="C5053" t="inlineStr">
+        <is>
+          <t>TILSIT FRIENDSHIP SIR 45%MM</t>
+        </is>
+      </c>
+      <c r="D5053" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5053"/>
+  <dimension ref="A1:D5088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4.48</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="126">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="131">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>G.BRIO KAKAO 280 G</t>
+          <t>G.BRIO KAKAO 280G</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="268">
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515">
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="548">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>LEVINDA BOMBONE 800 G</t>
+          <t>LEVINDA BOMBONE 800G</t>
         </is>
       </c>
       <c r="D667" t="n">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>LEVINDA BOMBONE 300 G</t>
+          <t>LEVINDA BOMBONE 300G</t>
         </is>
       </c>
       <c r="D669" t="n">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>FRIZI KOLA 250 G</t>
+          <t>FRIZI KOLA 250G</t>
         </is>
       </c>
       <c r="D671" t="n">
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="D696" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="697">
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="D746" t="n">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="747">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="D829" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="830">
@@ -16383,7 +16383,7 @@
         </is>
       </c>
       <c r="D887" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="888">
@@ -16401,7 +16401,7 @@
         </is>
       </c>
       <c r="D888" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="889">
@@ -16419,7 +16419,7 @@
         </is>
       </c>
       <c r="D889" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="890">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="D890" t="n">
-        <v>7.72</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="891">
@@ -20325,7 +20325,7 @@
         </is>
       </c>
       <c r="D1106" t="n">
-        <v>6.6</v>
+        <v>6.699999999999999</v>
       </c>
     </row>
     <row r="1107">
@@ -20343,7 +20343,7 @@
         </is>
       </c>
       <c r="D1107" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="1108">
@@ -20361,7 +20361,7 @@
         </is>
       </c>
       <c r="D1108" t="n">
-        <v>6.8</v>
+        <v>6.899999999999999</v>
       </c>
     </row>
     <row r="1109">
@@ -20379,7 +20379,7 @@
         </is>
       </c>
       <c r="D1109" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="1110">
@@ -20397,7 +20397,7 @@
         </is>
       </c>
       <c r="D1110" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="1111">
@@ -20415,7 +20415,7 @@
         </is>
       </c>
       <c r="D1111" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="1112">
@@ -20433,7 +20433,7 @@
         </is>
       </c>
       <c r="D1112" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="1113">
@@ -20451,7 +20451,7 @@
         </is>
       </c>
       <c r="D1113" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="1114">
@@ -25599,7 +25599,7 @@
         </is>
       </c>
       <c r="D1399" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="1400">
@@ -25833,7 +25833,7 @@
         </is>
       </c>
       <c r="D1412" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="1413">
@@ -26931,7 +26931,7 @@
         </is>
       </c>
       <c r="D1473" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="1474">
@@ -26967,7 +26967,7 @@
         </is>
       </c>
       <c r="D1475" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="1476">
@@ -27921,7 +27921,7 @@
         </is>
       </c>
       <c r="D1528" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="1529">
@@ -28317,7 +28317,7 @@
         </is>
       </c>
       <c r="D1550" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="1551">
@@ -28569,7 +28569,7 @@
         </is>
       </c>
       <c r="D1564" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1565">
@@ -29541,7 +29541,7 @@
         </is>
       </c>
       <c r="D1618" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="1619">
@@ -31773,7 +31773,7 @@
         </is>
       </c>
       <c r="D1742" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1743">
@@ -31881,7 +31881,7 @@
         </is>
       </c>
       <c r="D1748" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1749">
@@ -32061,7 +32061,7 @@
         </is>
       </c>
       <c r="D1758" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="1759">
@@ -32277,7 +32277,7 @@
         </is>
       </c>
       <c r="D1770" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="1771">
@@ -33339,7 +33339,7 @@
         </is>
       </c>
       <c r="D1829" t="n">
-        <v>5.100000000000001</v>
+        <v>5.200000000000001</v>
       </c>
     </row>
     <row r="1830">
@@ -36993,7 +36993,7 @@
         </is>
       </c>
       <c r="D2032" t="n">
-        <v>6.6</v>
+        <v>6.699999999999999</v>
       </c>
     </row>
     <row r="2033">
@@ -37803,7 +37803,7 @@
         </is>
       </c>
       <c r="D2077" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="2078">
@@ -38631,7 +38631,7 @@
         </is>
       </c>
       <c r="D2123" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="2124">
@@ -39477,7 +39477,7 @@
         </is>
       </c>
       <c r="D2170" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="2171">
@@ -39873,7 +39873,7 @@
         </is>
       </c>
       <c r="D2192" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="2193">
@@ -40683,7 +40683,7 @@
         </is>
       </c>
       <c r="D2237" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="2238">
@@ -41475,7 +41475,7 @@
         </is>
       </c>
       <c r="D2281" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="2282">
@@ -42357,7 +42357,7 @@
         </is>
       </c>
       <c r="D2330" t="n">
-        <v>6.8</v>
+        <v>6.899999999999999</v>
       </c>
     </row>
     <row r="2331">
@@ -43325,11 +43325,11 @@
       </c>
       <c r="C2384" t="inlineStr">
         <is>
-          <t>XXL UBRUS</t>
+          <t>LUMAX XXL UBRUS 1000G</t>
         </is>
       </c>
       <c r="D2384" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="2385">
@@ -43779,7 +43779,7 @@
         </is>
       </c>
       <c r="D2409" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="2410">
@@ -46245,7 +46245,7 @@
         </is>
       </c>
       <c r="D2546" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2547">
@@ -46929,7 +46929,7 @@
         </is>
       </c>
       <c r="D2584" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="2585">
@@ -47829,7 +47829,7 @@
         </is>
       </c>
       <c r="D2634" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="2635">
@@ -48671,11 +48671,11 @@
       </c>
       <c r="C2681" t="inlineStr">
         <is>
-          <t>NEKTAR LIMUNADA1.5L</t>
+          <t>NEKTAR LIMUNADA 1,5L</t>
         </is>
       </c>
       <c r="D2681" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="2682">
@@ -49071,7 +49071,7 @@
         </is>
       </c>
       <c r="D2703" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2704">
@@ -52653,7 +52653,7 @@
         </is>
       </c>
       <c r="D2902" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="2903">
@@ -54363,7 +54363,7 @@
         </is>
       </c>
       <c r="D2997" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="2998">
@@ -57063,7 +57063,7 @@
         </is>
       </c>
       <c r="D3147" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3148">
@@ -57315,7 +57315,7 @@
         </is>
       </c>
       <c r="D3161" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3162">
@@ -60033,7 +60033,7 @@
         </is>
       </c>
       <c r="D3312" t="n">
-        <v>6.3</v>
+        <v>6.399999999999999</v>
       </c>
     </row>
     <row r="3313">
@@ -65343,7 +65343,7 @@
         </is>
       </c>
       <c r="D3607" t="n">
-        <v>7.6</v>
+        <v>7.699999999999999</v>
       </c>
     </row>
     <row r="3608">
@@ -66297,7 +66297,7 @@
         </is>
       </c>
       <c r="D3660" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3661">
@@ -66315,7 +66315,7 @@
         </is>
       </c>
       <c r="D3661" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3662">
@@ -66675,7 +66675,7 @@
         </is>
       </c>
       <c r="D3681" t="n">
-        <v>16.8</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="3682">
@@ -67269,7 +67269,7 @@
         </is>
       </c>
       <c r="D3714" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3715">
@@ -67395,7 +67395,7 @@
         </is>
       </c>
       <c r="D3721" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3722">
@@ -70167,7 +70167,7 @@
         </is>
       </c>
       <c r="D3875" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="3876">
@@ -71571,7 +71571,7 @@
         </is>
       </c>
       <c r="D3953" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3954">
@@ -74397,7 +74397,7 @@
         </is>
       </c>
       <c r="D4110" t="n">
-        <v>10.93</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="4111">
@@ -75288,7 +75288,7 @@
       </c>
       <c r="B4160" t="inlineStr">
         <is>
-          <t>2611533</t>
+          <t>02611533</t>
         </is>
       </c>
       <c r="C4160" t="inlineStr">
@@ -80985,7 +80985,7 @@
         </is>
       </c>
       <c r="D4476" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4477">
@@ -81975,7 +81975,7 @@
         </is>
       </c>
       <c r="D4531" t="n">
-        <v>28.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4532">
@@ -86493,7 +86493,7 @@
         </is>
       </c>
       <c r="D4782" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4783">
@@ -86547,7 +86547,7 @@
         </is>
       </c>
       <c r="D4785" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4786">
@@ -89157,7 +89157,7 @@
         </is>
       </c>
       <c r="D4930" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4931">
@@ -89625,7 +89625,7 @@
         </is>
       </c>
       <c r="D4956" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4957">
@@ -91317,7 +91317,7 @@
         </is>
       </c>
       <c r="D5050" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5051">
@@ -91335,7 +91335,7 @@
         </is>
       </c>
       <c r="D5051" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5052">
@@ -91353,7 +91353,7 @@
         </is>
       </c>
       <c r="D5052" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5053">
@@ -91372,6 +91372,636 @@
       </c>
       <c r="D5053" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="5054">
+      <c r="A5054" t="n">
+        <v>5053</v>
+      </c>
+      <c r="B5054" t="inlineStr">
+        <is>
+          <t>8606018726011</t>
+        </is>
+      </c>
+      <c r="C5054" t="inlineStr">
+        <is>
+          <t>NECTAR MALINADA 0,5L</t>
+        </is>
+      </c>
+      <c r="D5054" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="5055">
+      <c r="A5055" t="n">
+        <v>5054</v>
+      </c>
+      <c r="B5055" t="inlineStr">
+        <is>
+          <t>00853469</t>
+        </is>
+      </c>
+      <c r="C5055" t="inlineStr">
+        <is>
+          <t>SIR EDAMER 45%MM ZELENE DOLINE</t>
+        </is>
+      </c>
+      <c r="D5055" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5056">
+      <c r="A5056" t="n">
+        <v>5055</v>
+      </c>
+      <c r="B5056" t="inlineStr">
+        <is>
+          <t>02115702</t>
+        </is>
+      </c>
+      <c r="C5056" t="inlineStr">
+        <is>
+          <t>SPECIJAL KOBASICA KG</t>
+        </is>
+      </c>
+      <c r="D5056" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5057">
+      <c r="A5057" t="n">
+        <v>5056</v>
+      </c>
+      <c r="B5057" t="inlineStr">
+        <is>
+          <t>02115682</t>
+        </is>
+      </c>
+      <c r="C5057" t="inlineStr">
+        <is>
+          <t>KAMP KOBASICA KG</t>
+        </is>
+      </c>
+      <c r="D5057" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="5058">
+      <c r="A5058" t="n">
+        <v>5057</v>
+      </c>
+      <c r="B5058" t="inlineStr">
+        <is>
+          <t>7622202253461</t>
+        </is>
+      </c>
+      <c r="C5058" t="inlineStr">
+        <is>
+          <t>7D PREL. CAKEBAR COCOA 32G</t>
+        </is>
+      </c>
+      <c r="D5058" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5059">
+      <c r="A5059" t="n">
+        <v>5058</v>
+      </c>
+      <c r="B5059" t="inlineStr">
+        <is>
+          <t>3875000977389</t>
+        </is>
+      </c>
+      <c r="C5059" t="inlineStr">
+        <is>
+          <t>BELLA PRIRODNA IZVORSKA VODA 5L</t>
+        </is>
+      </c>
+      <c r="D5059" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5060">
+      <c r="A5060" t="n">
+        <v>5059</v>
+      </c>
+      <c r="B5060" t="inlineStr">
+        <is>
+          <t>3858881104090</t>
+        </is>
+      </c>
+      <c r="C5060" t="inlineStr">
+        <is>
+          <t>LOLA FLASTER CARE CLASSIC</t>
+        </is>
+      </c>
+      <c r="D5060" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5061">
+      <c r="A5061" t="n">
+        <v>5060</v>
+      </c>
+      <c r="B5061" t="inlineStr">
+        <is>
+          <t>3850105169488</t>
+        </is>
+      </c>
+      <c r="C5061" t="inlineStr">
+        <is>
+          <t>NILA MY SENSUAL BLACK 900ML</t>
+        </is>
+      </c>
+      <c r="D5061" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="5062">
+      <c r="A5062" t="n">
+        <v>5061</v>
+      </c>
+      <c r="B5062" t="inlineStr">
+        <is>
+          <t>3850105190468</t>
+        </is>
+      </c>
+      <c r="C5062" t="inlineStr">
+        <is>
+          <t>ORNEL YELLOW 4L</t>
+        </is>
+      </c>
+      <c r="D5062" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="5063">
+      <c r="A5063" t="n">
+        <v>5062</v>
+      </c>
+      <c r="B5063" t="inlineStr">
+        <is>
+          <t>3850105190499</t>
+        </is>
+      </c>
+      <c r="C5063" t="inlineStr">
+        <is>
+          <t>ORNEL BLUE 4L</t>
+        </is>
+      </c>
+      <c r="D5063" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="5064">
+      <c r="A5064" t="n">
+        <v>5063</v>
+      </c>
+      <c r="B5064" t="inlineStr">
+        <is>
+          <t>3850105151926</t>
+        </is>
+      </c>
+      <c r="C5064" t="inlineStr">
+        <is>
+          <t>ORNEL BIS GOLDEN DREAM 400ML</t>
+        </is>
+      </c>
+      <c r="D5064" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="5065">
+      <c r="A5065" t="n">
+        <v>5064</v>
+      </c>
+      <c r="B5065" t="inlineStr">
+        <is>
+          <t>3850105185754</t>
+        </is>
+      </c>
+      <c r="C5065" t="inlineStr">
+        <is>
+          <t>ARF CRYSTAL SHINE 750ML</t>
+        </is>
+      </c>
+      <c r="D5065" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="5066">
+      <c r="A5066" t="n">
+        <v>5065</v>
+      </c>
+      <c r="B5066" t="inlineStr">
+        <is>
+          <t>3850105185723</t>
+        </is>
+      </c>
+      <c r="C5066" t="inlineStr">
+        <is>
+          <t>ARF DEOBAD 750ML</t>
+        </is>
+      </c>
+      <c r="D5066" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="5067">
+      <c r="A5067" t="n">
+        <v>5066</v>
+      </c>
+      <c r="B5067" t="inlineStr">
+        <is>
+          <t>3850105187109</t>
+        </is>
+      </c>
+      <c r="C5067" t="inlineStr">
+        <is>
+          <t>LIKVI KAPS. SUPR. ALL IN ONE 53/1</t>
+        </is>
+      </c>
+      <c r="D5067" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="5068">
+      <c r="A5068" t="n">
+        <v>5067</v>
+      </c>
+      <c r="B5068" t="inlineStr">
+        <is>
+          <t>3870281015546</t>
+        </is>
+      </c>
+      <c r="C5068" t="inlineStr">
+        <is>
+          <t>BONITO MJES. ZACINA ZA GRILL 30G</t>
+        </is>
+      </c>
+      <c r="D5068" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5069">
+      <c r="A5069" t="n">
+        <v>5068</v>
+      </c>
+      <c r="B5069" t="inlineStr">
+        <is>
+          <t>5000204435276</t>
+        </is>
+      </c>
+      <c r="C5069" t="inlineStr">
+        <is>
+          <t>DUCK MARINE 750ML</t>
+        </is>
+      </c>
+      <c r="D5069" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="5070">
+      <c r="A5070" t="n">
+        <v>5069</v>
+      </c>
+      <c r="B5070" t="inlineStr">
+        <is>
+          <t>5000204043945</t>
+        </is>
+      </c>
+      <c r="C5070" t="inlineStr">
+        <is>
+          <t>MR.MUSCLE BATHROOM 750ML PLATINUM</t>
+        </is>
+      </c>
+      <c r="D5070" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="5071">
+      <c r="A5071" t="n">
+        <v>5070</v>
+      </c>
+      <c r="B5071" t="inlineStr">
+        <is>
+          <t>40307381</t>
+        </is>
+      </c>
+      <c r="C5071" t="inlineStr">
+        <is>
+          <t>DAVIDOFF CLASSIC</t>
+        </is>
+      </c>
+      <c r="D5071" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="5072">
+      <c r="A5072" t="n">
+        <v>5071</v>
+      </c>
+      <c r="B5072" t="inlineStr">
+        <is>
+          <t>40306445</t>
+        </is>
+      </c>
+      <c r="C5072" t="inlineStr">
+        <is>
+          <t>DAVIDOFF GOLD</t>
+        </is>
+      </c>
+      <c r="D5072" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="5073">
+      <c r="A5073" t="n">
+        <v>5072</v>
+      </c>
+      <c r="B5073" t="inlineStr">
+        <is>
+          <t>8683749134537</t>
+        </is>
+      </c>
+      <c r="C5073" t="inlineStr">
+        <is>
+          <t>RITO LJESNJAK COKO. PRALINE 300G</t>
+        </is>
+      </c>
+      <c r="D5073" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5074">
+      <c r="A5074" t="n">
+        <v>5073</v>
+      </c>
+      <c r="B5074" t="inlineStr">
+        <is>
+          <t>8683749137330</t>
+        </is>
+      </c>
+      <c r="C5074" t="inlineStr">
+        <is>
+          <t>RITO KOKOS COKO. PRALINE 300G</t>
+        </is>
+      </c>
+      <c r="D5074" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5075">
+      <c r="A5075" t="n">
+        <v>5074</v>
+      </c>
+      <c r="B5075" t="inlineStr">
+        <is>
+          <t>8600763041689</t>
+        </is>
+      </c>
+      <c r="C5075" t="inlineStr">
+        <is>
+          <t>PATELINA PILECA PESTO 60G</t>
+        </is>
+      </c>
+      <c r="D5075" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="5076">
+      <c r="A5076" t="n">
+        <v>5075</v>
+      </c>
+      <c r="B5076" t="inlineStr">
+        <is>
+          <t>8606019651282</t>
+        </is>
+      </c>
+      <c r="C5076" t="inlineStr">
+        <is>
+          <t>NUTRINO LAB SO GUT BAN&amp;KOK 60G</t>
+        </is>
+      </c>
+      <c r="D5076" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="5077">
+      <c r="A5077" t="n">
+        <v>5076</v>
+      </c>
+      <c r="B5077" t="inlineStr">
+        <is>
+          <t>8606019651299</t>
+        </is>
+      </c>
+      <c r="C5077" t="inlineStr">
+        <is>
+          <t>NUTRINO LAB HAPPY GUT JAB&amp;CIM 60G</t>
+        </is>
+      </c>
+      <c r="D5077" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="5078">
+      <c r="A5078" t="n">
+        <v>5077</v>
+      </c>
+      <c r="B5078" t="inlineStr">
+        <is>
+          <t>8606019651305</t>
+        </is>
+      </c>
+      <c r="C5078" t="inlineStr">
+        <is>
+          <t>NUTRINO LAB VERRY GUT MAL&amp;JAG 60G</t>
+        </is>
+      </c>
+      <c r="D5078" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="5079">
+      <c r="A5079" t="n">
+        <v>5078</v>
+      </c>
+      <c r="B5079" t="inlineStr">
+        <is>
+          <t>3850104017537</t>
+        </is>
+      </c>
+      <c r="C5079" t="inlineStr">
+        <is>
+          <t>PODRAVKA COKOLINO 1KG</t>
+        </is>
+      </c>
+      <c r="D5079" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="5080">
+      <c r="A5080" t="n">
+        <v>5079</v>
+      </c>
+      <c r="B5080" t="inlineStr">
+        <is>
+          <t>3875000662810</t>
+        </is>
+      </c>
+      <c r="C5080" t="inlineStr">
+        <is>
+          <t>MARLBORO RED TITANIUM</t>
+        </is>
+      </c>
+      <c r="D5080" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5081">
+      <c r="A5081" t="n">
+        <v>5080</v>
+      </c>
+      <c r="B5081" t="inlineStr">
+        <is>
+          <t>3872292008005</t>
+        </is>
+      </c>
+      <c r="C5081" t="inlineStr">
+        <is>
+          <t>AT SUPER LJEPILO 3G</t>
+        </is>
+      </c>
+      <c r="D5081" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5082">
+      <c r="A5082" t="n">
+        <v>5081</v>
+      </c>
+      <c r="B5082" t="inlineStr">
+        <is>
+          <t>3872292004755</t>
+        </is>
+      </c>
+      <c r="C5082" t="inlineStr">
+        <is>
+          <t>MC WC FRESH. QUATRO LAVANDER 3X50G</t>
+        </is>
+      </c>
+      <c r="D5082" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="5083">
+      <c r="A5083" t="n">
+        <v>5082</v>
+      </c>
+      <c r="B5083" t="inlineStr">
+        <is>
+          <t>8606033742935</t>
+        </is>
+      </c>
+      <c r="C5083" t="inlineStr">
+        <is>
+          <t>CHIPSY RAVAN PAPRIKA 130G</t>
+        </is>
+      </c>
+      <c r="D5083" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5084">
+      <c r="A5084" t="n">
+        <v>5083</v>
+      </c>
+      <c r="B5084" t="inlineStr">
+        <is>
+          <t>8606033743178</t>
+        </is>
+      </c>
+      <c r="C5084" t="inlineStr">
+        <is>
+          <t>CHIPSY REBRASTI KECAP 55G</t>
+        </is>
+      </c>
+      <c r="D5084" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5085">
+      <c r="A5085" t="n">
+        <v>5084</v>
+      </c>
+      <c r="B5085" t="inlineStr">
+        <is>
+          <t>8606033742850</t>
+        </is>
+      </c>
+      <c r="C5085" t="inlineStr">
+        <is>
+          <t>CHIPSY REBRASTI CIZBURGER 85G</t>
+        </is>
+      </c>
+      <c r="D5085" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5086">
+      <c r="A5086" t="n">
+        <v>5085</v>
+      </c>
+      <c r="B5086" t="inlineStr">
+        <is>
+          <t>8601500140993</t>
+        </is>
+      </c>
+      <c r="C5086" t="inlineStr">
+        <is>
+          <t>IMLEK NERA ICE LATTE 0,23L CASA</t>
+        </is>
+      </c>
+      <c r="D5086" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="5087">
+      <c r="A5087" t="n">
+        <v>5086</v>
+      </c>
+      <c r="B5087" t="inlineStr">
+        <is>
+          <t>8601500140474</t>
+        </is>
+      </c>
+      <c r="C5087" t="inlineStr">
+        <is>
+          <t>IMLEK NERA ALMOND LATTE 0.23L CASA</t>
+        </is>
+      </c>
+      <c r="D5087" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="5088">
+      <c r="A5088" t="n">
+        <v>5087</v>
+      </c>
+      <c r="B5088" t="inlineStr">
+        <is>
+          <t>8601500140450</t>
+        </is>
+      </c>
+      <c r="C5088" t="inlineStr">
+        <is>
+          <t>IMLEK NERA STRONG 0.23L CASA</t>
+        </is>
+      </c>
+      <c r="D5088" t="n">
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/artikli.xlsx
+++ b/artikli.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5088"/>
+  <dimension ref="A1:D5099"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="138">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="141">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>ELF BALZAM ZA KOSU 500ML</t>
+          <t>ELF BALZAM ZA KOSU 500ML GIALLO</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="362">
@@ -6929,11 +6929,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>ELF BALZAM ZA KOSU</t>
+          <t>ELF BALZAM ZA KOSU 500ML VERDE</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="363">
@@ -6947,11 +6947,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>ELF BALZAM ZA KOSU 500ML</t>
+          <t>ELF BALZAM ZA KOSU 500ML BIANCO</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="364">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="366">
@@ -17405,11 +17405,11 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>KOSILI BEBI MLIJEKO 200ML</t>
+          <t>KOSILI BEBI MLIJEKO PLAVO 200ML</t>
         </is>
       </c>
       <c r="D944" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="945">
@@ -17495,11 +17495,11 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>KOSILI PUDER ZA DJECU</t>
+          <t>KOSILI PUDER ZA DJECU PLAVI 100G</t>
         </is>
       </c>
       <c r="D949" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="950">
@@ -17513,11 +17513,11 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>KOSILI PUDER ZA DJECU</t>
+          <t>KOSILI PUDER ZA DJECU ROZE 100G</t>
         </is>
       </c>
       <c r="D950" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="951">
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="D951" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="952">
@@ -17733,7 +17733,7 @@
         </is>
       </c>
       <c r="D962" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="963">
@@ -17751,7 +17751,7 @@
         </is>
       </c>
       <c r="D963" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="964">
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="D964" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="965">
@@ -25905,7 +25905,7 @@
         </is>
       </c>
       <c r="D1416" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1417">
@@ -47811,7 +47811,7 @@
         </is>
       </c>
       <c r="D2633" t="n">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="2634">
@@ -54759,7 +54759,7 @@
         </is>
       </c>
       <c r="D3019" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3020">
@@ -56163,7 +56163,7 @@
         </is>
       </c>
       <c r="D3097" t="n">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3098">
@@ -57081,7 +57081,7 @@
         </is>
       </c>
       <c r="D3148" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3149">
@@ -63273,7 +63273,7 @@
         </is>
       </c>
       <c r="D3492" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="3493">
@@ -71697,7 +71697,7 @@
         </is>
       </c>
       <c r="D3960" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3961">
@@ -83559,7 +83559,7 @@
         </is>
       </c>
       <c r="D4619" t="n">
-        <v>6.4</v>
+        <v>6.800000000000001</v>
       </c>
     </row>
     <row r="4620">
@@ -85485,7 +85485,7 @@
         </is>
       </c>
       <c r="D4726" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4727">
@@ -89931,7 +89931,7 @@
         </is>
       </c>
       <c r="D4973" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="4974">
@@ -89949,7 +89949,7 @@
         </is>
       </c>
       <c r="D4974" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4975">
@@ -89967,7 +89967,7 @@
         </is>
       </c>
       <c r="D4975" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="4976">
@@ -92002,6 +92002,204 @@
       </c>
       <c r="D5088" t="n">
         <v>2.3</v>
+      </c>
+    </row>
+    <row r="5089">
+      <c r="A5089" t="n">
+        <v>5088</v>
+      </c>
+      <c r="B5089" t="inlineStr">
+        <is>
+          <t>8605062103076</t>
+        </is>
+      </c>
+      <c r="C5089" t="inlineStr">
+        <is>
+          <t>PISTOLJ SAPUNICA NA BATERIJE</t>
+        </is>
+      </c>
+      <c r="D5089" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="5090">
+      <c r="A5090" t="n">
+        <v>5089</v>
+      </c>
+      <c r="B5090" t="inlineStr">
+        <is>
+          <t>8445290502353</t>
+        </is>
+      </c>
+      <c r="C5090" t="inlineStr">
+        <is>
+          <t>NESCAFE GOLD CREME 95G</t>
+        </is>
+      </c>
+      <c r="D5090" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="5091">
+      <c r="A5091" t="n">
+        <v>5090</v>
+      </c>
+      <c r="B5091" t="inlineStr">
+        <is>
+          <t>8606012143548</t>
+        </is>
+      </c>
+      <c r="C5091" t="inlineStr">
+        <is>
+          <t>LMX TOX SPR.PROT.LET.INS. 500ML</t>
+        </is>
+      </c>
+      <c r="D5091" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5092">
+      <c r="A5092" t="n">
+        <v>5091</v>
+      </c>
+      <c r="B5092" t="inlineStr">
+        <is>
+          <t>5999109545596</t>
+        </is>
+      </c>
+      <c r="C5092" t="inlineStr">
+        <is>
+          <t>AIRWICK FRESHMATIC 250ML COOL</t>
+        </is>
+      </c>
+      <c r="D5092" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="5093">
+      <c r="A5093" t="n">
+        <v>5092</v>
+      </c>
+      <c r="B5093" t="inlineStr">
+        <is>
+          <t>5054563204097</t>
+        </is>
+      </c>
+      <c r="C5093" t="inlineStr">
+        <is>
+          <t>AQUAFRESH PZZ ACTIVE FRESH 125ML</t>
+        </is>
+      </c>
+      <c r="D5093" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5094">
+      <c r="A5094" t="n">
+        <v>5093</v>
+      </c>
+      <c r="B5094" t="inlineStr">
+        <is>
+          <t>8720181347139</t>
+        </is>
+      </c>
+      <c r="C5094" t="inlineStr">
+        <is>
+          <t>DOVE DEO 150ML CUCUMBER</t>
+        </is>
+      </c>
+      <c r="D5094" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5095">
+      <c r="A5095" t="n">
+        <v>5094</v>
+      </c>
+      <c r="B5095" t="inlineStr">
+        <is>
+          <t>8681554633115</t>
+        </is>
+      </c>
+      <c r="C5095" t="inlineStr">
+        <is>
+          <t>FAIRY MAR.ZA CIS 100/1 UNI. LAVAN.</t>
+        </is>
+      </c>
+      <c r="D5095" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5096">
+      <c r="A5096" t="n">
+        <v>5095</v>
+      </c>
+      <c r="B5096" t="inlineStr">
+        <is>
+          <t>8605062103229</t>
+        </is>
+      </c>
+      <c r="C5096" t="inlineStr">
+        <is>
+          <t>JUMP ELF IGRAC. SA OPRUGOM</t>
+        </is>
+      </c>
+      <c r="D5096" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5097">
+      <c r="A5097" t="n">
+        <v>5096</v>
+      </c>
+      <c r="B5097" t="inlineStr">
+        <is>
+          <t>02610808</t>
+        </is>
+      </c>
+      <c r="C5097" t="inlineStr">
+        <is>
+          <t>POM. SIR LIVADA 45%MM</t>
+        </is>
+      </c>
+      <c r="D5097" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5098">
+      <c r="A5098" t="n">
+        <v>5097</v>
+      </c>
+      <c r="B5098" t="inlineStr">
+        <is>
+          <t>02119975</t>
+        </is>
+      </c>
+      <c r="C5098" t="inlineStr">
+        <is>
+          <t>MORTADELA KRALJICA</t>
+        </is>
+      </c>
+      <c r="D5098" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="5099">
+      <c r="A5099" t="n">
+        <v>5098</v>
+      </c>
+      <c r="B5099" t="inlineStr">
+        <is>
+          <t>8606033743055</t>
+        </is>
+      </c>
+      <c r="C5099" t="inlineStr">
+        <is>
+          <t>CHIPSY REBRASTI CILI 130G</t>
+        </is>
+      </c>
+      <c r="D5099" t="n">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
